--- a/Fitness_Database_Template.xlsx
+++ b/Fitness_Database_Template.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start_Here" sheetId="1" r:id="R06e1be4e42384054"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R7bfece57b28f409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="3" r:id="R596aec9545004984"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programs" sheetId="4" r:id="R5f392692f9d64149"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise_Cache" sheetId="5" r:id="R21efd4620ae14063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternatives" sheetId="6" r:id="R112016ae23d941bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ingredient_Cache" sheetId="7" r:id="R15520e33e242490e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recipes" sheetId="8" r:id="R4a4abbb75cbc4fe6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recipe_Ingredients" sheetId="9" r:id="R7105d38d2c164463"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workout_Sessions" sheetId="10" r:id="Rf6a32f76bd864f79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workout_Sets" sheetId="11" r:id="Rb0c5e6bcfb414e09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Food_Log" sheetId="12" r:id="R332e1cf080f041f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Body_Metrics" sheetId="13" r:id="Re417d8ee632d43ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Checkins" sheetId="14" r:id="R2118530ade8c453e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diet_Phases" sheetId="15" r:id="R9d8ff94f02594250"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cardio_Log" sheetId="16" r:id="R318c4edcbf7d418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progress_Photos" sheetId="17" r:id="R53030390d55143cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sync_Config" sheetId="18" r:id="Raa5901521005455a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_State" sheetId="19" r:id="R845a75d25d834b3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly_Review" sheetId="20" r:id="R7f8f0f9d7f6d4b65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookup" sheetId="21" r:id="R12e81618168e4ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment_Catalog" sheetId="22" r:id="R1973bd30165e4488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start_Here" sheetId="1" r:id="R79dc0ce731274553"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R65a4bd7ab3484bf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="3" r:id="R7df11d09a9a048c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programs" sheetId="4" r:id="Rf16381c9ee9643a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise_Cache" sheetId="5" r:id="R89b372ae26a64399"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternatives" sheetId="6" r:id="Rfa27dee741fa4561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ingredient_Cache" sheetId="7" r:id="Rcd05693fb7f44c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recipes" sheetId="8" r:id="R79ea834dd01f4b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recipe_Ingredients" sheetId="9" r:id="R0bffa7fa6b1b4ecd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workout_Sessions" sheetId="10" r:id="R4a96d1b0d6bd4658"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workout_Sets" sheetId="11" r:id="R83a7727281344edb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Food_Log" sheetId="12" r:id="R6ecc2401fe924d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Body_Metrics" sheetId="13" r:id="Rc3a08361526c4f7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Checkins" sheetId="14" r:id="R81f536b366cc4610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diet_Phases" sheetId="15" r:id="Rdde6ff097b224fe4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cardio_Log" sheetId="16" r:id="R98fc09250e544933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progress_Photos" sheetId="17" r:id="Rbddf667295a24100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sync_Config" sheetId="18" r:id="R7f5961be2ee1443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_State" sheetId="19" r:id="Rf3f79d903b1b460a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly_Review" sheetId="20" r:id="R33d3ef4c3454414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookup" sheetId="21" r:id="Re0fbdc0558d8451d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment_Catalog" sheetId="22" r:id="Rffbd9fd4941142ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,13 +34,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="0.0"/>
     <x:numFmt numFmtId="201" formatCode="dd-mmm"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="203" formatCode="yyyy-mm-dd hh:mm"/>
+    <x:numFmt numFmtId="204" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -81,8 +82,12 @@
       <x:color rgb="FF134E4A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -119,43 +124,33 @@
         <x:fgColor rgb="FFDFF4EF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F766E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDFF4EF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="10">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="104">
+  <x:cellXfs count="163">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -464,14 +459,232 @@
     </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="203" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="1">
+  <x:dxfs count="4">
     <x:dxf>
       <x:fill>
         <x:patternFill>
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF991B1B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -634,7 +847,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4f45ccbf0b3143cd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6417f86e8635469c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -809,124 +1022,153 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="92" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="60" t="str">
-        <x:v>Lift &amp; Cut 2.2 – Mobile App + Google Sheets Database</x:v>
-      </x:c>
-      <x:c r="B1" s="60"/>
+    <x:row r="1" ht="34" hidden="0" customHeight="1">
+      <x:c r="A1" s="111" t="str">
+        <x:v>Lift &amp; Cut 2.3</x:v>
+      </x:c>
+      <x:c r="B1" s="111" t="str">
+        <x:v>Recipe Import Foundation · Mobile App + Google Sheets Database</x:v>
+      </x:c>
       <x:c r="C1" s="5"/>
       <x:c r="D1" s="5"/>
       <x:c r="E1" s="5"/>
       <x:c r="F1" s="5"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="16"/>
       <x:c r="B2" s="16"/>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="61" t="str">
+    <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A3" s="116" t="str">
         <x:v>What this is</x:v>
       </x:c>
-      <x:c r="B3" s="16" t="str">
-        <x:v>A mobile-first fitness tracker plus a normalized spreadsheet database. The phone app is the main interface; this workbook is the cloud database, review tool, and manual-edit interface.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="61" t="str">
+      <x:c r="B3" s="117" t="str">
+        <x:v>A mobile-first fitness tracker plus a normalized spreadsheet database. The phone app remains the main interface; this workbook is the cloud database, review tool, and manual-edit interface.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="116" t="str">
+        <x:v>Recipe import</x:v>
+      </x:c>
+      <x:c r="B4" s="117" t="str">
+        <x:v>Import recipes from supported websites through your private Apps Script, from DRM-free EPUB cookbooks locally on the phone, or from pasted recipe text.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A5" s="116" t="str">
+        <x:v>Nutrition calculation</x:v>
+      </x:c>
+      <x:c r="B5" s="117" t="str">
+        <x:v>Recipe nutrition is calculated from matched ingredient records. Confirmed package-label values take priority; USDA FoodData Central and Open Food Facts can be searched through the app when the v2.3 backend is deployed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A6" s="116" t="str">
+        <x:v>First setup</x:v>
+      </x:c>
+      <x:c r="B6" s="117" t="str">
+        <x:v>1) Import this workbook into Google Sheets. 2) Open Extensions &gt; Apps Script. 3) Paste the v2.3 Code.gs. 4) Run initialiseFitnessDatabase. 5) Deploy as a Web App. 6) Enter the /exec URL and private key in the phone app.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A7" s="116" t="str">
+        <x:v>Existing installation</x:v>
+      </x:c>
+      <x:c r="B7" s="117" t="str">
+        <x:v>Replace Code.gs with the v2.3 script, save, run initialiseFitnessDatabase, then edit the existing web-app deployment and select New version. The private key remains unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A8" s="116" t="str">
+        <x:v>Optional USDA key</x:v>
+      </x:c>
+      <x:c r="B8" s="117" t="str">
+        <x:v>Lift &amp; Cut can use the rate-limited USDA DEMO_KEY. For more reference searches, use Lift &amp; Cut &gt; Set USDA FoodData Central API key. The key is stored privately in Apps Script properties, not in this workbook.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A9" s="116" t="str">
+        <x:v>Ingredient review</x:v>
+      </x:c>
+      <x:c r="B9" s="117" t="str">
+        <x:v>Imported ingredients are marked Confirmed, Likely, Needs unit conversion, or Unmatched. Review serving sizes, raw/cooked state, household measures, and branded labels before relying on calculated macros.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A10" s="116" t="str">
         <x:v>Equipment-aware training</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
-        <x:v>Select equipment in the phone app or in Equipment_Catalog. Exercise choices, substitutions, workout warnings, and equipment-matched program copies use structured equipment requirements.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="61" t="str">
-        <x:v>First setup</x:v>
-      </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>1) Import this workbook into Google Sheets. 2) Open Extensions &gt; Apps Script. 3) Paste the v2.2 Code.gs. 4) Run initialiseFitnessDatabase. 5) Deploy as a Web App. 6) Enter the /exec URL and private key in the phone app.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="61" t="str">
-        <x:v>Existing installation</x:v>
-      </x:c>
-      <x:c r="B6" s="16" t="str">
-        <x:v>Replace Code.gs with the v2.2 script, save, run initialiseFitnessDatabase, then create a new web-app deployment version. The private key remains unchanged.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="61" t="str">
-        <x:v>Editing equipment in Sheets</x:v>
-      </x:c>
-      <x:c r="B7" s="16" t="str">
-        <x:v>Set Selected to TRUE/FALSE in Equipment_Catalog, then use Lift &amp; Cut &gt; Rebuild app state from edited tables. Pull &amp; merge on the phone before making a new phone push.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="61" t="str">
-        <x:v>Editing exercises in Sheets</x:v>
-      </x:c>
-      <x:c r="B8" s="16" t="str">
-        <x:v>EquipmentOptionsJSON is a JSON array of valid equipment bundles. Example: [["Barbell + plates","Power rack / squat stands"],["Dumbbells"]]. Each inner array is one complete valid setup.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="61" t="str">
+      <x:c r="B10" s="117" t="str">
+        <x:v>Select equipment in the phone app or Equipment_Catalog. Exercise choices, substitutions, workout warnings, and equipment-matched program copies use structured equipment requirements.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A11" s="116" t="str">
         <x:v>Normal workflow</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
-        <x:v>Log workouts, food, recipes, measurements, check-ins, cardio, and diet phases in the phone app. Push to Sheets when you want a cloud backup and spreadsheet refresh.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="61" t="str">
+      <x:c r="B11" s="117" t="str">
+        <x:v>Log workouts, food, recipes, measurements, check-ins, cardio, and diet phases in the phone app. Push to Sheets for cloud backup and spreadsheet review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A12" s="116" t="str">
         <x:v>Conflict safety</x:v>
       </x:c>
-      <x:c r="B10" s="16" t="str">
+      <x:c r="B12" s="117" t="str">
         <x:v>The backend uses cloud revisions. If both the spreadsheet and phone changed, the app blocks a normal push until you pull and merge or deliberately force the phone copy.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="61" t="str">
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A13" s="116" t="str">
         <x:v>Photos</x:v>
       </x:c>
-      <x:c r="B11" s="16" t="str">
+      <x:c r="B13" s="117" t="str">
         <x:v>Progress-photo files stay on the phone and are not placed in Google Sheets. Their metadata appears in Progress_Photos. Full JSON backup includes the compressed photos.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="61" t="str">
+    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A14" s="116" t="str">
         <x:v>RFL</x:v>
       </x:c>
-      <x:c r="B12" s="16" t="str">
+      <x:c r="B14" s="117" t="str">
         <x:v>RFL targets are intentionally blank. Enter only values calculated from your edition of Lyle McDonald’s RFL. The RFL2 program reduces training volume to preserve muscle and strength.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="62" t="str">
+    <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A15" s="116" t="str">
         <x:v>Dietary defaults</x:v>
       </x:c>
-      <x:c r="B13" s="16" t="str">
-        <x:v>Recipe filters can avoid bell peppers and shellfish. Ingredient values are examples only; replace them with your food-label and measured-portion values.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="62" t="str">
+      <x:c r="B15" s="117" t="str">
+        <x:v>Recipe flags can identify possible bell peppers and shellfish. Reference ingredient values are starting points only; verify package labels and measured portions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="116" t="str">
         <x:v>Backup</x:v>
       </x:c>
-      <x:c r="B14" s="16" t="str">
+      <x:c r="B16" s="117" t="str">
         <x:v>Use the app’s full JSON export regularly. Keep at least one copy outside the phone.</x:v>
       </x:c>
     </x:row>
+    <x:row r="17"/>
+    <x:row r="18"/>
+    <x:row r="19"/>
+    <x:row r="20"/>
+    <x:row r="21"/>
+    <x:row r="22"/>
+    <x:row r="23"/>
+    <x:row r="24"/>
+    <x:row r="25"/>
+    <x:row r="26"/>
+    <x:row r="27"/>
+    <x:row r="28"/>
+    <x:row r="29"/>
+    <x:row r="30"/>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -1584,114 +1826,125 @@
   <x:cols>
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="44" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="56" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="66" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="63" t="str">
+      <x:c r="A1" s="118" t="str">
         <x:v>Field</x:v>
       </x:c>
-      <x:c r="B1" s="63" t="str">
+      <x:c r="B1" s="118" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C1" s="63" t="str">
+      <x:c r="C1" s="118" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="64" t="str">
+      <x:c r="A2" s="133" t="str">
         <x:v>AppVersion</x:v>
       </x:c>
-      <x:c r="B2" s="65" t="str">
-        <x:v>2.2.0</x:v>
-      </x:c>
-      <x:c r="C2" s="66" t="str">
+      <x:c r="B2" s="134" t="str">
+        <x:v>2.3.0</x:v>
+      </x:c>
+      <x:c r="C2" s="135" t="str">
         <x:v>Backend/app version</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="67" t="str">
+      <x:c r="A3" s="136" t="str">
         <x:v>SchemaVersion</x:v>
       </x:c>
-      <x:c r="B3" s="68" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="69" t="str">
+      <x:c r="B3" s="137" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="138" t="str">
         <x:v>Database schema</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="67" t="str">
+      <x:c r="A4" s="136" t="str">
         <x:v>SpreadsheetID</x:v>
       </x:c>
-      <x:c r="B4" s="68"/>
-      <x:c r="C4" s="69" t="str">
+      <x:c r="B4" s="137"/>
+      <x:c r="C4" s="138" t="str">
         <x:v>Filled by Apps Script setup</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="67" t="str">
+      <x:c r="A5" s="136" t="str">
         <x:v>PrivateSyncKey</x:v>
       </x:c>
-      <x:c r="B5" s="68"/>
-      <x:c r="C5" s="69" t="str">
+      <x:c r="B5" s="137"/>
+      <x:c r="C5" s="138" t="str">
         <x:v>Generated by Apps Script setup; keep private</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="67" t="str">
+      <x:c r="A6" s="136" t="str">
         <x:v>WebAppURL</x:v>
       </x:c>
-      <x:c r="B6" s="68"/>
-      <x:c r="C6" s="69" t="str">
+      <x:c r="B6" s="137"/>
+      <x:c r="C6" s="138" t="str">
         <x:v>Paste the deployed /exec URL here for reference</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="67" t="str">
+      <x:c r="A7" s="136" t="str">
         <x:v>CloudRevision</x:v>
       </x:c>
-      <x:c r="B7" s="68" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C7" s="69" t="str">
+      <x:c r="B7" s="137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="138" t="str">
         <x:v>Server-assigned revision</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="67" t="str">
+      <x:c r="A8" s="136" t="str">
         <x:v>LastPushAt</x:v>
       </x:c>
-      <x:c r="B8" s="68"/>
-      <x:c r="C8" s="69" t="str">
+      <x:c r="B8" s="137"/>
+      <x:c r="C8" s="138" t="str">
         <x:v>Most recent successful phone push</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="67" t="str">
+      <x:c r="A9" s="136" t="str">
         <x:v>LastRequestID</x:v>
       </x:c>
-      <x:c r="B9" s="68"/>
-      <x:c r="C9" s="69" t="str">
+      <x:c r="B9" s="137"/>
+      <x:c r="C9" s="138" t="str">
         <x:v>Most recent POST request</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="67" t="str">
+      <x:c r="A10" s="136" t="str">
         <x:v>LastStatus</x:v>
       </x:c>
-      <x:c r="B10" s="68"/>
-      <x:c r="C10" s="69" t="str">
+      <x:c r="B10" s="137"/>
+      <x:c r="C10" s="138" t="str">
         <x:v>Most recent POST result</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="77" t="str">
+      <x:c r="A11" s="140" t="str">
         <x:v>LastError</x:v>
       </x:c>
-      <x:c r="B11" s="78"/>
-      <x:c r="C11" s="79" t="str">
+      <x:c r="B11" s="141"/>
+      <x:c r="C11" s="142" t="str">
         <x:v>Most recent POST error</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="143" t="str">
+        <x:v>USDA_API_Key_Status</x:v>
+      </x:c>
+      <x:c r="B12" s="143" t="str">
+        <x:v>Using USDA DEMO_KEY</x:v>
+      </x:c>
+      <x:c r="C12" s="143" t="str">
+        <x:v>Personal keys are stored privately in Apps Script properties</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1704,120 +1957,108 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="90" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="100" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="63" t="str">
+      <x:c r="A1" s="118" t="str">
         <x:v>ChunkNo</x:v>
       </x:c>
-      <x:c r="B1" s="63" t="str">
+      <x:c r="B1" s="118" t="str">
         <x:v>StateChunk</x:v>
       </x:c>
-      <x:c r="C1" s="63" t="str">
+      <x:c r="C1" s="118" t="str">
         <x:v>Revision</x:v>
       </x:c>
-      <x:c r="D1" s="63" t="str">
+      <x:c r="D1" s="118" t="str">
         <x:v>UpdatedAt</x:v>
       </x:c>
-      <x:c r="E1" s="63" t="str">
+      <x:c r="E1" s="118" t="str">
         <x:v>LastRequestID</x:v>
       </x:c>
-      <x:c r="F1" s="63" t="str">
+      <x:c r="F1" s="118" t="str">
         <x:v>LastStatus</x:v>
       </x:c>
-      <x:c r="G1" s="63" t="str">
+      <x:c r="G1" s="118" t="str">
         <x:v>LastError</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="64" t="n">
+      <x:c r="A2" s="133" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="65" t="str">
-        <x:v>{"version":2,"schemaVersion":3,"createdFor":"","meta":{"appVersion":"2.2.0","revision":0,"lastModifiedAt":"2026-07-19T15:45:00.000Z","lastCloudSyncAt":"","lastCloudRevision":0,"clientId":""},"settings":{"profileName":"","age":"","heightCm":"","targetWeightKg":"","activeProgram":"UL4","dietMode":"Normal / moderate deficit","normalCalorieTarget":2200,"normalProteinTarget":170,"normalCarbTarget":180,"normalFatTarget":70,"rflCalorieTarget":"","rflProteinTarget":"","rflCarbTarget":"","rflFatTarget":"","stepsTarget":8000,"sleepTargetHrs":7.5,"waterTargetMl":2500,"noBellPeppers":false,"noShellfish":false,"lastSession":"UL4|lower-a","weekStartsMonday":true,"theme":"system","autoSync":false,"syncUrl":"","syncKey":"","availableEquipment":["Bodyweight / floor space","Power rack / squat stands","Barbell + plates","Adjustable bench","Adjustable dumbbells","Cable station / functional trainer","Pull-up bar","Gymnastic rings / suspension trainer","Calf raise platform / machine","Ankle strap","Rope cable attachment","Ab wheel"],"restTimerDefaultSec":120,"autoRestTimer":true,"restTimerSound":true,"autoAdvanceSets":true,"weightIncrementKg":2.5,"smallWeightIncrementKg":1,"trainView":"workout","dumbbellWeightIncrementKg":2,"customEquipment":[],"equipmentProfileName":"Custom home gym"},"programs":[{"id":"UL4","name":"Normal 4-day Upper/Lower","mode":"Normal / moderate deficit","sessions":[{"id":"lower-a","name":"Lower A","day":"Monday","exercises":[{"id":"ul4-lower-a-1","name":"High-bar back squat","sets":3,"reps":"6-8","rir":"1-2","notes":"Use controlled depth; substitute if back/knees complain.","order":1,"exerciseId":"EX001","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-2","name":"Romanian deadlift","sets":3,"reps":"6-8","rir":"1-2","notes":"Replace with hip thrust or cable pull-through if lower back is limiting.","order":2,"exerciseId":"EX008","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-3","name":"Bulgarian split squat","sets":2,"reps":"8-12 each leg","rir":"1-2","notes":"","order":3,"exerciseId":"EX006","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-4","name":"Cable leg curl","sets":2,"reps":"10-15","rir":"1-2","notes":"","order":4,"exerciseId":"EX012","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-5","name":"Standing calf raise","sets":3,"reps":"8-15","rir":"1-2","notes":"","order":5,"exerciseId":"EX013","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-6","name":"Dead bug or Pallof press","sets":2,"reps":"10-15","rir":"2","notes":"","order":6,"exerciseId":"EX124","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"}],"order":1,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""},{"id":"upper-a","name":"Upper A","day":"Tuesday","exercises":[{"id":"ul4-upper-a-1","name":"Barbell bench press","sets":3,"reps":"6-8","rir":"1-2","notes":"","order":1,"exerciseId":"EX014","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-2","name":"Chest-supported dumbbell row","sets":3,"reps":"6-10","rir":"1-2","notes":"Back-friendly row option.","order":2,"exerciseId":"EX023","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-3","name":"Incline dumbbell press","sets":2,"reps":"8-12","rir":"1-2","notes":"","order":3,"exerciseId":"EX016","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-4","name":"Cable lat pulldown or ring chin-up","sets":2,"reps":"8-12","rir":"1-2","notes":"","order":4,"exerciseId":"EX125","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-upper-a-5","name":"Cable lateral raise","sets":3,"reps":"12-20","rir":"1","notes":"GVS-style controlled delt work.","order":5,"exerciseId":"EX033","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-6","name":"Cable triceps pushdown","sets":2,"reps":"10-15","rir":"1","notes":"","order":6,"exerciseId":"EX038","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-7","name":"Incline dumbbell or cable curl","sets":2,"reps":"10-15","rir":"1","notes":"","order":7,"exerciseId":"EX126","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"}],"order":2,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""},{"id":"lower-b","name":"Lower B","day":"Thursday","exercises":[{"id":"ul4-lower-b-1","name":"Front squat or heels-elevated squat","sets":3,"reps":"6-10","rir":"1-2","notes":"Choose the squat pattern that feels best.","order":1,"exerciseId":"EX127","restSec":150,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-lower-b-2","name":"Barbell hip thrust","sets":3,"reps":"8-12","rir":"1-2","notes":"","order":2,"exerciseId":"EX010","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-b-3","name":"Reverse lunge","sets":2,"reps":"8-12 each leg","rir":"1-2","notes":"","order":3,"exerciseId":"EX007","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-b-4","name":"Cable leg curl","sets":2,"reps":"12-20","rir":"1-2","notes":"","order":4,"exerciseId":"EX012","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-b-5","name":"Standing calf raise","sets":3,"reps":"12-20","rir":"1-2","notes":"","order":5,"exerciseId":"EX013","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-b-6","name":"Ab wheel or cable crunch","sets":2,"reps":"8-15","rir":"1-2","notes":"","order":6,"exerciseId":"EX128","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"}],"order":3,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""},{"id":"upper-b","name":"Upper B","day":"Friday","exercises":[{"id":"ul4-upper-b-1","name":"Weighted chin-up or heavy pulldown","sets":3,"reps":"6-8","rir":"1-2","notes":"","order":1,"exerciseId":"EX129","restSec":150,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-upper-b-2","name":"Seated dumbbell overhead press","sets":3,"reps":"6-10","rir":"1-2","notes":"","order":2,"exerciseId":"EX020","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-b-3","name":"One-arm cable row","sets":2,"reps":"8-12","rir":"1-2","notes":"","order":3,"exerciseId":"EX024","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-b-4","name":"Close-grip bench press or weighted ring push-up","sets":2,"reps":"8-12","rir":"1-2","notes":"","order":4,"exerciseId":"EX130","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-upper-b-5","name":"Cable rear-delt fly or face pull","sets":3,"reps":"12-20","rir":"1","notes":"","order":5,"exerciseId":"EX131","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-upper-b-6","name":"Cable lateral raise","sets":2,"reps":"12-20","rir":"1","notes":"","order":6,"exerciseId":"EX033","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-b-7","name":"Overhead cable triceps extension","sets":2,"reps":"10-15","rir":"1","notes":"","order":7,"exerciseId":"EX039","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-b-8","name":"Dumbbell hammer curl","sets":2,"reps":"10-15","rir":"1","notes":"","order":8,"exerciseId":"EX043","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"}],"order":4,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""}],"description":"Four-day upper/lower plan for normal dieting, maintenance, or slow fat loss.","active":true,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"RFL2","name":"RFL 2-day Full Body","mode":"RFL / PSMF","sessions":[{"id":"rfl-full-body-a","name":"RFL Full Body A","day":"Monday","exercises":[{"id":"rfl2-rfl-full-body-a-1","name":"High-bar back squat","sets":2,"reps":"5-8","rir":"2-3","notes":"Preserve strength; no grinders.","order":1,"exerciseId":"EX001","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-2","name":"Barbell bench press","sets":2,"reps":"5-8","rir":"2-3","notes":"","order":2,"exerciseId":"EX014","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-3","name":"Chest-supported dumbbell row","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":3,"exerciseId":"EX023","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-4","name":"Romanian deadlift or hip thrust","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":4,"exerciseId":"EX132","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-a-5","name":"Cable lateral raise","sets":1,"reps":"12-20","rir":"2-3","notes":"","order":5,"exerciseId":"EX033","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-6","name":"Cable curl","sets":1,"reps":"10-15","rir":"2-3","notes":"","order":6,"exerciseId":"EX041","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-7","name":"Cable triceps pushdown","sets":1,"reps":"10-15","rir":"2-3","notes":"","order":7,"exerciseId":"EX038","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"}],"order":1,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""},{"id":"rfl-full-body-b","name":"RFL Full Body B","day":"Thursday","exercises":[{"id":"rfl2-rfl-full-body-b-1","name":"Front squat or Bulgarian split squat","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":1,"exerciseId":"EX133","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-b-2","name":"Incline dumbbell or seated dumbbell press","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":2,"exerciseId":"EX022","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-b-3","name":"Pulldown or chin-up","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":3,"exerciseId":"EX134","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-b-4","name":"Hip thrust or cable leg curl","sets":2,"reps":"8-12","rir":"2-3","notes":"","order":4,"exerciseId":"EX135","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-b-5","name":"Rear-delt cable fly","sets":1,"reps":"12-20","rir":"2-3","notes":"","order":5,"exerciseId":"EX037","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-b-6","name":"Hammer curl","sets":1,"reps":"10-15","rir":"2-3","notes":"","order":6,"exerciseId":"EX136","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-b-7","name":"Overhead triceps extension","sets":1,"reps":"10-15","rir":"2-3","notes":"","order":7,"exerciseId":"EX137","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"}],"order":2,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""}],"description":"Two-day low-volume full-body plan for RFL blocks; preserve strength rather than chase fatigue.","active":true,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"GVS_EXTRA","name":"Optional GVS-style Delts/Arms","mode":"Optional only outside RFL","sessions":[{"id":"delts-arms","name":"Delts/Arms","day":"Saturday","exercises":[{"id":"gvs_extra-delts-arms-1","name":"Cable lateral raise","sets":3,"reps":"15-25","rir":"0-1 on final safe set","notes":"Only if recovered; skip during RFL.","order":1,"exerciseId":"EX033","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"gvs_extra-delts-arms-2","name":"Cable rear-delt fly","sets":3,"reps":"15-25","rir":"0-1 on final safe set","notes":"","order":2,"exerciseId":"EX035","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"gvs_extra-delts-arms-3","name":"Cable or ring curl","sets":2,"reps":"10-15","rir":"1","notes":"","order":3,"exerciseId":"EX045","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"gvs_extra-delts-arms-4","name":"Overhead cable triceps extension","sets":2,"reps":"10-15","rir":"1","notes":"","order":4,"exerciseId":"EX039","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"gvs_extra-delts-arms-5","name":"Standing calf raise","sets":3,"reps":"12-20","rir":"1","notes":"","order":5,"exerciseId":"EX013","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"}],"order":1,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""}],"description":"Optional short delt/arm/calves session only when recovered and outside RFL.","active":true,"updatedAt":"2026-07-19T10:00:00.000Z"}],"exercises":[{"id":"EX001","name":"High-bar back squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates","primaryFor":"Squat","difficulty":"Main lift","notes":"Use if bracing and depth remain controlled.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[]},{"id":"EX002","name":"Front squat","muscle":"Quads / Core","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates","primaryFor":"Squat","difficulty":"Main lift","notes":"Useful if it is more back-friendly than back squat.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[]},{"id":"EX003","name":"Heels-elevated squat","muscle":"Quads","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates OR Dumbbells","primaryFor":"Squat","difficulty":"Main lift","notes":"More quad bias; use a small wedge or plates under heels.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates"],["Dumbbells"]],"optionalEquipment":["Slant board / heel wedge"]},{"id":"EX004","name":"Box squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates + Bench or box","primaryFor":"Squat","difficulty":"Substitution","notes":"Useful for controlled depth.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates","Bench or box"]],"optionalEquipment":[]},{"id":"EX005","name":"Goblet squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Dumbbells OR Kettlebells","primaryFor":"Squat","difficulty":"Substitution","notes":"Good warm-up or deload option.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"],["Kettlebells"]],"optionalEquipment":["Slant board / heel wedge"]},{"id":"EX006","name":"Bulgarian split squat","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bench or box","primaryFor":"Squat","difficulty":"Accessory","notes":"High stimulus with lower spinal loading.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bench or box"]],"optionalEquipment":["Dumbbells"]},{"id":"EX007","name":"Reverse lunge","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bodyweight / floor space","primaryFor":"Squat","difficulty":"Accessory","notes":"Usually knee-friendly if stride is controlled.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells"]},{"id":"EX008","name":"Romanian deadlift","muscle":"Hamstrings / Glutes","pattern":"Hip hinge","equipment":"Barbell + plates OR Dumbbells OR Kettlebells","primaryFor":"Hinge","difficulty":"Main lift","notes":"Only use if lower back is not the limiter.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates"],["Dumbbells"],["Kettlebells"]],"optionalEquipment":[]},{"id":"EX009","name":"Dumbbell Romanian deadlift","muscle":"Hamstrings / Glutes","pattern":"Hip hinge","equipment":"Dumbbells","primaryFor":"Hinge","difficulty":"Substitution","notes":"Easier to control than barbell for some lifters.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[]},{"id":"EX010","name":"Barbell hip thrust","muscle":"Glutes / Hamstrings","pattern":"Hip extension","equipment":"Barbell + plates + Bench","primaryFor":"Hinge","difficulty":"Main lift","notes":"Back-friendly hinge replacement.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates","Bench"]],"optionalEquipment":[]},{"id":"EX011","name":"Cable pull-through","muscle":"Glutes / Hamstrings","pattern":"Hip hinge","equipment":"Cable station","primaryFor":"Hinge","difficulty":"Substitution","notes":"Good replacement for RDL if back feels taxed.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX012","name":"Cable leg curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Cable station + Ankle strap","primaryFor":"Hamstrings","difficulty":"Accessory","notes":"Can use bench/prone setup with ankle strap.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station","Ankle strap"]],"optionalEquipment":[]},{"id":"EX013","name":"Standing calf raise","muscle":"Calves","pattern":"Calf raise","equipment":"Bodyweight / floor space","primaryFor":"Calves","difficulty":"Accessory","notes":"Pause in stretched and contracted positions.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Barbell + plates","Calf raise platform / machine"]},{"id":"EX014","name":"Barbell bench press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Power rack / squat stands + Barbell + plates + Bench","primaryFor":"Press","difficulty":"Main lift","notes":"Use safeties in rack.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates","Bench"]],"optionalEquipment":[]},{"id":"EX015","name":"Dumbbell bench press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Dumbbells + Bench","primaryFor":"Press","difficulty":"Substitution","notes":"Good shoulder-friendly press variation.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[]},{"id":"EX016","name":"Incline dumbbell press","muscle":"Upper chest","pattern":"Incline press","equipment":"Dumbbells + Adjustable bench","primaryFor":"Press","difficulty":"Accessory","notes":"Use controlled eccentric.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Adjustable bench"]],"optionalEquipment":[]},{"id":"EX017","name":"Floor press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Barbell + plates OR Dumbbells","primaryFor":"Press","difficulty":"Substitution","notes":"Good if shoulder range is sensitive.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates"],["Dumbbells"]],"optionalEquipment":["Power rack / squat stands"]},{"id":"EX018","name":"Close-grip bench press","muscle":"Triceps / Chest","pattern":"Horizontal press","equipment":"Power rack / squat stands + Barbell + plates + Bench","primaryFor":"Triceps","difficulty":"Accessory","notes":"Avoid painful wrist/elbow angles.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates","Bench"]],"optionalEquipment":[]},{"id":"EX019","name":"Weighted ring push-up","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Gymnastic rings / suspension trainer","primaryFor":"Press","difficulty":"Substitution","notes":"Progress by adding load or elevating feet.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Gymnastic rings / suspension trainer"]],"optionalEquipment":["Weighted vest"]},{"id":"EX020","name":"Seated dumbbell overhead press","muscle":"Delts / Triceps","pattern":"Vertical press","equipment":"Dumbbells + Bench","primaryFor":"Press","difficulty":"Main lift","notes":"More back-friendly than standing press.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[]},{"id":"EX021","name":"Standing overhead press","muscle":"Delts / Triceps","pattern":"Vertical press","equipment":"Barbell + plates","primaryFor":"Press","difficulty":"Substitution","notes":"Use only if bracing is solid.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates"]],"optionalEquipment":[]},{"id":"EX022","name":"Incline dumbbell or seated dumbbell press","muscle":"Chest / Delts","pattern":"Incline or vertical press","equipment":"Dumbbells + Adjustable bench","primaryFor":"Press","difficulty":"RFL combined slot","notes":"Choose the one that feels strongest that day.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Adjustable bench"]],"optionalEquipment":[]},{"id":"EX023","name":"Chest-supported dumbbell row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Dumbbells + Adjustable bench","primaryFor":"Row","difficulty":"Main lift","notes":"Preferred back-friendly row.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Adjustable bench"]],"optionalEquipment":[]},{"id":"EX024","name":"One-arm cable row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Cable station","primaryFor":"Row","difficulty":"Accessory","notes":"Keep torso stable.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX025","name":"Seated cable row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Cable station OR Lat pulldown / low row machine","primaryFor":"Row","difficulty":"Substitution","notes":"Good controlled row option.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"],["Lat pulldown / low row machine"]],"optionalEquipment":[]},{"id":"EX026","name":"One-arm dumbbell row","muscle":"Lats / Upper back","pattern":"Horizontal pull","equipment":"Dumbbells + Bench","primaryFor":"Row","difficulty":"Substitution","notes":"Support torso on bench.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[]},{"id":"EX027","name":"Inverted row","muscle":"Upper back","pattern":"Horizontal pull","equipment":"Gymnastic rings / suspension trainer OR Power rack / squat stands + Barbell + plates","primaryFor":"Row","difficulty":"Substitution","notes":"Adjust body angle for difficulty.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Gymnastic rings / suspension trainer"],["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":["Weighted vest"]},{"id":"EX028","name":"Barbell row","muscle":"Upper back","pattern":"Horizontal pull","equipment":"Barbell + plates","primaryFor":"Row","difficulty":"Caution","notes":"Use only if lower back is not limiting.","rflOk":"No during RFL if fatigued","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates"]],"optionalEquipment":[]},{"id":"EX029","name":"Cable lat pulldown","muscle":"Lats","pattern":"Vertical pull","equipment":"Cable station OR Lat pulldown / low row machine","primaryFor":"Vertical pull","difficulty":"Main lift","notes":"Use controlled stretch.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"],["Lat pulldown / low row machine"]],"optionalEquipment":[]},{"id":"EX030","name":"Ring chin-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Gymnastic rings / suspension trainer","primaryFor":"Vertical pull","difficulty":"Substitution","notes":"Use assistance if needed.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Gymnastic rings / suspension trainer"]],"optionalEquipment":["Resistance bands / tubes","Dip belt / loading belt"]},{"id":"EX031","name":"Weighted chin-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Pull-up bar + Dip belt / loading belt","primaryFor":"Vertical pull","difficulty":"Main lift","notes":"Only load when reps are clean.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Pull-up bar","Dip belt / loading belt"]],"optionalEquipment":[]},{"id":"EX032","name":"Straight-arm cable pulldown","muscle":"Lats","pattern":"Pullover","equipment":"Cable station","primaryFor":"Vertical pull","difficulty":"Accessory","notes":"Good lat isolation add-on.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX033","name":"Cable lateral raise","muscle":"Side delts","pattern":"Lateral raise","equipment":"Cable station","primaryFor":"Delts","difficulty":"GVS-style accessory","notes":"High-control delt work.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX034","name":"Dumbbell lateral raise","muscle":"Side delts","pattern":"Lateral raise","equipment":"Dumbbells","primaryFor":"Delts","difficulty":"Substitution","notes":"Use strict reps; avoid swinging.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[]},{"id":"EX035","name":"Cable rear-delt fly","muscle":"Rear delts","pattern":"Rear delt","equipment":"Cable station","primaryFor":"Rear delts","difficulty":"Accessory","notes":"Lead with elbows, not hands.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX036","name":"Face pull","muscle":"Rear delts / Upper back","pattern":"Rear delt / external rotation","equipment":"Cable station + Rope cable attachment","primaryFor":"Rear delts","difficulty":"Substitution","notes":"Good shoulder-health option.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station","Rope cable attachment"]],"optionalEquipment":[]},{"id":"EX037","name":"Rear-delt cable fly","muscle":"Rear delts","pattern":"Rear delt","equipment":"Cable station","primaryFor":"Rear delts","difficulty":"Accessory","notes":"Same as cable rear-delt fly.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX038","name":"Cable triceps pushdown","muscle":"Triceps","pattern":"Elbow extension","equipment":"Cable station","primaryFor":"Triceps","difficulty":"Accessory","notes":"Keep upper arm fixed.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX039","name":"Overhead cable triceps extension","muscle":"Triceps long head","pattern":"Elbow extension","equipment":"Cable station + Rope cable attachment","primaryFor":"Triceps","difficulty":"Accessory","notes":"Use pain-free elbow path.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station","Rope cable attachment"]],"optionalEquipment":[]},{"id":"EX040","name":"Dumbbell skull crusher","muscle":"Triceps","pattern":"Elbow extension","equipment":"Dumbbells","primaryFor":"Triceps","difficulty":"Substitution","notes":"Use light and controlled.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[]},{"id":"EX041","name":"Cable curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Cable station","primaryFor":"Biceps","difficulty":"Accessory","notes":"Constant tension curl.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX042","name":"Incline dumbbell curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Dumbbells + Adjustable bench","primaryFor":"Biceps","difficulty":"Accessory","notes":"Great long-head stretch; do not overextend shoulder.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Adjustable bench"]],"optionalEquipment":[]},{"id":"EX043","name":"Dumbbell hammer curl","muscle":"Biceps / Brachialis","pattern":"Elbow flexion","equipment":"Dumbbells","primaryFor":"Biceps","difficulty":"Accessory","notes":"Neutral-grip elbow-friendly curl.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[]},{"id":"EX044","name":"Ring curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Gymnastic rings / suspension trainer","primaryFor":"Biceps","difficulty":"Substitution","notes":"Adjust angle for difficulty.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Gymnastic rings / suspension trainer"]],"optionalEquipment":[]},{"id":"EX045","name":"Cable or ring curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Cable station OR Gymnastic rings / suspension trainer","primaryFor":"Biceps","difficulty":"Optional slot","notes":"Choose cable if elbows feel sensitive.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"],["Gymnastic rings / suspension trainer"]],"optionalEquipment":[]},{"id":"EX046","name":"Dead bug","muscle":"Core","pattern":"Anti-extension","equipment":"Bodyweight / floor space","primaryFor":"Core","difficulty":"Accessory","notes":"Control lower back position.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":[]},{"id":"EX047","name":"Pallof press","muscle":"Core","pattern":"Anti-rotation","equipment":"Cable station OR Resistance bands / tubes","primaryFor":"Core","difficulty":"Accessory","notes":"Pause each rep.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.00</x:v>
-      </x:c>
-      <x:c r="C2" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D2" s="101" t="n">
-        <x:v>46222.65625</x:v>
-      </x:c>
-      <x:c r="E2" s="65" t="str">
+      <x:c r="B2" s="134" t="str">
+        <x:v>{"version":2,"schemaVersion":4,"createdFor":"","meta":{"appVersion":"2.3.0","revision":0,"lastModifiedAt":"2026-07-19T20:55:00.000Z","lastCloudSyncAt":"","lastCloudRevision":0,"clientId":""},"settings":{"profileName":"","age":"","heightCm":"","targetWeightKg":"","activeProgram":"UL4","dietMode":"Normal / moderate deficit","normalCalorieTarget":2200,"normalProteinTarget":170,"normalCarbTarget":180,"normalFatTarget":70,"rflCalorieTarget":"","rflProteinTarget":"","rflCarbTarget":"","rflFatTarget":"","stepsTarget":8000,"sleepTargetHrs":7.5,"waterTargetMl":2500,"noBellPeppers":false,"noShellfish":false,"lastSession":"UL4|lower-a","weekStartsMonday":true,"theme":"system","autoSync":false,"syncUrl":"","syncKey":"","availableEquipment":["Bodyweight / floor space","Power rack / squat stands","Barbell + plates","Adjustable bench","Adjustable dumbbells","Cable station / functional trainer","Pull-up bar","Gymnastic rings / suspension trainer","Calf raise platform / machine","Ankle strap","Rope cable attachment","Ab wheel"],"restTimerDefaultSec":120,"autoRestTimer":true,"restTimerSound":true,"autoAdvanceSets":true,"weightIncrementKg":2.5,"smallWeightIncrementKg":1,"trainView":"workout","dumbbellWeightIncrementKg":2,"customEquipment":[],"equipmentProfileName":"Custom home gym","recipeImportAutoMatch":true,"recipeImportPreferMetric":true,"foodReferenceSource":"USDA + Open Food Facts"},"programs":[{"id":"UL4","name":"Normal 4-day Upper/Lower","mode":"Normal / moderate deficit","sessions":[{"id":"lower-a","name":"Lower A","day":"Monday","exercises":[{"id":"ul4-lower-a-1","name":"High-bar back squat","sets":3,"reps":"6-8","rir":"1-2","notes":"Use controlled depth; substitute if back/knees complain.","order":1,"exerciseId":"EX001","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-2","name":"Romanian deadlift","sets":3,"reps":"6-8","rir":"1-2","notes":"Replace with hip thrust or cable pull-through if lower back is limiting.","order":2,"exerciseId":"EX008","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-3","name":"Bulgarian split squat","sets":2,"reps":"8-12 each leg","rir":"1-2","notes":"","order":3,"exerciseId":"EX006","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-4","name":"Cable leg curl","sets":2,"reps":"10-15","rir":"1-2","notes":"","order":4,"exerciseId":"EX012","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-5","name":"Standing calf raise","sets":3,"reps":"8-15","rir":"1-2","notes":"","order":5,"exerciseId":"EX013","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-a-6","name":"Dead bug or Pallof press","sets":2,"reps":"10-15","rir":"2","notes":"","order":6,"exerciseId":"EX124","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"}],"order":1,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""},{"id":"upper-a","name":"Upper A","day":"Tuesday","exercises":[{"id":"ul4-upper-a-1","name":"Barbell bench press","sets":3,"reps":"6-8","rir":"1-2","notes":"","order":1,"exerciseId":"EX014","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-2","name":"Chest-supported dumbbell row","sets":3,"reps":"6-10","rir":"1-2","notes":"Back-friendly row option.","order":2,"exerciseId":"EX023","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-3","name":"Incline dumbbell press","sets":2,"reps":"8-12","rir":"1-2","notes":"","order":3,"exerciseId":"EX016","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-4","name":"Cable lat pulldown or ring chin-up","sets":2,"reps":"8-12","rir":"1-2","notes":"","order":4,"exerciseId":"EX125","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-upper-a-5","name":"Cable lateral raise","sets":3,"reps":"12-20","rir":"1","notes":"GVS-style controlled delt work.","order":5,"exerciseId":"EX033","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-6","name":"Cable triceps pushdown","sets":2,"reps":"10-15","rir":"1","notes":"","order":6,"exerciseId":"EX038","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-a-7","name":"Incline dumbbell or cable curl","sets":2,"reps":"10-15","rir":"1","notes":"","order":7,"exerciseId":"EX126","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"}],"order":2,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""},{"id":"lower-b","name":"Lower B","day":"Thursday","exercises":[{"id":"ul4-lower-b-1","name":"Front squat or heels-elevated squat","sets":3,"reps":"6-10","rir":"1-2","notes":"Choose the squat pattern that feels best.","order":1,"exerciseId":"EX127","restSec":150,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-lower-b-2","name":"Barbell hip thrust","sets":3,"reps":"8-12","rir":"1-2","notes":"","order":2,"exerciseId":"EX010","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-b-3","name":"Reverse lunge","sets":2,"reps":"8-12 each leg","rir":"1-2","notes":"","order":3,"exerciseId":"EX007","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-b-4","name":"Cable leg curl","sets":2,"reps":"12-20","rir":"1-2","notes":"","order":4,"exerciseId":"EX012","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-b-5","name":"Standing calf raise","sets":3,"reps":"12-20","rir":"1-2","notes":"","order":5,"exerciseId":"EX013","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-lower-b-6","name":"Ab wheel or cable crunch","sets":2,"reps":"8-15","rir":"1-2","notes":"","order":6,"exerciseId":"EX128","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"}],"order":3,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""},{"id":"upper-b","name":"Upper B","day":"Friday","exercises":[{"id":"ul4-upper-b-1","name":"Weighted chin-up or heavy pulldown","sets":3,"reps":"6-8","rir":"1-2","notes":"","order":1,"exerciseId":"EX129","restSec":150,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-upper-b-2","name":"Seated dumbbell overhead press","sets":3,"reps":"6-10","rir":"1-2","notes":"","order":2,"exerciseId":"EX020","restSec":150,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-b-3","name":"One-arm cable row","sets":2,"reps":"8-12","rir":"1-2","notes":"","order":3,"exerciseId":"EX024","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-b-4","name":"Close-grip bench press or weighted ring push-up","sets":2,"reps":"8-12","rir":"1-2","notes":"","order":4,"exerciseId":"EX130","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-upper-b-5","name":"Cable rear-delt fly or face pull","sets":3,"reps":"12-20","rir":"1","notes":"","order":5,"exerciseId":"EX131","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ul4-upper-b-6","name":"Cable lateral raise","sets":2,"reps":"12-20","rir":"1","notes":"","order":6,"exerciseId":"EX033","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-b-7","name":"Overhead cable triceps extension","sets":2,"reps":"10-15","rir":"1","notes":"","order":7,"exerciseId":"EX039","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ul4-upper-b-8","name":"Dumbbell hammer curl","sets":2,"reps":"10-15","rir":"1","notes":"","order":8,"exerciseId":"EX043","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"}],"order":4,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""}],"description":"Four-day upper/lower plan for normal dieting, maintenance, or slow fat loss.","active":true,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"RFL2","name":"RFL 2-day Full Body","mode":"RFL / PSMF","sessions":[{"id":"rfl-full-body-a","name":"RFL Full Body A","day":"Monday","exercises":[{"id":"rfl2-rfl-full-body-a-1","name":"High-bar back squat","sets":2,"reps":"5-8","rir":"2-3","notes":"Preserve strength; no grinders.","order":1,"exerciseId":"EX001","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-2","name":"Barbell bench press","sets":2,"reps":"5-8","rir":"2-3","notes":"","order":2,"exerciseId":"EX014","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-3","name":"Chest-supported dumbbell row","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":3,"exerciseId":"EX023","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-4","name":"Romanian deadlift or hip thrust","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":4,"exerciseId":"EX132","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-a-5","name":"Cable lateral raise","sets":1,"reps":"12-20","rir":"2-3","notes":"","order":5,"exerciseId":"EX033","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-6","name":"Cable curl","sets":1,"reps":"10-15","rir":"2-3","notes":"","order":6,"exerciseId":"EX041","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-a-7","name":"Cable triceps pushdown","sets":1,"reps":"10-15","rir":"2-3","notes":"","order":7,"exerciseId":"EX038","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"}],"order":1,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""},{"id":"rfl-full-body-b","name":"RFL Full Body B","day":"Thursday","exercises":[{"id":"rfl2-rfl-full-body-b-1","name":"Front squat or Bulgarian split squat","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":1,"exerciseId":"EX133","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-b-2","name":"Incline dumbbell or seated dumbbell press","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":2,"exerciseId":"EX022","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-b-3","name":"Pulldown or chin-up","sets":2,"reps":"6-10","rir":"2-3","notes":"","order":3,"exerciseId":"EX134","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-b-4","name":"Hip thrust or cable leg curl","sets":2,"reps":"8-12","rir":"2-3","notes":"","order":4,"exerciseId":"EX135","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-b-5","name":"Rear-delt cable fly","sets":1,"reps":"12-20","rir":"2-3","notes":"","order":5,"exerciseId":"EX037","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"rfl2-rfl-full-body-b-6","name":"Hammer curl","sets":1,"reps":"10-15","rir":"2-3","notes":"","order":6,"exerciseId":"EX136","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"rfl2-rfl-full-body-b-7","name":"Overhead triceps extension","sets":1,"reps":"10-15","rir":"2-3","notes":"","order":7,"exerciseId":"EX137","restSec":90,"updatedAt":"2026-07-19T15:45:00.000Z"}],"order":2,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""}],"description":"Two-day low-volume full-body plan for RFL blocks; preserve strength rather than chase fatigue.","active":true,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"GVS_EXTRA","name":"Optional GVS-style Delts/Arms","mode":"Optional only outside RFL","sessions":[{"id":"delts-arms","name":"Delts/Arms","day":"Saturday","exercises":[{"id":"gvs_extra-delts-arms-1","name":"Cable lateral raise","sets":3,"reps":"15-25","rir":"0-1 on final safe set","notes":"Only if recovered; skip during RFL.","order":1,"exerciseId":"EX033","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"gvs_extra-delts-arms-2","name":"Cable rear-delt fly","sets":3,"reps":"15-25","rir":"0-1 on final safe set","notes":"","order":2,"exerciseId":"EX035","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"gvs_extra-delts-arms-3","name":"Cable or ring curl","sets":2,"reps":"10-15","rir":"1","notes":"","order":3,"exerciseId":"EX045","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"gvs_extra-delts-arms-4","name":"Overhead cable triceps extension","sets":2,"reps":"10-15","rir":"1","notes":"","order":4,"exerciseId":"EX039","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"gvs_extra-delts-arms-5","name":"Standing calf raise","sets":3,"reps":"12-20","rir":"1","notes":"","order":5,"exerciseId":"EX013","restSec":90,"updatedAt":"2026-07-19T10:00:00.000Z"}],"order":1,"updatedAt":"2026-07-19T10:00:00.000Z","notes":""}],"description":"Optional short delt/arm/calves session only when recovered and outside RFL.","active":true,"updatedAt":"2026-07-19T10:00:00.000Z"}],"exercises":[{"id":"EX001","name":"High-bar back squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates","primaryFor":"Squat","difficulty":"Main lift","notes":"Use if bracing and depth remain controlled.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[]},{"id":"EX002","name":"Front squat","muscle":"Quads / Core","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates","primaryFor":"Squat","difficulty":"Main lift","notes":"Useful if it is more back-friendly than back squat.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[]},{"id":"EX003","name":"Heels-elevated squat","muscle":"Quads","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates OR Dumbbells","primaryFor":"Squat","difficulty":"Main lift","notes":"More quad bias; use a small wedge or plates under heels.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates"],["Dumbbells"]],"optionalEquipment":["Slant board / heel wedge"]},{"id":"EX004","name":"Box squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates + Bench or box","primaryFor":"Squat","difficulty":"Substitution","notes":"Useful for controlled depth.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates","Bench or box"]],"optionalEquipment":[]},{"id":"EX005","name":"Goblet squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Dumbbells OR Kettlebells","primaryFor":"Squat","difficulty":"Substitution","notes":"Good warm-up or deload option.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"],["Kettlebells"]],"optionalEquipment":["Slant board / heel wedge"]},{"id":"EX006","name":"Bulgarian split squat","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bench or box","primaryFor":"Squat","difficulty":"Accessory","notes":"High stimulus with lower spinal loading.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bench or box"]],"optionalEquipment":["Dumbbells"]},{"id":"EX007","name":"Reverse lunge","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bodyweight / floor space","primaryFor":"Squat","difficulty":"Accessory","notes":"Usually knee-friendly if stride is controlled.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells"]},{"id":"EX008","name":"Romanian deadlift","muscle":"Hamstrings / Glutes","pattern":"Hip hinge","equipment":"Barbell + plates OR Dumbbells OR Kettlebells","primaryFor":"Hinge","difficulty":"Main lift","notes":"Only use if lower back is not the limiter.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates"],["Dumbbells"],["Kettlebells"]],"optionalEquipment":[]},{"id":"EX009","name":"Dumbbell Romanian deadlift","muscle":"Hamstrings / Glutes","pattern":"Hip hinge","equipment":"Dumbbells","primaryFor":"Hinge","difficulty":"Substitution","notes":"Easier to control than barbell for some lifters.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[]},{"id":"EX010","name":"Barbell hip thrust","muscle":"Glutes / Hamstrings","pattern":"Hip extension","equipment":"Barbell + plates + Bench","primaryFor":"Hinge","difficulty":"Main lift","notes":"Back-friendly hinge replacement.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates","Bench"]],"optionalEquipment":[]},{"id":"EX011","name":"Cable pull-through","muscle":"Glutes / Hamstrings","pattern":"Hip hinge","equipment":"Cable station","primaryFor":"Hinge","difficulty":"Substitution","notes":"Good replacement for RDL if back feels taxed.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX012","name":"Cable leg curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Cable station + Ankle strap","primaryFor":"Hamstrings","difficulty":"Accessory","notes":"Can use bench/prone setup with ankle strap.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station","Ankle strap"]],"optionalEquipment":[]},{"id":"EX013","name":"Standing calf raise","muscle":"Calves","pattern":"Calf raise","equipment":"Bodyweight / floor space","primaryFor":"Calves","difficulty":"Accessory","notes":"Pause in stretched and contracted positions.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Barbell + plates","Calf raise platform / machine"]},{"id":"EX014","name":"Barbell bench press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Power rack / squat stands + Barbell + plates + Bench","primaryFor":"Press","difficulty":"Main lift","notes":"Use safeties in rack.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates","Bench"]],"optionalEquipment":[]},{"id":"EX015","name":"Dumbbell bench press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Dumbbells + Bench","primaryFor":"Press","difficulty":"Substitution","notes":"Good shoulder-friendly press variation.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[]},{"id":"EX016","name":"Incline dumbbell press","muscle":"Upper chest","pattern":"Incline press","equipment":"Dumbbells + Adjustable bench","primaryFor":"Press","difficulty":"Accessory","notes":"Use controlled eccentric.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Adjustable bench"]],"optionalEquipment":[]},{"id":"EX017","name":"Floor press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Barbell + plates OR Dumbbells","primaryFor":"Press","difficulty":"Substitution","notes":"Good if shoulder range is sensitive.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates"],["Dumbbells"]],"optionalEquipment":["Power rack / squat stands"]},{"id":"EX018","name":"Close-grip bench press","muscle":"Triceps / Chest","pattern":"Horizontal press","equipment":"Power rack / squat stands + Barbell + plates + Bench","primaryFor":"Triceps","difficulty":"Accessory","notes":"Avoid painful wrist/elbow angles.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Power rack / squat stands","Barbell + plates","Bench"]],"optionalEquipment":[]},{"id":"EX019","name":"Weighted ring push-up","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Gymnastic rings / suspension trainer","primaryFor":"Press","difficulty":"Substitution","notes":"Progress by adding load or elevating feet.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Gymnastic rings / suspension trainer"]],"optionalEquipment":["Weighted vest"]},{"id":"EX020","name":"Seated dumbbell overhead press","muscle":"Delts / Triceps","pattern":"Vertical press","equipment":"Dumbbells + Bench","primaryFor":"Press","difficulty":"Main lift","notes":"More back-friendly than standing press.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[]},{"id":"EX021","name":"Standing overhead press","muscle":"Delts / Triceps","pattern":"Vertical press","equipment":"Barbell + plates","primaryFor":"Press","difficulty":"Substitution","notes":"Use only if bracing is solid.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates"]],"optionalEquipment":[]},{"id":"EX022","name":"Incline dumbbell or seated dumbbell press","muscle":"Chest / Delts","pattern":"Incline or vertical press","equipment":"Dumbbells + Adjustable bench","primaryFor":"Press","difficulty":"RFL combined slot","notes":"Choose the one that feels strongest that day.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Adjustable bench"]],"optionalEquipment":[]},{"id":"EX023","name":"Chest-supported dumbbell row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Dumbbells + Adjustable bench","primaryFor":"Row","difficulty":"Main lift","notes":"Preferred back-friendly row.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Adjustable bench"]],"optionalEquipment":[]},{"id":"EX024","name":"One-arm cable row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Cable station","primaryFor":"Row","difficulty":"Accessory","notes":"Keep torso stable.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX025","name":"Seated cable row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Cable station OR Lat pulldown / low row machine","primaryFor":"Row","difficulty":"Substitution","notes":"Good controlled row option.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"],["Lat pulldown / low row machine"]],"optionalEquipment":[]},{"id":"EX026","name":"One-arm dumbbell row","muscle":"Lats / Upper back","pattern":"Horizontal pull","equipment":"Dumbbells + Bench","primaryFor":"Row","difficulty":"Substitution","notes":"Support torso on bench.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[]},{"id":"EX027","name":"Inverted row","muscle":"Upper back","pattern":"Horizontal pull","equipment":"Gymnastic rings / suspension trainer OR Power rack / squat stands + Barbell + plates","primaryFor":"Row","difficulty":"Substitution","notes":"Adjust body angle for difficulty.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Gymnastic rings / suspension trainer"],["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":["Weighted vest"]},{"id":"EX028","name":"Barbell row","muscle":"Upper back","pattern":"Horizontal pull","equipment":"Barbell + plates","primaryFor":"Row","difficulty":"Caution","notes":"Use only if lower back is not limiting.","rflOk":"No during RFL if fatigued","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Barbell + plates"]],"optionalEquipment":[]},{"id":"EX029","name":"Cable lat pulldown","muscle":"Lats","pattern":"Vertical pull","equipment":"Cable station OR Lat pulldown / low row machine","primaryFor":"Vertical pull","difficulty":"Main lift","notes":"Use controlled stretch.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"],["Lat pulldown / low row machine"]],"optionalEquipment":[]},{"id":"EX030","name":"Ring chin-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Gymnastic rings / suspension trainer","primaryFor":"Vertical pull","difficulty":"Substitution","notes":"Use assistance if needed.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Gymnastic rings / suspension trainer"]],"optionalEquipment":["Resistance bands / tubes","Dip belt / loading belt"]},{"id":"EX031","name":"Weighted chin-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Pull-up bar + Dip belt / loading belt","primaryFor":"Vertical pull","difficulty":"Main lift","notes":"Only load when reps are clean.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Pull-up bar","Dip belt / loading belt"]],"optionalEquipment":[]},{"id":"EX032","name":"Straight-arm cable pulldown","muscle":"Lats","pattern":"Pullover","equipment":"Cable station","primaryFor":"Vertical pull","difficulty":"Accessory","notes":"Good lat isolation add-on.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX033","name":"Cable lateral raise","muscle":"Side delts","pattern":"Lateral raise","equipment":"Cable station","primaryFor":"Delts","difficulty":"GVS-style accessory","notes":"High-control delt work.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX034","name":"Dumbbell lateral raise","muscle":"Side delts","pattern":"Lateral raise","equipment":"Dumbbells","primaryFor":"Delts","difficulty":"Substitution","notes":"Use strict reps; avoid swinging.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[]},{"id":"EX035","name":"Cable rear-delt fly","muscle":"Rear delts","pattern":"Rear delt","equipment":"Cable station","primaryFor":"Rear delts","difficulty":"Accessory","notes":"Lead with elbows, not hands.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX036","name":"Face pull","muscle":"Rear delts / Upper back","pattern":"Rear delt / external rotation","equipment":"Cable station + Rope cable attachment","primaryFor":"Rear delts","difficulty":"Substitution","notes":"Good shoulder-health option.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station","Rope cable attachment"]],"optionalEquipment":[]},{"id":"EX037","name":"Rear-delt cable fly","muscle":"Rear delts","pattern":"Rear delt","equipment":"Cable station","primaryFor":"Rear delts","difficulty":"Accessory","notes":"Same as cable rear-delt fly.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX038","name":"Cable triceps pushdown","muscle":"Triceps","pattern":"Elbow extension","equipment":"Cable station","primaryFor":"Triceps","difficulty":"Accessory","notes":"Keep upper arm fixed.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX039","name":"Overhead cable triceps extension","muscle":"Triceps long head","pattern":"Elbow extension","equipment":"Cable station + Rope cable attachment","primaryFor":"Triceps","difficulty":"Accessory","notes":"Use pain-free elbow path.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station","Rope cable attachment"]],"optionalEquipment":[]},{"id":"EX040","name":"Dumbbell skull crusher","muscle":"Triceps","pattern":"Elbow extension","equipment":"Dumbbells","primaryFor":"Triceps","difficulty":"Substitution","notes":"Use light and controlled.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[]},{"id":"EX041","name":"Cable curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Cable station","primaryFor":"Biceps","difficulty":"Accessory","notes":"Constant tension curl.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX042","name":"Incline dumbbell curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Dumbbells + Adjustable bench","primaryFor":"Biceps","difficulty":"Accessory","notes":"Great long-head stretch; do not overextend shoulder.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells","Adjustable bench"]],"optionalEquipment":[]},{"id":"EX043","name":"Dumbbell hammer curl","muscle":"Biceps / Brachialis","pattern":"Elbow flexion","equipment":"Dumbbells","primaryFor":"Biceps","difficulty":"Accessory","notes":"Neutral-grip elbow-friendly curl.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[]},{"id":"EX044","name":"Ring curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Gymnastic rings / suspension trainer","primaryFor":"Biceps","difficulty":"Substitution","notes":"Adjust angle for difficulty.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Gymnastic rings / suspension trainer"]],"optionalEquipment":[]},{"id":"EX045","name":"Cable or ring curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Cable station OR Gymnastic rings / suspension trainer","primaryFor":"Biceps","difficulty":"Optional slot","notes":"Choose cable if elbows feel sensitive.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"],["Gymnastic rings / suspension trainer"]],"optionalEquipment":[]},{"id":"EX046","name":"Dead bug","muscle":"Core","pattern":"Anti-extension","equipment":"Bodyweight / floor space","primaryFor":"Core","difficulty":"Accessory","notes":"Control lower back position.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":[]},{"id":"EX047","name":"Pallof press","muscle":"Core","pattern":"Anti-rotation","equipment":"Cable station OR Resistance bands / tubes","primaryFor":"Core","difficulty":"Accessory","notes":"Pause each rep.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"],["Resistance bands / tubes"]],"optionalEquipment":[]},{"id":"EX048","name":"Ab wheel","muscle":"Core","pattern":"Anti-extension","equipment":"Ab wheel","primaryFor":"Core","difficulty":"Accessory","notes":"Use only if lower back stays neutral.","rflOk":"No if fatigued","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Ab wheel"]],"optionalEquipment":[]},{"id":"EX049","name":"Cable crunch","muscle":"Abs","pattern":"Spinal flexion","equipment":"Cable station","primaryFor":"Core","difficulty":"Substitution","notes":"Controlled range; avoid yanking.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX050","name":"Brisk walking","muscle":"Cardio / Recovery","pattern":"Aerobic","equipment":"Bodyweight / floor space OR Treadmill","primaryFor":"Cardio","difficulty":"Recovery","notes":"Easy pace where you can speak in sentences.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"],["Treadmill"]],"optionalEquipment":["Weighted vest"]},{"id":"EX051","name":"Easy bike","muscle":"Cardio / Recovery","pattern":"Aerobic","equipment":"Exercise bike","primaryFor":"Cardio","difficulty":"Recovery","notes":"Low impact option if available.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Exercise bike"]],"optionalEquipment":[]},{"id":"EX052","name":"Mobility flow","muscle":"Recovery","pattern":"Mobility","equipment":"Bodyweight / floor space","primaryFor":"Recovery","difficulty":"Recovery","notes":"5-10 minutes hips, t-spine, ankles.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":[]},{"id":"EX053","name":"Push-up","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Weighted vest","Resistance bands / tubes"],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"Use handles or dumbbells as grips if wrists prefer neutral.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX054","name":"Feet-elevated push-up","muscle":"Upper chest / Triceps","pattern":"Incline press","equipment":"Bodyweight / floor space + Bench or box","equipmentOptions":[["Bodyweight / floor space","Bench or box"]],"optionalEquipment":["Weighted vest"],"primaryFor":"Incline press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX055","name":"Pike push-up","muscle":"Delts / Triceps","pattern":"Vertical press","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Bench or box"],"primaryFor":"Vertical press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX056","name":"Parallel-bar dip","muscle":"Chest / Triceps","pattern":"Vertical dip","equipment":"Dip station / parallel bars","equipmentOptions":[["Dip station / parallel bars"]],"optionalEquipment":["Dip belt / loading belt","Resistance bands / tubes"],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX057","name":"Band-assisted dip","muscle":"Chest / Triceps","pattern":"Vertical dip","equipment":"Dip station / parallel bars + Resistance bands / tubes","equipmentOptions":[["Dip station / parallel bars","Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX058","name":"Low-bar back squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Use only if shoulder position and technique are comfortable.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX059","name":"Safety-bar squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Safety squat bar","equipmentOptions":[["Power rack / squat stands","Safety squat bar"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Often easier on shoulders and upper back.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX060","name":"Smith-machine squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Smith machine","equipmentOptions":[["Smith machine"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Choose a foot position that keeps the movement comfortable.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX061","name":"Landmine squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Barbell + plates + Landmine attachment","equipmentOptions":[["Barbell + plates","Landmine attachment"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Substitution","notes":"Stable front-loaded squat option.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX062","name":"Leg press","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Leg press / hack squat","equipmentOptions":[["Leg press / hack squat"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Use controlled depth and avoid pelvis rolling.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX063","name":"Hack squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Leg press / hack squat","equipmentOptions":[["Leg press / hack squat"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Quad-biased machine squat.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX064","name":"Leg extension","muscle":"Quads","pattern":"Knee extension","equipment":"Leg extension machine","equipmentOptions":[["Leg extension machine"]],"optionalEquipment":[],"primaryFor":"Quads","difficulty":"Isolation","notes":"Control the top and lower without bouncing.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX065","name":"Step-up","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bench or box","equipmentOptions":[["Bench or box"]],"optionalEquipment":["Dumbbells","Kettlebells"],"primaryFor":"Single-leg","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX066","name":"Walking lunge","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Kettlebells","Weighted vest"],"primaryFor":"Single-leg","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX067","name":"Bodyweight split squat","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Weighted vest"],"primaryFor":"Single-leg","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX068","name":"Conventional deadlift","muscle":"Hamstrings / Glutes / Back","pattern":"Hip hinge","equipment":"Barbell + plates","equipmentOptions":[["Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"Use only when technique and recovery support it.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX069","name":"Sumo deadlift","muscle":"Glutes / Hamstrings / Adductors","pattern":"Hip hinge","equipment":"Barbell + plates","equipmentOptions":[["Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"Choose stance based on comfort and proportions.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX070","name":"Trap-bar deadlift","muscle":"Quads / Glutes / Hamstrings","pattern":"Hip hinge","equipment":"Trap / hex bar + Barbell plates","equipmentOptions":[["Trap / hex bar","Barbell plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"Often easier to keep the load close to the body.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX071","name":"Rack pull","muscle":"Glutes / Back","pattern":"Hip hinge","equipment":"Power rack / squat stands + Barbell + plates","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"Use sparingly; high loading can be fatiguing.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX072","name":"Good morning","muscle":"Hamstrings / Glutes","pattern":"Hip hinge","equipment":"Power rack / squat stands + Barbell + plates","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Substitution","notes":"Light, controlled hinge; not a max-load movement.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX073","name":"Kettlebell Romanian deadlift","muscle":"Hamstrings / Glutes","pattern":"Hip hinge","equipment":"Kettlebells","equipmentOptions":[["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX074","name":"Kettlebell swing","muscle":"Glutes / Conditioning","pattern":"Ballistic hinge","equipment":"Kettlebells","equipmentOptions":[["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Conditioning","difficulty":"Conditioning","notes":"Use only with established hinge technique.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX075","name":"Dumbbell hip thrust","muscle":"Glutes / Hamstrings","pattern":"Hip extension","equipment":"Dumbbells + Bench","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[],"primaryFor":"Hip extension","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX076","name":"Glute bridge","muscle":"Glutes / Hamstrings","pattern":"Hip extension","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Barbell + plates","Resistance bands / tubes"],"primaryFor":"Hip extension","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX077","name":"Seated leg curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Leg curl machine","equipmentOptions":[["Leg curl machine"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX078","name":"Lying leg curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Leg curl machine","equipmentOptions":[["Leg curl machine"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX079","name":"Banded leg curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Resistance bands / tubes + Secure band anchor","equipmentOptions":[["Resistance bands / tubes","Secure band anchor"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX080","name":"Stability-ball leg curl","muscle":"Hamstrings / Glutes","pattern":"Knee flexion","equipment":"Stability ball","equipmentOptions":[["Stability ball"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX081","name":"Nordic hamstring curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Glute-ham developer / Nordic bench","equipmentOptions":[["Glute-ham developer / Nordic bench"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Advanced","notes":"Use assistance and a controlled eccentric.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX082","name":"Glute-ham raise","muscle":"Hamstrings / Glutes","pattern":"Knee flexion","equipment":"Glute-ham developer / Nordic bench","equipmentOptions":[["Glute-ham developer / Nordic bench"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Advanced","notes":"Scale range of motion as needed.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX083","name":"Seated calf raise","muscle":"Soleus / Calves","pattern":"Calf raise","equipment":"Calf raise platform / machine OR Bench + Dumbbells","equipmentOptions":[["Calf raise platform / machine"],["Bench","Dumbbells"]],"optionalEquipment":[],"primaryFor":"Calf raise","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX084","name":"Single-leg calf raise","muscle":"Calves","pattern":"Calf raise","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Calf raise platform / machine"],"primaryFor":"Calf raise","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX085","name":"Smith-machine bench press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Smith machine + Bench","equipmentOptions":[["Smith machine","Bench"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX086","name":"Chest press machine","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Chest press / pec deck machine","equipmentOptions":[["Chest press / pec deck machine"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX087","name":"Dumbbell fly","muscle":"Chest","pattern":"Chest isolation","equipment":"Dumbbells + Bench","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[],"primaryFor":"Chest","difficulty":"Isolation</x:v>
+      </x:c>
+      <x:c r="C2" s="134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="157" t="n">
+        <x:v>46222.875</x:v>
+      </x:c>
+      <x:c r="E2" s="134" t="str">
         <x:v>template</x:v>
       </x:c>
-      <x:c r="F2" s="65" t="str">
-        <x:v>v2.2 template</x:v>
-      </x:c>
-      <x:c r="G2" s="66" t="str"/>
+      <x:c r="F2" s="134" t="str">
+        <x:v>v2.3 template</x:v>
+      </x:c>
+      <x:c r="G2" s="135"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="71" t="n">
+      <x:c r="A3" s="136" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="72" t="str">
-        <x:v>0Z","equipmentOptions":[["Cable station"],["Resistance bands / tubes"]],"optionalEquipment":[]},{"id":"EX048","name":"Ab wheel","muscle":"Core","pattern":"Anti-extension","equipment":"Ab wheel","primaryFor":"Core","difficulty":"Accessory","notes":"Use only if lower back stays neutral.","rflOk":"No if fatigued","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Ab wheel"]],"optionalEquipment":[]},{"id":"EX049","name":"Cable crunch","muscle":"Abs","pattern":"Spinal flexion","equipment":"Cable station","primaryFor":"Core","difficulty":"Substitution","notes":"Controlled range; avoid yanking.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Cable station"]],"optionalEquipment":[]},{"id":"EX050","name":"Brisk walking","muscle":"Cardio / Recovery","pattern":"Aerobic","equipment":"Bodyweight / floor space OR Treadmill","primaryFor":"Cardio","difficulty":"Recovery","notes":"Easy pace where you can speak in sentences.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"],["Treadmill"]],"optionalEquipment":["Weighted vest"]},{"id":"EX051","name":"Easy bike","muscle":"Cardio / Recovery","pattern":"Aerobic","equipment":"Exercise bike","primaryFor":"Cardio","difficulty":"Recovery","notes":"Low impact option if available.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Exercise bike"]],"optionalEquipment":[]},{"id":"EX052","name":"Mobility flow","muscle":"Recovery","pattern":"Mobility","equipment":"Bodyweight / floor space","primaryFor":"Recovery","difficulty":"Recovery","notes":"5-10 minutes hips, t-spine, ankles.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T10:00:00.000Z","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":[]},{"id":"EX053","name":"Push-up","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Weighted vest","Resistance bands / tubes"],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"Use handles or dumbbells as grips if wrists prefer neutral.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX054","name":"Feet-elevated push-up","muscle":"Upper chest / Triceps","pattern":"Incline press","equipment":"Bodyweight / floor space + Bench or box","equipmentOptions":[["Bodyweight / floor space","Bench or box"]],"optionalEquipment":["Weighted vest"],"primaryFor":"Incline press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX055","name":"Pike push-up","muscle":"Delts / Triceps","pattern":"Vertical press","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Bench or box"],"primaryFor":"Vertical press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX056","name":"Parallel-bar dip","muscle":"Chest / Triceps","pattern":"Vertical dip","equipment":"Dip station / parallel bars","equipmentOptions":[["Dip station / parallel bars"]],"optionalEquipment":["Dip belt / loading belt","Resistance bands / tubes"],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX057","name":"Band-assisted dip","muscle":"Chest / Triceps","pattern":"Vertical dip","equipment":"Dip station / parallel bars + Resistance bands / tubes","equipmentOptions":[["Dip station / parallel bars","Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX058","name":"Low-bar back squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Use only if shoulder position and technique are comfortable.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX059","name":"Safety-bar squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Safety squat bar","equipmentOptions":[["Power rack / squat stands","Safety squat bar"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Often easier on shoulders and upper back.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX060","name":"Smith-machine squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Smith machine","equipmentOptions":[["Smith machine"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Choose a foot position that keeps the movement comfortable.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX061","name":"Landmine squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Barbell + plates + Landmine attachment","equipmentOptions":[["Barbell + plates","Landmine attachment"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Substitution","notes":"Stable front-loaded squat option.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX062","name":"Leg press","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Leg press / hack squat","equipmentOptions":[["Leg press / hack squat"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Use controlled depth and avoid pelvis rolling.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX063","name":"Hack squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Leg press / hack squat","equipmentOptions":[["Leg press / hack squat"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Main lift","notes":"Quad-biased machine squat.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX064","name":"Leg extension","muscle":"Quads","pattern":"Knee extension","equipment":"Leg extension machine","equipmentOptions":[["Leg extension machine"]],"optionalEquipment":[],"primaryFor":"Quads","difficulty":"Isolation","notes":"Control the top and lower without bouncing.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX065","name":"Step-up","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bench or box","equipmentOptions":[["Bench or box"]],"optionalEquipment":["Dumbbells","Kettlebells"],"primaryFor":"Single-leg","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX066","name":"Walking lunge","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Kettlebells","Weighted vest"],"primaryFor":"Single-leg","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX067","name":"Bodyweight split squat","muscle":"Quads / Glutes","pattern":"Single-leg","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Weighted vest"],"primaryFor":"Single-leg","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX068","name":"Conventional deadlift","muscle":"Hamstrings / Glutes / Back","pattern":"Hip hinge","equipment":"Barbell + plates","equipmentOptions":[["Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"Use only when technique and recovery support it.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX069","name":"Sumo deadlift","muscle":"Glutes / Hamstrings / Adductors","pattern":"Hip hinge","equipment":"Barbell + plates","equipmentOptions":[["Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"Choose stance based on comfort and proportions.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX070","name":"Trap-bar deadlift","muscle":"Quads / Glutes / Hamstrings","pattern":"Hip hinge","equipment":"Trap / hex bar + Barbell plates","equipmentOptions":[["Trap / hex bar","Barbell plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"Often easier to keep the load close to the body.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX071","name":"Rack pull","muscle":"Glutes / Back","pattern":"Hip hinge","equipment":"Power rack / squat stands + Barbell + plates","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"Use sparingly; high loading can be fatiguing.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX072","name":"Good morning","muscle":"Hamstrings / Glutes","pattern":"Hip hinge","equipment":"Power rack / squat stands + Barbell + plates","equipmentOptions":[["Power rack / squat stands","Barbell + plates"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Substitution","notes":"Light, controlled hinge; not a max-load movement.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX073","name":"Kettlebell Romanian deadlift","muscle":"Hamstrings / Glutes","pattern":"Hip hinge","equipment":"Kettlebells","equipmentOptions":[["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX074","name":"Kettlebell swing","muscle":"Glutes / Conditioning","pattern":"Ballistic hinge","equipment":"Kettlebells","equipmentOptions":[["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Conditioning","difficulty":"Conditioning","notes":"Use only with established hinge technique.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX075","name":"Dumbbell hip thrust","muscle":"Glutes / Hamstrings","pattern":"Hip extension","equipment":"Dumbbells + Bench","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[],"primaryFor":"Hip extension","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX076","name":"Glute bridge","muscle":"Glutes / Hamstrings","pattern":"Hip extension","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Barbell + plates","Resistance bands / tubes"],"primaryFor":"Hip extension","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX077","name":"Seated leg curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Leg curl machine","equipmentOptions":[["Leg curl machine"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX078","name":"Lying leg curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Leg curl machine","equipmentOptions":[["Leg curl machine"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX079","name":"Banded leg curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Resistance bands / tubes + Secure band anchor","equipmentOptions":[["Resistance bands / tubes","Secure band anchor"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX080","name":"Stability-ball leg curl","muscle":"Hamstrings / Glutes","pattern":"Knee flexion","equipment":"Stability ball","equipmentOptions":[["Stability ball"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX081","name":"Nordic hamstring curl","muscle":"Hamstrings","pattern":"Knee flexion","equipment":"Glute-ham developer / Nordic bench","equipmentOptions":[["Glute-ham developer / Nordic bench"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Advanced","notes":"Use assistance and a controlled eccentric.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX082","name":"Glute-ham raise","muscle":"Hamstrings / Glutes","pattern":"Knee flexion","equipment":"Glute-ham developer / Nordic bench","equipmentOptions":[["Glute-ham developer / Nordic bench"]],"optionalEquipment":[],"primaryFor":"Knee flexion","difficulty":"Advanced","notes":"Scale range of motion as needed.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX083","name":"Seated calf raise","muscle":"Soleus / Calves","pattern":"Calf raise","equipment":"Calf raise platform / machine OR Bench + Dumbbells","equipmentOptions":[["Calf raise platform / machine"],["Bench","Dumbbells"]],"optionalEquipment":[],"primaryFor":"Calf raise","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX084","name":"Single-leg calf raise","muscle":"Calves","pattern":"Calf raise","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Dumbbells","Calf raise platform / machine"],"primaryFor":"Calf raise","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX085","name":"Smith-machine bench press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Smith machine + Bench","equipmentOptions":[["Smith machine","Bench"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX086","name":"Chest press machine","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Chest press / pec deck machine","equipmentOptions":[["Chest press / pec deck machine"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX087","name":"Dumbbell fly","muscle":"Chest","pattern":"Chest isolation","equipment":"Dumbbells + Bench","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[],"primaryFor":"Chest","difficulty":"Isolation","notes":"Use a comfortable range; avoid excessive stretch.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX088","name":"Pec deck fly","muscle":"Chest","pattern":"Chest isolation","equipment":"Chest press / pec deck machine","equipmentOptions":[["Chest press / pec deck machine"]],"optionalEquipment":[],"primaryFor":"Chest","difficulty":"Isolation","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX089","name":"Landmine press","muscle":"Delts / Upper chest / Triceps","pattern":"Vertical press","equipment":"Barbell + plates + Landmine attachment","equipmentOptions":[["Barbell + plates","Landmine attachment"]],"optionalEquipment":[],"primaryFor":"Vertical press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX090","name":"Arnold press","muscle":"Delts / Triceps","pattern":"Vertical press","equipment":"Dumbbells + Bench","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[],"primaryFor":"Vertical press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX091","name":"Dumbbell pullover","muscle":"Lats / Chest","pattern":"Pullover","equipment":"Dumbbells + Bench","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[],"primaryFor":"Pullover","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX092","name":"Landmine T-bar row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Barbell + plates + Landmine attachment","equipmentOptions":[["Barbell + plates","Landmine attachment"]],"optionalEquipment":[],"primaryFor":"Horizontal pull","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX093","name":"Band row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Resistance bands / tubes + Secure band anchor","equipmentOptions":[["Resistance bands / tubes","Secure band anchor"]],"optionalEquipment":[],"primaryFor":"Horizontal pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX094","name":"Band lat pulldown","muscle":"Lats","pattern":"Vertical pull","equipment":"Resistance bands / tubes + High band anchor","equipmentOptions":[["Resistance bands / tubes","High band anchor"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX095","name":"Pull-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Pull-up bar","equipmentOptions":[["Pull-up bar"]],"optionalEquipment":["Resistance bands / tubes","Dip belt / loading belt"],"primaryFor":"Vertical pull","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX096","name":"Band-assisted pull-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Pull-up bar + Resistance bands / tubes","equipmentOptions":[["Pull-up bar","Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX097","name":"Dumbbell rear-delt fly","muscle":"Rear delts / Upper back","pattern":"Rear delt","equipment":"Dumbbells","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[],"primaryFor":"Rear delt","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX098","name":"Reverse pec deck","muscle":"Rear delts / Upper back","pattern":"Rear delt","equipment":"Chest press / pec deck machine","equipmentOptions":[["Chest press / pec deck machine"]],"optionalEquipment":[],"primaryFor":"Rear delt","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX099","name":"Band face pull","muscle":"Rear delts / Upper back","pattern":"Rear delt / external rotation","equipment":"Resistance bands / tubes + High band anchor","equipmentOptions":[["Resistance bands / tubes","High band anchor"]],"optionalEquipment":[],"primaryFor":"Rear delt","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX100","name":"Band lateral raise","muscle":"Side delts","pattern":"Lateral raise","equipment":"Resistance bands / tubes","equipmentOptions":[["Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Lateral raise","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX101","name":"EZ-bar curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"EZ curl bar + Barbell plates","equipmentOptions":[["EZ curl bar","Barbell plates"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX102","name":"Preacher curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Preacher curl bench + EZ curl bar + Barbell plates OR Preacher curl bench + Dumbbells","equipmentOptions":[["Preacher curl bench","EZ curl bar","Barbell plates"],["Preacher curl bench","Dumbbells"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX103","name":"Band curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Resistance bands / tubes","equipmentOptions":[["Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX104","name":"EZ-bar skull crusher","muscle":"Triceps","pattern":"Elbow extension","equipment":"EZ curl bar + Barbell plates + Bench","equipmentOptions":[["EZ curl bar","Barbell plates","Bench"]],"optionalEquipment":[],"primaryFor":"Elbow extension","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX105","name":"Band triceps pushdown","muscle":"Triceps","pattern":"Elbow extension","equipment":"Resistance bands / tubes + High band anchor","equipmentOptions":[["Resistance bands / tubes","High band anchor"]],"optionalEquipment":[],"primaryFor":"Elbow extension","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX106","name":"Close-grip push-up","muscle":"Triceps / Chest","pattern":"Horizontal press","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Resistance bands / tubes","Weighted vest"],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX107","name":"Stability-ball crunch","muscle":"Abs","pattern":"Spinal flexion","equipment":"Stability ball","equipmentOptions":[["Stability ball"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX108","name":"Reverse crunch","muscle":"Abs","pattern":"Spinal flexion","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX109","name":"Side plank","muscle":"Obliques / Core","pattern":"Anti-lateral flexion","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX110","name":"Farmer carry","muscle":"Grip / Traps / Core","pattern":"Loaded carry","equipment":"Dumbbells OR Kettlebells","equipmentOptions":[["Dumbbells"],["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Loaded carry","difficulty":"Substitution","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX111","name":"Suitcase carry","muscle":"Core / Grip","pattern":"Loaded carry","equipment":"Dumbbells OR Kettlebells","equipmentOptions":[["Dumbbells"],["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Loaded carry","difficulty":"Substitution","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX112","name":"Trap-bar carry","muscle":"Grip / Traps / Core","pattern":"Loaded carry","equipment":"Trap / hex bar + Barbell plates","equipmentOptions":[["Trap / hex bar","Barbell plates"]],"optionalEquipment":[],"primaryFor":"Loaded carry","difficulty":"Substitution","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX113","name":"Rowing machine","muscle":"Cardio / Recovery","pattern":"Aerobic","equipment":"Rowing machine","equipmentOptions":[["Rowing machine"]],"optionalEquipment":[],"primaryFor":"Cardio","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX114","name":"Elliptical","muscle":"Cardio / Recovery","pattern":"Aerobic","equipment":"Elliptical / cross trainer","equipmentOptions":[["Elliptical / cross trainer"]],"optionalEquipment":[],"primaryFor":"Cardio","difficulty":"Conditioning","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX115","name":"Jump rope","muscle":"Cardio / Calves","pattern":"Conditioning","equipment":"Jump rope","equipmentOptions":[["Jump rope"]],"optionalEquipment":[],"primaryFor":"Conditioning","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX116","name":"Sled push","muscle":"Quads / Conditioning","pattern":"Conditioning","equipment":"Weight sled / prowler","equipmentOptions":[["Weight sled / prowler"]],"optionalEquipment":[],"primaryFor":"Conditioning","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX117","name":"Medicine-ball slam","muscle":"Full body / Conditioning","pattern":"Conditioning","equipment":"Medicine ball","equipmentOptions":[["Medicine ball"]],"optionalEquipment":[],"primaryFor":"Conditioning","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX118","name":"Sandbag carry","muscle":"Full body / Grip","pattern":"Loaded carry","equipment":"Sandbag","equipmentOptions":[["Sandbag"]],"optionalEquipment":[],"primaryFor":"Loaded carry","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX119","name":"Kettlebell goblet squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Kettlebells","equipmentOptions":[["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX120","name":"Slant-board squat","muscle":"Quads","pattern":"Squat","equipment":"Slant board / heel wedge","equipmentOptions":[["Slant board / heel wedge"]],"optionalEquipment":["Dumbbells","Kettlebells","Weighted vest"],"primaryFor":"Squat","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX121","name":"Smith-machine hip thrust","muscle":"Glutes / Hamstrings","pattern":"Hip extension","equipment":"Smith machine + Bench","equipmentOptions":[["Smith machine","Bench"]],"optionalEquipment":[],"primaryFor":"Hip extension","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX122","name":"Swiss-bar bench press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Power rack / squat stands + Swiss / football bar + Barbell plates + Bench","equipmentOptions":[["Power rack / squat stands","Swiss / football bar","Barbell plates","Bench"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Main lift","notes":"Neutral grips may be shoulder friendly.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX123","name":"Band Pallof press","muscle":"Core","pattern":"Anti-rotation","equipment":"Resistance bands / tubes + Secure band anchor","equipmentOptions":[["Resistance bands / tubes","Secure band anchor"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX124","name":"Dead bug or Pallof press","muscle":"Core","pattern":"Anti-extension / anti-rotation","equipment":"Bodyweight / floor space OR Cable station OR Resistance bands / tubes + Secure band anchor","equipmentOptions":[["Bodyweight / floor space"],["Cable station"],["Resistance bands / tubes","Secure band anchor"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX125","name":"Cable lat pulldown or ring chin-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Cable station OR Lat pulldown / low row machine OR Gymnastic rings / suspension trainer","equipmentOptions":[["Cable station"],["Lat pulldown / low row machine"],["Gymnastic rings / suspension trainer"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX126","name":"Incline dumbbell or cable curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Dumbbells + Adjustable bench OR Cable station","equipmentOptions":[["Dumbbells","Adjustable bench"],["Cable station"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX127","name":"Front squat or heels-elevated squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates OR Dumbbells","equipmentOptions":[["Power rack / squat stands","Barbell + plates"],["Dumbbells"]],"optionalEquipment":["Slant board / heel wedge"],"primaryFor":"Squat","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX128","name":"Ab wheel or cable crunch","muscle":"Abs / Core","pattern":"Core","equipment":"Ab wheel OR Cable station","equipmentOptions":[["Ab wheel"],["Cable station"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX129","name":"Weighted chin-up or heavy pulldown","muscle":"Lats / Biceps","pattern":"Vertical pull",</x:v>
-      </x:c>
-      <x:c r="C3" s="72" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D3" s="102" t="n">
-        <x:v>46222.65625</x:v>
-      </x:c>
-      <x:c r="E3" s="72" t="str">
+      <x:c r="B3" s="137" t="str">
+        <x:v>","notes":"Use a comfortable range; avoid excessive stretch.","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX088","name":"Pec deck fly","muscle":"Chest","pattern":"Chest isolation","equipment":"Chest press / pec deck machine","equipmentOptions":[["Chest press / pec deck machine"]],"optionalEquipment":[],"primaryFor":"Chest","difficulty":"Isolation","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX089","name":"Landmine press","muscle":"Delts / Upper chest / Triceps","pattern":"Vertical press","equipment":"Barbell + plates + Landmine attachment","equipmentOptions":[["Barbell + plates","Landmine attachment"]],"optionalEquipment":[],"primaryFor":"Vertical press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX090","name":"Arnold press","muscle":"Delts / Triceps","pattern":"Vertical press","equipment":"Dumbbells + Bench","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[],"primaryFor":"Vertical press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX091","name":"Dumbbell pullover","muscle":"Lats / Chest","pattern":"Pullover","equipment":"Dumbbells + Bench","equipmentOptions":[["Dumbbells","Bench"]],"optionalEquipment":[],"primaryFor":"Pullover","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX092","name":"Landmine T-bar row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Barbell + plates + Landmine attachment","equipmentOptions":[["Barbell + plates","Landmine attachment"]],"optionalEquipment":[],"primaryFor":"Horizontal pull","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX093","name":"Band row","muscle":"Upper back / Lats","pattern":"Horizontal pull","equipment":"Resistance bands / tubes + Secure band anchor","equipmentOptions":[["Resistance bands / tubes","Secure band anchor"]],"optionalEquipment":[],"primaryFor":"Horizontal pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX094","name":"Band lat pulldown","muscle":"Lats","pattern":"Vertical pull","equipment":"Resistance bands / tubes + High band anchor","equipmentOptions":[["Resistance bands / tubes","High band anchor"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX095","name":"Pull-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Pull-up bar","equipmentOptions":[["Pull-up bar"]],"optionalEquipment":["Resistance bands / tubes","Dip belt / loading belt"],"primaryFor":"Vertical pull","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX096","name":"Band-assisted pull-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Pull-up bar + Resistance bands / tubes","equipmentOptions":[["Pull-up bar","Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX097","name":"Dumbbell rear-delt fly","muscle":"Rear delts / Upper back","pattern":"Rear delt","equipment":"Dumbbells","equipmentOptions":[["Dumbbells"]],"optionalEquipment":[],"primaryFor":"Rear delt","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX098","name":"Reverse pec deck","muscle":"Rear delts / Upper back","pattern":"Rear delt","equipment":"Chest press / pec deck machine","equipmentOptions":[["Chest press / pec deck machine"]],"optionalEquipment":[],"primaryFor":"Rear delt","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX099","name":"Band face pull","muscle":"Rear delts / Upper back","pattern":"Rear delt / external rotation","equipment":"Resistance bands / tubes + High band anchor","equipmentOptions":[["Resistance bands / tubes","High band anchor"]],"optionalEquipment":[],"primaryFor":"Rear delt","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX100","name":"Band lateral raise","muscle":"Side delts","pattern":"Lateral raise","equipment":"Resistance bands / tubes","equipmentOptions":[["Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Lateral raise","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX101","name":"EZ-bar curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"EZ curl bar + Barbell plates","equipmentOptions":[["EZ curl bar","Barbell plates"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX102","name":"Preacher curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Preacher curl bench + EZ curl bar + Barbell plates OR Preacher curl bench + Dumbbells","equipmentOptions":[["Preacher curl bench","EZ curl bar","Barbell plates"],["Preacher curl bench","Dumbbells"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX103","name":"Band curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Resistance bands / tubes","equipmentOptions":[["Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX104","name":"EZ-bar skull crusher","muscle":"Triceps","pattern":"Elbow extension","equipment":"EZ curl bar + Barbell plates + Bench","equipmentOptions":[["EZ curl bar","Barbell plates","Bench"]],"optionalEquipment":[],"primaryFor":"Elbow extension","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX105","name":"Band triceps pushdown","muscle":"Triceps","pattern":"Elbow extension","equipment":"Resistance bands / tubes + High band anchor","equipmentOptions":[["Resistance bands / tubes","High band anchor"]],"optionalEquipment":[],"primaryFor":"Elbow extension","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX106","name":"Close-grip push-up","muscle":"Triceps / Chest","pattern":"Horizontal press","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":["Resistance bands / tubes","Weighted vest"],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX107","name":"Stability-ball crunch","muscle":"Abs","pattern":"Spinal flexion","equipment":"Stability ball","equipmentOptions":[["Stability ball"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX108","name":"Reverse crunch","muscle":"Abs","pattern":"Spinal flexion","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX109","name":"Side plank","muscle":"Obliques / Core","pattern":"Anti-lateral flexion","equipment":"Bodyweight / floor space","equipmentOptions":[["Bodyweight / floor space"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX110","name":"Farmer carry","muscle":"Grip / Traps / Core","pattern":"Loaded carry","equipment":"Dumbbells OR Kettlebells","equipmentOptions":[["Dumbbells"],["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Loaded carry","difficulty":"Substitution","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX111","name":"Suitcase carry","muscle":"Core / Grip","pattern":"Loaded carry","equipment":"Dumbbells OR Kettlebells","equipmentOptions":[["Dumbbells"],["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Loaded carry","difficulty":"Substitution","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX112","name":"Trap-bar carry","muscle":"Grip / Traps / Core","pattern":"Loaded carry","equipment":"Trap / hex bar + Barbell plates","equipmentOptions":[["Trap / hex bar","Barbell plates"]],"optionalEquipment":[],"primaryFor":"Loaded carry","difficulty":"Substitution","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX113","name":"Rowing machine","muscle":"Cardio / Recovery","pattern":"Aerobic","equipment":"Rowing machine","equipmentOptions":[["Rowing machine"]],"optionalEquipment":[],"primaryFor":"Cardio","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX114","name":"Elliptical","muscle":"Cardio / Recovery","pattern":"Aerobic","equipment":"Elliptical / cross trainer","equipmentOptions":[["Elliptical / cross trainer"]],"optionalEquipment":[],"primaryFor":"Cardio","difficulty":"Conditioning","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX115","name":"Jump rope","muscle":"Cardio / Calves","pattern":"Conditioning","equipment":"Jump rope","equipmentOptions":[["Jump rope"]],"optionalEquipment":[],"primaryFor":"Conditioning","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX116","name":"Sled push","muscle":"Quads / Conditioning","pattern":"Conditioning","equipment":"Weight sled / prowler","equipmentOptions":[["Weight sled / prowler"]],"optionalEquipment":[],"primaryFor":"Conditioning","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX117","name":"Medicine-ball slam","muscle":"Full body / Conditioning","pattern":"Conditioning","equipment":"Medicine ball","equipmentOptions":[["Medicine ball"]],"optionalEquipment":[],"primaryFor":"Conditioning","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX118","name":"Sandbag carry","muscle":"Full body / Grip","pattern":"Loaded carry","equipment":"Sandbag","equipmentOptions":[["Sandbag"]],"optionalEquipment":[],"primaryFor":"Loaded carry","difficulty":"Conditioning","notes":"","rflOk":"Maybe","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX119","name":"Kettlebell goblet squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Kettlebells","equipmentOptions":[["Kettlebells"]],"optionalEquipment":[],"primaryFor":"Squat","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX120","name":"Slant-board squat","muscle":"Quads","pattern":"Squat","equipment":"Slant board / heel wedge","equipmentOptions":[["Slant board / heel wedge"]],"optionalEquipment":["Dumbbells","Kettlebells","Weighted vest"],"primaryFor":"Squat","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX121","name":"Smith-machine hip thrust","muscle":"Glutes / Hamstrings","pattern":"Hip extension","equipment":"Smith machine + Bench","equipmentOptions":[["Smith machine","Bench"]],"optionalEquipment":[],"primaryFor":"Hip extension","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX122","name":"Swiss-bar bench press","muscle":"Chest / Triceps","pattern":"Horizontal press","equipment":"Power rack / squat stands + Swiss / football bar + Barbell plates + Bench","equipmentOptions":[["Power rack / squat stands","Swiss / football bar","Barbell plates","Bench"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Main lift","notes":"Neutral grips may be shoulder friendly.","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX123","name":"Band Pallof press","muscle":"Core","pattern":"Anti-rotation","equipment":"Resistance bands / tubes + Secure band anchor","equipmentOptions":[["Resistance bands / tubes","Secure band anchor"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX124","name":"Dead bug or Pallof press","muscle":"Core","pattern":"Anti-extension / anti-rotation","equipment":"Bodyweight / floor space OR Cable station OR Resistance bands / tubes + Secure band anchor","equipmentOptions":[["Bodyweight / floor space"],["Cable station"],["Resistance bands / tubes","Secure band anchor"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX125","name":"Cable lat pulldown or ring chin-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Cable station OR Lat pulldown / low row machine OR Gymnastic rings / suspension trainer","equipmentOptions":[["Cable station"],["Lat pulldown / low row machine"],["Gymnastic rings / suspension trainer"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX126","name":"Incline dumbbell or cable curl","muscle":"Biceps","pattern":"Elbow flexion","equipment":"Dumbbells + Adjustable bench OR Cable station","equipmentOptions":[["Dumbbells","Adjustable bench"],["Cable station"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX127","name":"Front squat or heels-elevated squat","muscle":"Quads / Glutes","pattern":"Squat","equipment":"Power rack / squat stands + Barbell + plates OR Dumbbells","equipmentOptions":[["Power rack / squat stands","Barbell + plates"],["Dumbbells"]],"optionalEquipment":["Slant board / heel wedge"],"primaryFor":"Squat","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX128","name":"Ab wheel or cable crunch","muscle":"Abs / Core","pattern":"Core","equipment":"Ab wheel OR Cable station","equipmentOptions":[["Ab wheel"],["Cable station"]],"optionalEquipment":[],"primaryFor":"Core","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX129","name":"Weighted chin-up or heavy pulldown","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Pull-up bar + Dip belt / loading belt OR Cable station OR Lat pulldown / low row machine","equipmentOptions":[["Pull-up bar","Dip belt / loading belt"],["Cable station"],["Lat pulldown / low row machine"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX130","name":"Close-grip bench press or weighted ring push-up","muscle":"Triceps / Chest","pattern":"Horizontal press","equipment":"Power rack / squat stands + Barbell + plates + Bench OR Gymnastic rings / suspension trainer","equipmentOptions":[["Power rack / squat stands","Barbell + plates","Bench"],["Gymnastic rings / suspension trainer"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX131","name":"Cable rear-delt fly or face pull","muscle":"Rear delts / Upper back","pattern":"Rear delt","equipment":"Cable station OR Cable station + Rope cable attachment","equipmentOptions":[["Cable station"],["Cable station","Rope cable attachment"]],"optionalEquipment":[],"primaryFor":"Rear delt","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX132","name":"Romanian deadlift or hip thrust","muscle":"Hamstrings / Glutes","pattern":"Hip hinge / extension","equipment":"Barbell + plates OR Dumbbells OR Kettlebells OR Barbell + plates + Bench OR Smith machine + Bench","equipmentOptions":[["Barbell + plates"],["Dumbbells"],["Kettlebells"],["Barbell + plates","Bench"],["Smith machine","Bench"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX133","name":"Front squat or Bulgarian split squat","muscle":"Quads / Glutes","pattern":"Squat / single-leg","equipment":"Power rack / squat stands + Barbell + plates OR Bench or box","equipmentOptions":[["Power rack / squat stands","Barbell + plates"],["Bench or box"]],"optionalEquipment":["Dumbbells"],"primaryFor":"Squat","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX134","name":"Pulldown or chin-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Cable station OR Lat pulldown / low row machine OR Pull-up bar OR Gymnastic rings / suspension trainer","equipmentOptions":[["Cable station"],["Lat pulldown / low row machine"],["Pull-up bar"],["Gymnastic rings / suspension trainer"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX135","name":"Hip thrust or cable leg curl","muscle":"Glutes / Hamstrings","pattern":"Hip extension / knee flexion","equipment":"Barbell + plates + Bench OR Smith machine + Bench OR Cable station + Ankle strap OR Leg curl machine","equipmentOptions":[["Barbell + plates","Bench"],["Smith machine","Bench"],["Cable station","Ankle strap"],["Leg curl machine"]],"optionalEquipment":[],"primaryFor":"Hip extension","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX136","name":"Hammer curl","muscle":"Biceps / Brachialis","pattern":"Elbow flexion","equipment":"Dumbbells OR Cable station OR Resistance bands / tubes","equipmentOptions":[["Dumbbells"],["Cable station"],["Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX137","name":"Overhead triceps extension","muscle":"Triceps long head","pattern":"Elbow extension","equipment":"Cable station + Rope cable attachment OR Dumbbells OR EZ curl bar + Barbell plates + Bench OR Resistance bands / tubes + High band anchor","equipmentOptions":[["Cable station","Rope cable attachment"],["Dumbbells"],["EZ curl bar","Barbell plates","Bench"],["Resistance bands / tubes","High band anchor"]],"optionalEquipment":[],"primaryFor":"Elbow extension","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"}],"alternatives":[{"defaultExercise":"High-bar back squat","alternative":"Front squat","reason":"Back feels taxed","notes":"More upright torso.","id":"ALT001","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"High-bar back squat","alternative":"Heels-elevated squat","reason":"Need more quad bias","notes":"Can use dumbbells or barbell.","id":"ALT002","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"High-bar back squat","alternative":"Box squat","reason":"Need controlled depth","notes":"Use safety pins and a stable box.","id":"ALT003","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"High-bar back squat","alternative":"Goblet squat","reason":"Deload or warm-up","notes":"Lower loading.","id":"ALT004","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Front squat or heels-elevated squat","alternative":"High-bar back squat","reason":"Front rack uncomfortable","notes":"Return to standard squat if back tolerates it.","id":"ALT005","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Front squat or heels-elevated squat","alternative":"Bulgarian split squat","reason":"Back-sensitive day","notes":"Hard leg stimulus with less spinal loading.","id":"ALT006","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift","alternative":"Barbell hip thrust","reason":"Lower back discomfort","notes":"Default replacement.","id":"ALT007","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift","alternative":"Cable pull-through","reason":"Lower back discomfort","notes":"Cable hinge pattern.","id":"ALT008","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift","alternative":"Dumbbell Romanian deadlift","reason":"Technique practice","notes":"Smaller load increments.","id":"ALT009","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift or hip thrust","alternative":"Barbell hip thrust","reason":"RFL fatigue","notes":"Back-friendly option.","id":"ALT010","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift or hip thrust","alternative":"Cable pull-through","reason":"Back-sensitive day","notes":"Keep RIR 2-3.","id":"ALT011","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Barbell hip thrust","alternative":"Cable pull-through","reason":"Bench setup unavailable","notes":"Good cable substitute.","id":"ALT012","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Barbell bench press","alternative":"Dumbbell bench press","reason":"Shoulder comfort","notes":"Greater freedom of movement.","id":"ALT013","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Barbell bench press","alternative":"Floor press","reason":"Shoulder range limitation","notes":"Reduced bottom range.","id":"ALT014","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Barbell bench press","alternative":"Weighted ring push-up","reason":"Want shoulder-friendly press","notes":"Progress with load/body angle.","id":"ALT015","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell press","alternative":"Dumbbell bench press","reason":"Incline setup unavailable","notes":"Flat press substitute.","id":"ALT016","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell or seated dumbbell press","alternative":"Seated dumbbell overhead press","reason":"Prefer vertical press","notes":"RFL press slot.","id":"ALT017","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell or seated dumbbell press","alternative":"Incline dumbbell press","reason":"Prefer chest emphasis","notes":"RFL press slot.","id":"ALT018","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Chest-supported dumbbell row","alternative":"Seated cable row","reason":"Bench unavailable","notes":"Stable cable row.","id":"ALT019","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Chest-supported dumbbell row","alternative":"One-arm cable row","reason":"Need unilateral work","notes":"Control torso.","id":"ALT020","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Chest-supported dumbbell row","alternative":"Inverted row","reason":"No dumbbell setup","notes":"Bodyweight row.","id":"ALT021","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"One-arm cable row","alternative":"Seated cable row","reason":"Want bilateral row","notes":"Use cable station.","id":"ALT022","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Cable lat pulldown","reason":"Chin-ups not ready","notes":"Progress load on cable.","id":"ALT023","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Weighted chin-up","reason":"Strong chin-ups","notes":"Use clean reps only.","id":"ALT024","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Cable lat pulldown","reason":"Need stable load","notes":"Good progression.","id":"ALT025","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Ring chin-up","reason":"Want bodyweight progression","notes":"Use assistance as required.","id":"ALT026","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Pulldown or chin-up","alternative":"Cable lat pulldown","reason":"RFL fatigue","notes":"Easy load control.","id":"ALT027","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Pulldown or chin-up","alternative":"Ring chin-up","reason":"Bodyweight option","notes":"Keep 2-3 RIR in RFL.","id":"ALT028","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Seated dumbbell overhead press","alternative":"Incline dumbbell press","reason":"Shoulder irritation","notes":"Use pain-free angle.","id":"ALT029","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Seated dumbbell overhead press","alternative":"Standing overhead press","reason":"Want barbell progression","notes":"Only if lower back feels stable.","id":"ALT030","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable lateral raise","alternative":"Dumbbell lateral raise","reason":"Cable unavailable","notes":"Keep strict and controlled.","id":"ALT031","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable lateral raise","alternative":"Lean-away cable lateral raise","reason":"Need different line of pull","notes":"Stay light.","id":"ALT032","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable rear-delt fly or face pull","alternative":"Cable rear-delt fly","reason":"Rear delt emphasis","notes":"Strict reps.","id":"ALT033","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable rear-delt fly or face pull","alternative":"Face pull","reason":"Shoulder-health emphasis","notes":"Use rope attachment.","id":"ALT034","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Rear-delt cable fly","alternative":"Face pull","reason":"Shoulder-friendly substitute","notes":"Keep elbows high.","id":"ALT035","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable triceps pushdown","alternative":"Overhead cable triceps extension","reason":"Need long-head work","notes":"Use pain-free elbow path.","id":"ALT036","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Overhead cable triceps extension","alternative":"Cable triceps pushdown","reason":"Elbow discomfort","notes":"Often more comfortable.","id":"ALT037","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell or cable curl","alternative":"Cable curl","reason":"Elbow-friendly tension","notes":"Good default.","id":"ALT038","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell or cable curl","alternative":"Incline dumbbell curl","reason":"Stretch emphasis","notes":"Use controlled range.","id":"ALT039","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Dumbbell hammer curl","alternative":"Cable curl","reason":"Elbow discomfort","notes":"Cable may feel smoother.","id":"ALT040","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Dead bug or Pallof press","alternative":"Dead bug","reason":"No cable needed","notes":"Low fatigue core.","id":"ALT041","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Dead bug or Pallof press","alternative":"Pallof press","reason":"Anti-rotation focus","notes":"Cable setup.","id":"ALT042","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Ab wheel or cable crunch","alternative":"Cable crunch","reason":"Lower back sensitivity","notes":"Easier to control.","id":"ALT043","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Ab wheel or cable crunch","alternative":"Dead bug","reason":"Fatigued RFL day","notes":"Lowest-risk option.","id":"ALT044","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ALT045","defaultExercise":"High-bar back squat","alternative":"Safety-bar squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT046","defaultExercise":"High-bar back squat","alternative":"Smith-machine squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT047","defaultExercise":"High-bar back squat","alternative":"Landmine squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT048","defaultExercise":"High-bar back squat","alternative":"Leg press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT049","defaultExercise":"High-bar back squat","alternative":"Hack squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT050","defaultExercise":"High-bar back squat","alternative":"Kettlebell goblet squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT051","defaultExercise":"High-bar back squat","alternative":"Bodyweight split squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT052","defaultExercise":"Front squat or heels-elevated squat","alternative":"Front squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT053","defaultExercise":"Front squat or heels-elevated squat","alternative":"Goblet squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT054","defaultExercise":"Front squat or heels-elevated squat","alternative":"Landmine squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT055","defaultExercise":"Front squat or heels-elevated squat","alternative":"Leg press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT056","defaultExercise":"Front squat or heels-elevated squat","alternative":"Hack squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT057","defaultExercise":"Front squat or heels-elevated squat","alternative":"Smith-machine squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT058","defaultExercise":"Front squat or heels-elevated squat","alternative":"Slant-board squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT059","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Front squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT060","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Bulgarian split squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT061","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Goblet squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT062","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Leg press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT063","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Hack squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT064","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Bodyweight split squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT065","defaultExercise":"Romanian deadlift","alternative":"Kettlebell Romanian deadlift","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT066","defaultExercise":"Romanian deadlift","alternative":"Trap-bar deadlift","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT067","defaultExercise":"Romanian deadlift","alternative":"Stability-ball leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT068","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Romanian deadlift","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT069","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Dumbbell Romanian deadlift","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT070","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Dumbbell hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT071","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Smith-machine hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT072","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Glute bridge","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT073","defaultExercise":"Barbell hip thrust","alternative":"Dumbbell hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT074","defaultExercise":"Barbell hip thrust","alternative":"Smith-machine hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT075","defaultExercise":"Barbell hip thrust","alternative":"Glute bridge","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT076","defaultExercise":"Hip thrust or cable leg curl","alternative":"Barbell hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT077","defaultExercise":"Hip thrust or cable leg curl","alternative":"Dumbbell hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT078","defaultExercise":"Hip thrust or cable leg curl","alternative":"Smith-machine hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT079","defaultExercise":"Hip thrust or cable leg curl","alternative":"Cable leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT080","defaultExercise":"Hip thrust or cable leg curl","alternative":"Seated leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT081","defaultExercise":"Hip thrust or cable leg curl","alternative":"Lying leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT082","defaultExercise":"Hip thrust or cable leg curl","alternative":"Banded leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT083","defaultExercise":"Hip thrust or cable leg curl","alternative":"Stability-ball leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT084","defaultExercise":"Bulgarian split squat","alternative":"Reverse lunge","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT085","defaultExercise":"Bulgarian split squat","alternative":"Step-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT086","defaultExercise":"Bulgarian split squat","alternative":"Walking lunge","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT087","defaultExercise":"Bulgarian split squat","alternative":"Bodyweight split squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT088","defaultExercise":"Bulgarian split squat","alternative":"Leg press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT089","defaultExercise":"Cable leg curl","alternative":"Seated leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT090","defaultExercise":"Cable leg curl","alternative":"Lying leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT091","defaultExercise":"Cable leg curl","alternative":"Banded leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT092","defaultExercise":"Cable leg curl","alternative":"Stability-ball leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT093","defaultExercise":"Cable leg curl","alternative":"Nordic hamstring curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT094","defaultExercise":"Standing calf raise","alternative":"Single-leg calf raise","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT095","defaultExercise":"Standing calf raise","alternative":"Seated calf raise","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT096","defaultExercise":"Barbell bench press","alternative":"Push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT097","defaultExercise":"Barbell bench press","alternative":"Smith-machine bench press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT098","defaultExercise":"Barbell bench press","alternative":"Chest press machine","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT099","defaultExercise":"Barbell bench press","alternative":"Swiss-bar bench press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT100","defaultExercise":"Incline dumbbell press","alternative":"Feet-elevated push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT101","defaultExercise":"Incline dumbbell press","alternative":"Landmine press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT102","defaultExercise":"Incline dumbbell press","alternative":"Chest press machine","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT103","defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT104","defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Band-assisted pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT105","defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Band lat pulldown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT106","defaultExercise":"Pulldown or chin-up","alternative":"Pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT107","defaultExercise":"Pulldown or chin-up","alternative":"Band-assisted pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT108","defaultExercise":"Pulldown or chin-up","alternative":"Band lat pulldown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT109","defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT110","defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Ring chin-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT111","defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Band lat pulldown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT112","defaultExercise":"Chest-supported dumbbell row","alternative":"One-arm dumbbell row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT113","defaultExercise":"Chest-supported dumbbell row","alternative":"Band row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT114","defaultExercise":"Chest-supported dumbbell row","alternative":"Landmine T-bar row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT115","defaultExercise":"One-arm cable row","alternative":"One-arm dumbbell row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT116","defaultExercise":"One-arm cable row","alternative":"Band row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT117","defaultExercise":"One-arm cable row","alternative":"Landmine T-bar row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT118","defaultExercise":"Seated dumbbell overhead press","alternative":"Arnold press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT119","defaultExercise":"Seated dumbbell overhead press","alternative":"Landmine press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT120","defaultExercise":"Seated dumbbell overhead press","alternative":"Pike push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT121","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Close-grip bench press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT122","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Weighted ring push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT123","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Parallel-bar dip","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT124","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Close-grip push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT125","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Band-assisted dip","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT126","defaultExercise":"Cable lateral raise","alternative":"Band lateral raise","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT127","defaultExercise":"Cable rear-delt fly or face pull","alternative":"Dumbbell rear-delt fly","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT128","defaultExercise":"Cable</x:v>
+      </x:c>
+      <x:c r="C3" s="137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D3" s="158" t="n">
+        <x:v>46222.875</x:v>
+      </x:c>
+      <x:c r="E3" s="137" t="str">
         <x:v>template</x:v>
       </x:c>
-      <x:c r="F3" s="72" t="str">
-        <x:v>v2.2 template</x:v>
-      </x:c>
-      <x:c r="G3" s="73" t="str"/>
+      <x:c r="F3" s="137" t="str">
+        <x:v>v2.3 template</x:v>
+      </x:c>
+      <x:c r="G3" s="138"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="71" t="n">
+      <x:c r="A4" s="136" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="72" t="str">
-        <x:v>"equipment":"Pull-up bar + Dip belt / loading belt OR Cable station OR Lat pulldown / low row machine","equipmentOptions":[["Pull-up bar","Dip belt / loading belt"],["Cable station"],["Lat pulldown / low row machine"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX130","name":"Close-grip bench press or weighted ring push-up","muscle":"Triceps / Chest","pattern":"Horizontal press","equipment":"Power rack / squat stands + Barbell + plates + Bench OR Gymnastic rings / suspension trainer","equipmentOptions":[["Power rack / squat stands","Barbell + plates","Bench"],["Gymnastic rings / suspension trainer"]],"optionalEquipment":[],"primaryFor":"Horizontal press","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX131","name":"Cable rear-delt fly or face pull","muscle":"Rear delts / Upper back","pattern":"Rear delt","equipment":"Cable station OR Cable station + Rope cable attachment","equipmentOptions":[["Cable station"],["Cable station","Rope cable attachment"]],"optionalEquipment":[],"primaryFor":"Rear delt","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX132","name":"Romanian deadlift or hip thrust","muscle":"Hamstrings / Glutes","pattern":"Hip hinge / extension","equipment":"Barbell + plates OR Dumbbells OR Kettlebells OR Barbell + plates + Bench OR Smith machine + Bench","equipmentOptions":[["Barbell + plates"],["Dumbbells"],["Kettlebells"],["Barbell + plates","Bench"],["Smith machine","Bench"]],"optionalEquipment":[],"primaryFor":"Hip hinge","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX133","name":"Front squat or Bulgarian split squat","muscle":"Quads / Glutes","pattern":"Squat / single-leg","equipment":"Power rack / squat stands + Barbell + plates OR Bench or box","equipmentOptions":[["Power rack / squat stands","Barbell + plates"],["Bench or box"]],"optionalEquipment":["Dumbbells"],"primaryFor":"Squat","difficulty":"Main lift","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX134","name":"Pulldown or chin-up","muscle":"Lats / Biceps","pattern":"Vertical pull","equipment":"Cable station OR Lat pulldown / low row machine OR Pull-up bar OR Gymnastic rings / suspension trainer","equipmentOptions":[["Cable station"],["Lat pulldown / low row machine"],["Pull-up bar"],["Gymnastic rings / suspension trainer"]],"optionalEquipment":[],"primaryFor":"Vertical pull","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX135","name":"Hip thrust or cable leg curl","muscle":"Glutes / Hamstrings","pattern":"Hip extension / knee flexion","equipment":"Barbell + plates + Bench OR Smith machine + Bench OR Cable station + Ankle strap OR Leg curl machine","equipmentOptions":[["Barbell + plates","Bench"],["Smith machine","Bench"],["Cable station","Ankle strap"],["Leg curl machine"]],"optionalEquipment":[],"primaryFor":"Hip extension","difficulty":"Substitution","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX136","name":"Hammer curl","muscle":"Biceps / Brachialis","pattern":"Elbow flexion","equipment":"Dumbbells OR Cable station OR Resistance bands / tubes","equipmentOptions":[["Dumbbells"],["Cable station"],["Resistance bands / tubes"]],"optionalEquipment":[],"primaryFor":"Elbow flexion","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"EX137","name":"Overhead triceps extension","muscle":"Triceps long head","pattern":"Elbow extension","equipment":"Cable station + Rope cable attachment OR Dumbbells OR EZ curl bar + Barbell plates + Bench OR Resistance bands / tubes + High band anchor","equipmentOptions":[["Cable station","Rope cable attachment"],["Dumbbells"],["EZ curl bar","Barbell plates","Bench"],["Resistance bands / tubes","High band anchor"]],"optionalEquipment":[],"primaryFor":"Elbow extension","difficulty":"Isolation","notes":"","rflOk":"Yes","favourite":false,"updatedAt":"2026-07-19T15:45:00.000Z"}],"alternatives":[{"defaultExercise":"High-bar back squat","alternative":"Front squat","reason":"Back feels taxed","notes":"More upright torso.","id":"ALT001","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"High-bar back squat","alternative":"Heels-elevated squat","reason":"Need more quad bias","notes":"Can use dumbbells or barbell.","id":"ALT002","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"High-bar back squat","alternative":"Box squat","reason":"Need controlled depth","notes":"Use safety pins and a stable box.","id":"ALT003","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"High-bar back squat","alternative":"Goblet squat","reason":"Deload or warm-up","notes":"Lower loading.","id":"ALT004","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Front squat or heels-elevated squat","alternative":"High-bar back squat","reason":"Front rack uncomfortable","notes":"Return to standard squat if back tolerates it.","id":"ALT005","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Front squat or heels-elevated squat","alternative":"Bulgarian split squat","reason":"Back-sensitive day","notes":"Hard leg stimulus with less spinal loading.","id":"ALT006","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift","alternative":"Barbell hip thrust","reason":"Lower back discomfort","notes":"Default replacement.","id":"ALT007","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift","alternative":"Cable pull-through","reason":"Lower back discomfort","notes":"Cable hinge pattern.","id":"ALT008","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift","alternative":"Dumbbell Romanian deadlift","reason":"Technique practice","notes":"Smaller load increments.","id":"ALT009","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift or hip thrust","alternative":"Barbell hip thrust","reason":"RFL fatigue","notes":"Back-friendly option.","id":"ALT010","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Romanian deadlift or hip thrust","alternative":"Cable pull-through","reason":"Back-sensitive day","notes":"Keep RIR 2-3.","id":"ALT011","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Barbell hip thrust","alternative":"Cable pull-through","reason":"Bench setup unavailable","notes":"Good cable substitute.","id":"ALT012","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Barbell bench press","alternative":"Dumbbell bench press","reason":"Shoulder comfort","notes":"Greater freedom of movement.","id":"ALT013","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Barbell bench press","alternative":"Floor press","reason":"Shoulder range limitation","notes":"Reduced bottom range.","id":"ALT014","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Barbell bench press","alternative":"Weighted ring push-up","reason":"Want shoulder-friendly press","notes":"Progress with load/body angle.","id":"ALT015","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell press","alternative":"Dumbbell bench press","reason":"Incline setup unavailable","notes":"Flat press substitute.","id":"ALT016","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell or seated dumbbell press","alternative":"Seated dumbbell overhead press","reason":"Prefer vertical press","notes":"RFL press slot.","id":"ALT017","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell or seated dumbbell press","alternative":"Incline dumbbell press","reason":"Prefer chest emphasis","notes":"RFL press slot.","id":"ALT018","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Chest-supported dumbbell row","alternative":"Seated cable row","reason":"Bench unavailable","notes":"Stable cable row.","id":"ALT019","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Chest-supported dumbbell row","alternative":"One-arm cable row","reason":"Need unilateral work","notes":"Control torso.","id":"ALT020","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Chest-supported dumbbell row","alternative":"Inverted row","reason":"No dumbbell setup","notes":"Bodyweight row.","id":"ALT021","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"One-arm cable row","alternative":"Seated cable row","reason":"Want bilateral row","notes":"Use cable station.","id":"ALT022","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Cable lat pulldown","reason":"Chin-ups not ready","notes":"Progress load on cable.","id":"ALT023","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Weighted chin-up","reason":"Strong chin-ups","notes":"Use clean reps only.","id":"ALT024","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Cable lat pulldown","reason":"Need stable load","notes":"Good progression.","id":"ALT025","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Ring chin-up","reason":"Want bodyweight progression","notes":"Use assistance as required.","id":"ALT026","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Pulldown or chin-up","alternative":"Cable lat pulldown","reason":"RFL fatigue","notes":"Easy load control.","id":"ALT027","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Pulldown or chin-up","alternative":"Ring chin-up","reason":"Bodyweight option","notes":"Keep 2-3 RIR in RFL.","id":"ALT028","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Seated dumbbell overhead press","alternative":"Incline dumbbell press","reason":"Shoulder irritation","notes":"Use pain-free angle.","id":"ALT029","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Seated dumbbell overhead press","alternative":"Standing overhead press","reason":"Want barbell progression","notes":"Only if lower back feels stable.","id":"ALT030","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable lateral raise","alternative":"Dumbbell lateral raise","reason":"Cable unavailable","notes":"Keep strict and controlled.","id":"ALT031","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable lateral raise","alternative":"Lean-away cable lateral raise","reason":"Need different line of pull","notes":"Stay light.","id":"ALT032","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable rear-delt fly or face pull","alternative":"Cable rear-delt fly","reason":"Rear delt emphasis","notes":"Strict reps.","id":"ALT033","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable rear-delt fly or face pull","alternative":"Face pull","reason":"Shoulder-health emphasis","notes":"Use rope attachment.","id":"ALT034","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Rear-delt cable fly","alternative":"Face pull","reason":"Shoulder-friendly substitute","notes":"Keep elbows high.","id":"ALT035","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Cable triceps pushdown","alternative":"Overhead cable triceps extension","reason":"Need long-head work","notes":"Use pain-free elbow path.","id":"ALT036","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Overhead cable triceps extension","alternative":"Cable triceps pushdown","reason":"Elbow discomfort","notes":"Often more comfortable.","id":"ALT037","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell or cable curl","alternative":"Cable curl","reason":"Elbow-friendly tension","notes":"Good default.","id":"ALT038","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Incline dumbbell or cable curl","alternative":"Incline dumbbell curl","reason":"Stretch emphasis","notes":"Use controlled range.","id":"ALT039","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Dumbbell hammer curl","alternative":"Cable curl","reason":"Elbow discomfort","notes":"Cable may feel smoother.","id":"ALT040","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Dead bug or Pallof press","alternative":"Dead bug","reason":"No cable needed","notes":"Low fatigue core.","id":"ALT041","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Dead bug or Pallof press","alternative":"Pallof press","reason":"Anti-rotation focus","notes":"Cable setup.","id":"ALT042","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Ab wheel or cable crunch","alternative":"Cable crunch","reason":"Lower back sensitivity","notes":"Easier to control.","id":"ALT043","updatedAt":"2026-07-19T10:00:00.000Z"},{"defaultExercise":"Ab wheel or cable crunch","alternative":"Dead bug","reason":"Fatigued RFL day","notes":"Lowest-risk option.","id":"ALT044","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ALT045","defaultExercise":"High-bar back squat","alternative":"Safety-bar squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT046","defaultExercise":"High-bar back squat","alternative":"Smith-machine squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT047","defaultExercise":"High-bar back squat","alternative":"Landmine squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT048","defaultExercise":"High-bar back squat","alternative":"Leg press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT049","defaultExercise":"High-bar back squat","alternative":"Hack squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT050","defaultExercise":"High-bar back squat","alternative":"Kettlebell goblet squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT051","defaultExercise":"High-bar back squat","alternative":"Bodyweight split squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT052","defaultExercise":"Front squat or heels-elevated squat","alternative":"Front squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT053","defaultExercise":"Front squat or heels-elevated squat","alternative":"Goblet squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT054","defaultExercise":"Front squat or heels-elevated squat","alternative":"Landmine squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT055","defaultExercise":"Front squat or heels-elevated squat","alternative":"Leg press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT056","defaultExercise":"Front squat or heels-elevated squat","alternative":"Hack squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT057","defaultExercise":"Front squat or heels-elevated squat","alternative":"Smith-machine squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT058","defaultExercise":"Front squat or heels-elevated squat","alternative":"Slant-board squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT059","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Front squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT060","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Bulgarian split squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT061","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Goblet squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT062","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Leg press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT063","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Hack squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT064","defaultExercise":"Front squat or Bulgarian split squat","alternative":"Bodyweight split squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT065","defaultExercise":"Romanian deadlift","alternative":"Kettlebell Romanian deadlift","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT066","defaultExercise":"Romanian deadlift","alternative":"Trap-bar deadlift","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT067","defaultExercise":"Romanian deadlift","alternative":"Stability-ball leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT068","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Romanian deadlift","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT069","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Dumbbell Romanian deadlift","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT070","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Dumbbell hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT071","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Smith-machine hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT072","defaultExercise":"Romanian deadlift or hip thrust","alternative":"Glute bridge","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT073","defaultExercise":"Barbell hip thrust","alternative":"Dumbbell hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT074","defaultExercise":"Barbell hip thrust","alternative":"Smith-machine hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT075","defaultExercise":"Barbell hip thrust","alternative":"Glute bridge","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT076","defaultExercise":"Hip thrust or cable leg curl","alternative":"Barbell hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT077","defaultExercise":"Hip thrust or cable leg curl","alternative":"Dumbbell hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT078","defaultExercise":"Hip thrust or cable leg curl","alternative":"Smith-machine hip thrust","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT079","defaultExercise":"Hip thrust or cable leg curl","alternative":"Cable leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT080","defaultExercise":"Hip thrust or cable leg curl","alternative":"Seated leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT081","defaultExercise":"Hip thrust or cable leg curl","alternative":"Lying leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT082","defaultExercise":"Hip thrust or cable leg curl","alternative":"Banded leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT083","defaultExercise":"Hip thrust or cable leg curl","alternative":"Stability-ball leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT084","defaultExercise":"Bulgarian split squat","alternative":"Reverse lunge","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT085","defaultExercise":"Bulgarian split squat","alternative":"Step-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT086","defaultExercise":"Bulgarian split squat","alternative":"Walking lunge","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT087","defaultExercise":"Bulgarian split squat","alternative":"Bodyweight split squat","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT088","defaultExercise":"Bulgarian split squat","alternative":"Leg press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT089","defaultExercise":"Cable leg curl","alternative":"Seated leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT090","defaultExercise":"Cable leg curl","alternative":"Lying leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT091","defaultExercise":"Cable leg curl","alternative":"Banded leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT092","defaultExercise":"Cable leg curl","alternative":"Stability-ball leg curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT093","defaultExercise":"Cable leg curl","alternative":"Nordic hamstring curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT094","defaultExercise":"Standing calf raise","alternative":"Single-leg calf raise","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT095","defaultExercise":"Standing calf raise","alternative":"Seated calf raise","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT096","defaultExercise":"Barbell bench press","alternative":"Push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT097","defaultExercise":"Barbell bench press","alternative":"Smith-machine bench press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT098","defaultExercise":"Barbell bench press","alternative":"Chest press machine","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT099","defaultExercise":"Barbell bench press","alternative":"Swiss-bar bench press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT100","defaultExercise":"Incline dumbbell press","alternative":"Feet-elevated push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT101","defaultExercise":"Incline dumbbell press","alternative":"Landmine press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT102","defaultExercise":"Incline dumbbell press","alternative":"Chest press machine","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT103","defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT104","defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Band-assisted pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT105","defaultExercise":"Cable lat pulldown or ring chin-up","alternative":"Band lat pulldown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT106","defaultExercise":"Pulldown or chin-up","alternative":"Pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT107","defaultExercise":"Pulldown or chin-up","alternative":"Band-assisted pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT108","defaultExercise":"Pulldown or chin-up","alternative":"Band lat pulldown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT109","defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Pull-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT110","defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Ring chin-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT111","defaultExercise":"Weighted chin-up or heavy pulldown","alternative":"Band lat pulldown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT112","defaultExercise":"Chest-supported dumbbell row","alternative":"One-arm dumbbell row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT113","defaultExercise":"Chest-supported dumbbell row","alternative":"Band row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT114","defaultExercise":"Chest-supported dumbbell row","alternative":"Landmine T-bar row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT115","defaultExercise":"One-arm cable row","alternative":"One-arm dumbbell row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT116","defaultExercise":"One-arm cable row","alternative":"Band row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT117","defaultExercise":"One-arm cable row","alternative":"Landmine T-bar row","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT118","defaultExercise":"Seated dumbbell overhead press","alternative":"Arnold press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT119","defaultExercise":"Seated dumbbell overhead press","alternative":"Landmine press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT120","defaultExercise":"Seated dumbbell overhead press","alternative":"Pike push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT121","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Close-grip bench press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT122","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Weighted ring push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT123","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Parallel-bar dip","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT124","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Close-grip push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT125","defaultExercise":"Close-grip bench press or weighted ring push-up","alternative":"Band-assisted dip","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT126","defaultExercise":"Cable lateral raise","alternative":"Band lateral raise","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT127","defaultExercise":"Cable rear-delt fly or face pull","alternative":"Dumbbell rear-delt fly","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT128","defaultExercise":"Cable rear-delt fly or face pull","alternative":"Reverse pec deck","reason":"Equipment match","notes":"Equipment-</x:v>
-      </x:c>
-      <x:c r="C4" s="72" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="102" t="n">
-        <x:v>46222.65625</x:v>
-      </x:c>
-      <x:c r="E4" s="72" t="str">
+      <x:c r="B4" s="137" t="str">
+        <x:v> rear-delt fly or face pull","alternative":"Reverse pec deck","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT129","defaultExercise":"Cable rear-delt fly or face pull","alternative":"Band face pull","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT130","defaultExercise":"Rear-delt cable fly","alternative":"Dumbbell rear-delt fly","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT131","defaultExercise":"Rear-delt cable fly","alternative":"Reverse pec deck","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT132","defaultExercise":"Rear-delt cable fly","alternative":"Band face pull","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT133","defaultExercise":"Cable triceps pushdown","alternative":"Band triceps pushdown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT134","defaultExercise":"Cable triceps pushdown","alternative":"Dumbbell skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT135","defaultExercise":"Cable triceps pushdown","alternative":"EZ-bar skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT136","defaultExercise":"Cable triceps pushdown","alternative":"Close-grip push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT137","defaultExercise":"Overhead cable triceps extension","alternative":"Dumbbell skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT138","defaultExercise":"Overhead cable triceps extension","alternative":"EZ-bar skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT139","defaultExercise":"Overhead cable triceps extension","alternative":"Band triceps pushdown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT140","defaultExercise":"Overhead triceps extension","alternative":"Overhead cable triceps extension","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT141","defaultExercise":"Overhead triceps extension","alternative":"Dumbbell skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT142","defaultExercise":"Overhead triceps extension","alternative":"EZ-bar skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT143","defaultExercise":"Overhead triceps extension","alternative":"Band triceps pushdown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT144","defaultExercise":"Incline dumbbell or cable curl","alternative":"EZ-bar curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT145","defaultExercise":"Incline dumbbell or cable curl","alternative":"Band curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT146","defaultExercise":"Incline dumbbell or cable curl","alternative":"Preacher curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT147","defaultExercise":"Cable curl","alternative":"Incline dumbbell curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT148","defaultExercise":"Cable curl","alternative":"Dumbbell hammer curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT149","defaultExercise":"Cable curl","alternative":"EZ-bar curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT150","defaultExercise":"Cable curl","alternative":"Band curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT151","defaultExercise":"Cable curl","alternative":"Preacher curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT152","defaultExercise":"Dumbbell hammer curl","alternative":"EZ-bar curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT153","defaultExercise":"Dumbbell hammer curl","alternative":"Band curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT154","defaultExercise":"Hammer curl","alternative":"Dumbbell hammer curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT155","defaultExercise":"Hammer curl","alternative":"Cable curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT156","defaultExercise":"Hammer curl","alternative":"Band curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT157","defaultExercise":"Dead bug or Pallof press","alternative":"Band Pallof press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT158","defaultExercise":"Dead bug or Pallof press","alternative":"Side plank","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT159","defaultExercise":"Ab wheel or cable crunch","alternative":"Ab wheel","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT160","defaultExercise":"Ab wheel or cable crunch","alternative":"Reverse crunch","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT161","defaultExercise":"Ab wheel or cable crunch","alternative":"Stability-ball crunch","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"}],"ingredientCache":[{"id":"ING001","name":"Chicken breast","servingDescription":"100 g cooked","kcal":165,"protein":31,"carbs":0,"fat":3.6,"notes":"Example only; replace with your package/cooked-weight values.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"cooked","baseAmount":100.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING002","name":"0% Greek yoghurt","servingDescription":"100 g","kcal":59,"protein":10.3,"carbs":3.6,"fat":0.4,"notes":"Example only; brands vary.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"","baseAmount":100.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING003","name":"Whey protein","servingDescription":"30 g scoop","kcal":120,"protein":24,"carbs":3,"fat":2,"notes":"Use the exact label values.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"","baseAmount":30.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{"scoop":30.0},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING004","name":"Egg whites","servingDescription":"100 g","kcal":52,"protein":10.9,"carbs":0.7,"fat":0.2,"notes":"Example only.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"","baseAmount":100.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING005","name":"Cooked white rice","servingDescription":"100 g","kcal":130,"protein":2.4,"carbs":28.2,"fat":0.3,"notes":"Cooked weight; example only.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"","baseAmount":100.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING006","name":"Boiled potato","servingDescription":"100 g","kcal":87,"protein":1.9,"carbs":20.1,"fat":0.1,"notes":"Example only.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"","baseAmount":100.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING007","name":"Tuna in water, drained","servingDescription":"100 g","kcal":116,"protein":25.5,"carbs":0,"fat":0.8,"notes":"Check the can label.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"","baseAmount":100.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING008","name":"Low-fat cottage cheese","servingDescription":"100 g","kcal":82,"protein":11.1,"carbs":3.4,"fat":2.3,"notes":"Brands vary.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"","baseAmount":100.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING009","name":"Lean turkey mince","servingDescription":"100 g","kcal":145,"protein":21,"carbs":0,"fat":6,"notes":"Use your package values.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"","baseAmount":100.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING010","name":"Courgette","servingDescription":"100 g","kcal":17,"protein":1.2,"carbs":3.1,"fat":0.3,"notes":"Example only.","updatedAt":"2026-07-19T10:00:00.000Z","brand":"","foodState":"","baseAmount":100.0,"baseUnit":"g","densityGPerMl":"","fibre":0,"sodiumMg":0,"aliases":[],"commonMeasures":{},"source":"Example cache – verify","sourceId":"","sourceUrl":"","confirmed":false},{"id":"ING011","name":"Chicken breast, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":120,"protein":22.5,"carbs":0,"fat":2.6,"fibre":0,"sodiumMg":45,"aliases":["raw chicken breast","chicken fillet"],"commonMeasures":{},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING012","name":"Olive oil","brand":"","foodState":"","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":884,"protein":0,"carbs":0,"fat":100,"fibre":0,"sodiumMg":0,"aliases":["extra virgin olive oil","evoo"],"commonMeasures":{"tbsp":13.5,"tsp":4.5},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING013","name":"Onion, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":40,"protein":1.1,"carbs":9.3,"fat":0.1,"fibre":1.7,"sodiumMg":4,"aliases":["onion","yellow onion","white onion","red onion"],"commonMeasures":{"each":150,"medium":150,"small":90,"large":220},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING014","name":"Garlic, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":149,"protein":6.4,"carbs":33.1,"fat":0.5,"fibre":2.1,"sodiumMg":17,"aliases":["garlic","garlic clove"],"commonMeasures":{"clove":3,"tsp":2.8},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING015","name":"Chopped tomatoes, canned","brand":"","foodState":"canned","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":24,"protein":1.2,"carbs":4.0,"fat":0.2,"fibre":1.2,"sodiumMg":120,"aliases":["canned tomatoes","tinned tomatoes","chopped tomato"],"commonMeasures":{"can":400},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING016","name":"Tomato passata","brand":"","foodState":"","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":29,"protein":1.4,"carbs":4.8,"fat":0.2,"fibre":1.5,"sodiumMg":210,"aliases":["passata","tomato puree sauce"],"commonMeasures":{"cup":245,"tbsp":15},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING017","name":"Spinach, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":23,"protein":2.9,"carbs":3.6,"fat":0.4,"fibre":2.2,"sodiumMg":79,"aliases":["spinach","baby spinach"],"commonMeasures":{"cup":30},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING018","name":"Broccoli, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":34,"protein":2.8,"carbs":6.6,"fat":0.4,"fibre":2.6,"sodiumMg":33,"aliases":["broccoli","broccoli florets"],"commonMeasures":{"cup":91},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING019","name":"Carrot, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":41,"protein":0.9,"carbs":9.6,"fat":0.2,"fibre":2.8,"sodiumMg":69,"aliases":["carrot","carrots"],"commonMeasures":{"each":61,"medium":61,"cup":128},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING020","name":"Mushrooms, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":22,"protein":3.1,"carbs":3.3,"fat":0.3,"fibre":1.0,"sodiumMg":5,"aliases":["mushroom","mushrooms","button mushrooms"],"commonMeasures":{"cup":70},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING021","name":"Rolled oats, dry","brand":"","foodState":"dry","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":379,"protein":13.2,"carbs":67.7,"fat":6.5,"fibre":10.1,"sodiumMg":6,"aliases":["oats","rolled oats","porridge oats"],"commonMeasures":{"cup":80,"tbsp":5},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING022","name":"Basmati rice, dry","brand":"","foodState":"dry","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":356,"protein":8.9,"carbs":78.6,"fat":0.9,"fibre":1.0,"sodiumMg":5,"aliases":["basmati rice","white rice dry","uncooked rice"],"commonMeasures":{"cup":185},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING023","name":"Pasta, dry","brand":"","foodState":"dry","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":371,"protein":13.0,"carbs":74.7,"fat":1.5,"fibre":3.2,"sodiumMg":6,"aliases":["dry pasta","uncooked pasta","spaghetti dry"],"commonMeasures":{"cup":100},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING024","name":"Pasta, cooked","brand":"","foodState":"cooked","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":158,"protein":5.8,"carbs":30.9,"fat":0.9,"fibre":1.8,"sodiumMg":1,"aliases":["cooked pasta","boiled pasta"],"commonMeasures":{"cup":140},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING025","name":"Lean beef mince, 5% fat","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":137,"protein":21.4,"carbs":0,"fat":5.0,"fibre":0,"sodiumMg":66,"aliases":["lean beef mince","ground beef 5%","minced beef"],"commonMeasures":{},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING026","name":"Salmon fillet, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":208,"protein":20.0,"carbs":0,"fat":13.0,"fibre":0,"sodiumMg":59,"aliases":["salmon","salmon fillet"],"commonMeasures":{},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING027","name":"Whole egg, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":143,"protein":12.6,"carbs":0.7,"fat":9.5,"fibre":0,"sodiumMg":142,"aliases":["egg","eggs","whole egg"],"commonMeasures":{"each":50,"large":50,"medium":44},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING028","name":"Skimmed milk","brand":"","foodState":"","servingDescription":"100 ml","baseAmount":100,"baseUnit":"ml","densityGPerMl":1,"kcal":34,"protein":3.4,"carbs":5.0,"fat":0.1,"fibre":0,"sodiumMg":44,"aliases":["skim milk","skimmed milk","fat free milk"],"commonMeasures":{"cup":244,"tbsp":15},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING029","name":"Cheddar cheese","brand":"","foodState":"","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":403,"protein":25.0,"carbs":1.3,"fat":33.0,"fibre":0,"sodiumMg":621,"aliases":["cheddar","cheese"],"commonMeasures":{"cup":113,"slice":28},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING030","name":"Lentils, cooked","brand":"","foodState":"cooked","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":116,"protein":9.0,"carbs":20.1,"fat":0.4,"fibre":7.9,"sodiumMg":2,"aliases":["lentils","cooked lentils"],"commonMeasures":{"cup":198},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING031","name":"Chickpeas, drained","brand":"","foodState":"drained","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":139,"protein":7.2,"carbs":19.1,"fat":2.9,"fibre":5.1,"sodiumMg":240,"aliases":["chickpeas","garbanzo beans"],"commonMeasures":{"cup":164,"can":240},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING032","name":"Kidney beans, drained","brand":"","foodState":"drained","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":110,"protein":7.7,"carbs":14.5,"fat":0.6,"fibre":6.4,"sodiumMg":240,"aliases":["kidney beans","red kidney beans"],"commonMeasures":{"cup":177,"can":240},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING033","name":"Banana, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":89,"protein":1.1,"carbs":22.8,"fat":0.3,"fibre":2.6,"sodiumMg":1,"aliases":["banana"],"commonMeasures":{"each":118,"medium":118,"small":101,"large":136},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING034","name":"Apple, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":52,"protein":0.3,"carbs":13.8,"fat":0.2,"fibre":2.4,"sodiumMg":1,"aliases":["apple"],"commonMeasures":{"each":182,"medium":182,"small":149,"large":223},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING035","name":"Blueberries, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":57,"protein":0.7,"carbs":14.5,"fat":0.3,"fibre":2.4,"sodiumMg":1,"aliases":["blueberries","blueberry"],"commonMeasures":{"cup":148},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING036","name":"Honey","brand":"","foodState":"","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":304,"protein":0.3,"carbs":82.4,"fat":0,"fibre":0.2,"sodiumMg":4,"aliases":["honey"],"commonMeasures":{"tbsp":21,"tsp":7},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING037","name":"Plain wheat flour","brand":"","foodState":"dry","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":364,"protein":10.3,"carbs":76.3,"fat":1.0,"fibre":2.7,"sodiumMg":2,"aliases":["flour","plain flour","all purpose flour"],"commonMeasures":{"cup":125,"tbsp":8},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING038","name":"Butter","brand":"","foodState":"","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":717,"protein":0.9,"carbs":0.1,"fat":81.1,"fibre":0,"sodiumMg":11,"aliases":["butter","unsalted butter","salted butter"],"commonMeasures":{"tbsp":14,"tsp":4.7},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING039","name":"Granulated sugar","brand":"","foodState":"dry","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":387,"protein":0,"carbs":100,"fat":0,"fibre":0,"sodiumMg":1,"aliases":["sugar","white sugar","caster sugar"],"commonMeasures":{"cup":200,"tbsp":12.5,"tsp":4.2},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING040","name":"Soy sauce","brand":"","foodState":"","servingDescription":"100 ml","baseAmount":100,"baseUnit":"ml","densityGPerMl":1,"kcal":53,"protein":8.1,"carbs":4.9,"fat":0.6,"fibre":0.8,"sodiumMg":5493,"aliases":["soy sauce","light soy sauce"],"commonMeasures":{"tbsp":15,"tsp":5},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING041","name":"Lemon juice","brand":"","foodState":"","servingDescription":"100 ml","baseAmount":100,"baseUnit":"ml","densityGPerMl":1,"kcal":22,"protein":0.4,"carbs":6.9,"fat":0.2,"fibre":0.3,"sodiumMg":1,"aliases":["lemon juice","juice of lemon"],"commonMeasures":{"tbsp":15,"tsp":5,"lemon":48},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING042","name":"Coconut milk, canned","brand":"","foodState":"canned","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":197,"protein":2.0,"carbs":2.8,"fat":21.3,"fibre":0,"sodiumMg":15,"aliases":["coconut milk","full fat coconut milk"],"commonMeasures":{"cup":240,"can":400},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING043","name":"White bread","brand":"","foodState":"","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":250,"protein":9.0,"carbs":49.0,"fat":3.2,"fibre":2.7,"sodiumMg":491,"aliases":["bread","white bread"],"commonMeasures":{"slice":36},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING044","name":"Sweet potato, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":86,"protein":1.6,"carbs":20.1,"fat":0.1,"fibre":3.0,"sodiumMg":55,"aliases":["sweet potato","sweet potatoes"],"commonMeasures":{"each":130,"medium":130},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING045","name":"Avocado, raw","brand":"","foodState":"raw","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":160,"protein":2.0,"carbs":8.5,"fat":14.7,"fibre":6.7,"sodiumMg":7,"aliases":["avocado"],"commonMeasures":{"each":136,"half":68},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING046","name":"Low-fat mayonnaise","brand":"","foodState":"","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":270,"protein":1.0,"carbs":12.0,"fat":24.0,"fibre":0,"sodiumMg":700,"aliases":["light mayonnaise","low fat mayo","mayonnaise"],"commonMeasures":{"tbsp":15,"tsp":5},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING047","name":"Peanut butter","brand":"","foodState":"","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":588,"protein":25.0,"carbs":20.0,"fat":50.0,"fibre":6.0,"sodiumMg":426,"aliases":["peanut butter"],"commonMeasures":{"tbsp":16,"tsp":5.3},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING048","name":"Plain low-fat yoghurt","brand":"","foodState":"","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":63,"protein":5.3,"carbs":7.0,"fat":1.6,"fibre":0,"sodiumMg":70,"aliases":["plain yoghurt","low fat yogurt","natural yoghurt"],"commonMeasures":{"cup":245,"tbsp":15},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING049","name":"Quinoa, cooked","brand":"","foodState":"cooked","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":120,"protein":4.4,"carbs":21.3,"fat":1.9,"fibre":2.8,"sodiumMg":7,"aliases":["quinoa","cooked quinoa"],"commonMeasures":{"cup":185},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"},{"id":"ING050","name":"Frozen mixed vegetables","brand":"","foodState":"frozen","servingDescription":"100 g","baseAmount":100,"baseUnit":"g","densityGPerMl":"","kcal":65,"protein":3.0,"carbs":11.0,"fat":0.6,"fibre":4.0,"sodiumMg":60,"aliases":["mixed vegetables","frozen vegetables"],"commonMeasures":{"cup":150},"source":"Generic reference – verify","sourceId":"","sourceUrl":"","confirmed":false,"notes":"Starting reference value. Confirm against a package label or reference record before relying on it.","updatedAt":"2026-07-19T20:55:00.000Z"}],"recipes":[{"id":"RCP001","name":"Chicken courgette rice bowl","category":"Normal cut","servings":2,"totalKcal":780,"protein":92,"carbs":72,"fat":14,"rflFriendly":"No","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Example values only. No bell peppers; adjust to your ingredients.","favourite":false,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z","sourceType":"Seed","sourceName":"Lift &amp; Cut starter recipe","sourceUrl":"","sourceAuthor":"","sourceBook":"","importedAt":"","prepTime":"","cookTime":"","totalTime":"","yieldText":"2 servings","finishedWeightG":"","fibre":0,"sodiumMg":0,"nutritionConfidence":"Manual","importStatus":"Ready","tags":[],"imageUrl":"","sourceNutrition":{},"calculateFromIngredients":false},{"id":"RCP002","name":"Greek yoghurt whey bowl","category":"High protein","servings":1,"totalKcal":410,"protein":55,"carbs":32,"fat":6,"rflFriendly":"Yes","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Good quick protein option; use exact label values.","favourite":true,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z","sourceType":"Seed","sourceName":"Lift &amp; Cut starter recipe","sourceUrl":"","sourceAuthor":"","sourceBook":"","importedAt":"","prepTime":"","cookTime":"","totalTime":"","yieldText":"1 servings","finishedWeightG":"","fibre":0,"sodiumMg":0,"nutritionConfidence":"Manual","importStatus":"Ready","tags":[],"imageUrl":"","sourceNutrition":{},"calculateFromIngredients":false},{"id":"RCP003","name":"Egg-white spinach omelette","category":"RFL-friendly","servings":1,"totalKcal":260,"protein":42,"carbs":8,"fat":6,"rflFriendly":"Yes","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Use herbs, spinach, mushrooms; avoid bell peppers.","favourite":true,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z","sourceType":"Seed","sourceName":"Lift &amp; Cut starter recipe","sourceUrl":"","sourceAuthor":"","sourceBook":"","importedAt":"","prepTime":"","cookTime":"","totalTime":"","yieldText":"1 servings","finishedWeightG":"","fibre":0,"sodiumMg":0,"nutritionConfidence":"Manual","importStatus":"Ready","tags":[],"imageUrl":"","sourceNutrition":{},"calculateFromIngredients":false},{"id":"RCP004","name":"Lean turkey tomato mince","category":"Batch cook","servings":4,"totalKcal":1280,"protein":156,"carbs":64,"fat":36,"rflFriendly":"Maybe","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Serve with rice/potatoes outside RFL or vegetables during RFL.","favourite":false,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z","sourceType":"Seed","sourceName":"Lift &amp; Cut starter recipe","sourceUrl":"","sourceAuthor":"","sourceBook":"","importedAt":"","prepTime":"","cookTime":"","totalTime":"","yieldText":"4 servings","finishedWeightG":"","fibre":0,"sodiumMg":0,"nutritionConfidence":"Manual","importStatus":"Ready","tags":[],"imageUrl":"","sourceNutrition":{},"calculateFromIngredients":false},{"id":"RCP005","name":"Tuna potato salad","category":"Normal cut","servings":2,"totalKcal":650,"protein":62,"carbs":82,"fat":8,"rflFriendly":"No","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Tuna is not shellfish; avoid mayo-heavy versions.","favourite":false,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z","sourceType":"Seed","sourceName":"Lift &amp; Cut starter recipe","sourceUrl":"","sourceAuthor":"","sourceBook":"","importedAt":"","prepTime":"","cookTime":"","totalTime":"","yieldText":"2 servings","finishedWeightG":"","fibre":0,"sodiumMg":0,"nutritionConfidence":"Manual","importStatus":"Ready","tags":[],"imageUrl":"","sourceNutrition":{},"calculateFromIngredients":false},{"id":"RCP006","name":"Cottage cheese chicken salad","category":"RFL-friendly","servings":1,"totalKcal":360,"protein":60,"carbs":14,"fat":7,"rflFriendly":"Yes","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Use cucumber, lettuce, tomato; no bell peppers.","favourite":true,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z","sourceType":"Seed","sourceName":"Lift &amp; Cut starter recipe","sourceUrl":"","sourceAuthor":"","sourceBook":"","importedAt":"","prepTime":"","cookTime":"","totalTime":"","yieldText":"1 servings","finishedWeightG":"","fibre":0,"sodiumMg":0,"nutritionConfidence":"Manual","importStatus":"Ready","tags":[],"imageUrl":"","sourceNutrition":{},"calculateFromIngredients":false}],"workoutSessions":[],"workoutLogs":[],"foodLog":[],"bodyMetrics":[],"dailyCheckins":[],"dietPhases":[],"cardioLogs":[],"progressPhotos":[]}</x:v>
+      </x:c>
+      <x:c r="C4" s="137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="158" t="n">
+        <x:v>46222.875</x:v>
+      </x:c>
+      <x:c r="E4" s="137" t="str">
         <x:v>template</x:v>
       </x:c>
-      <x:c r="F4" s="72" t="str">
-        <x:v>v2.2 template</x:v>
-      </x:c>
-      <x:c r="G4" s="73" t="str"/>
+      <x:c r="F4" s="137" t="str">
+        <x:v>v2.3 template</x:v>
+      </x:c>
+      <x:c r="G4" s="138"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="74" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="75" t="str">
-        <x:v>compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT129","defaultExercise":"Cable rear-delt fly or face pull","alternative":"Band face pull","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT130","defaultExercise":"Rear-delt cable fly","alternative":"Dumbbell rear-delt fly","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT131","defaultExercise":"Rear-delt cable fly","alternative":"Reverse pec deck","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT132","defaultExercise":"Rear-delt cable fly","alternative":"Band face pull","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT133","defaultExercise":"Cable triceps pushdown","alternative":"Band triceps pushdown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT134","defaultExercise":"Cable triceps pushdown","alternative":"Dumbbell skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT135","defaultExercise":"Cable triceps pushdown","alternative":"EZ-bar skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT136","defaultExercise":"Cable triceps pushdown","alternative":"Close-grip push-up","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT137","defaultExercise":"Overhead cable triceps extension","alternative":"Dumbbell skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT138","defaultExercise":"Overhead cable triceps extension","alternative":"EZ-bar skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT139","defaultExercise":"Overhead cable triceps extension","alternative":"Band triceps pushdown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT140","defaultExercise":"Overhead triceps extension","alternative":"Overhead cable triceps extension","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT141","defaultExercise":"Overhead triceps extension","alternative":"Dumbbell skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT142","defaultExercise":"Overhead triceps extension","alternative":"EZ-bar skull crusher","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT143","defaultExercise":"Overhead triceps extension","alternative":"Band triceps pushdown","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT144","defaultExercise":"Incline dumbbell or cable curl","alternative":"EZ-bar curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT145","defaultExercise":"Incline dumbbell or cable curl","alternative":"Band curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT146","defaultExercise":"Incline dumbbell or cable curl","alternative":"Preacher curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT147","defaultExercise":"Cable curl","alternative":"Incline dumbbell curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT148","defaultExercise":"Cable curl","alternative":"Dumbbell hammer curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT149","defaultExercise":"Cable curl","alternative":"EZ-bar curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT150","defaultExercise":"Cable curl","alternative":"Band curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT151","defaultExercise":"Cable curl","alternative":"Preacher curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT152","defaultExercise":"Dumbbell hammer curl","alternative":"EZ-bar curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT153","defaultExercise":"Dumbbell hammer curl","alternative":"Band curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT154","defaultExercise":"Hammer curl","alternative":"Dumbbell hammer curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT155","defaultExercise":"Hammer curl","alternative":"Cable curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT156","defaultExercise":"Hammer curl","alternative":"Band curl","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT157","defaultExercise":"Dead bug or Pallof press","alternative":"Band Pallof press","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT158","defaultExercise":"Dead bug or Pallof press","alternative":"Side plank","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT159","defaultExercise":"Ab wheel or cable crunch","alternative":"Ab wheel","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT160","defaultExercise":"Ab wheel or cable crunch","alternative":"Reverse crunch","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"},{"id":"ALT161","defaultExercise":"Ab wheel or cable crunch","alternative":"Stability-ball crunch","reason":"Equipment match","notes":"Equipment-compatible option.","updatedAt":"2026-07-19T15:45:00.000Z"}],"ingredientCache":[{"id":"ING001","name":"Chicken breast","servingDescription":"100 g cooked","kcal":165,"protein":31,"carbs":0,"fat":3.6,"notes":"Example only; replace with your package/cooked-weight values.","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ING002","name":"0% Greek yoghurt","servingDescription":"100 g","kcal":59,"protein":10.3,"carbs":3.6,"fat":0.4,"notes":"Example only; brands vary.","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ING003","name":"Whey protein","servingDescription":"30 g scoop","kcal":120,"protein":24,"carbs":3,"fat":2,"notes":"Use the exact label values.","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ING004","name":"Egg whites","servingDescription":"100 g","kcal":52,"protein":10.9,"carbs":0.7,"fat":0.2,"notes":"Example only.","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ING005","name":"Cooked white rice","servingDescription":"100 g","kcal":130,"protein":2.4,"carbs":28.2,"fat":0.3,"notes":"Cooked weight; example only.","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ING006","name":"Boiled potato","servingDescription":"100 g","kcal":87,"protein":1.9,"carbs":20.1,"fat":0.1,"notes":"Example only.","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ING007","name":"Tuna in water, drained","servingDescription":"100 g","kcal":116,"protein":25.5,"carbs":0,"fat":0.8,"notes":"Check the can label.","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ING008","name":"Low-fat cottage cheese","servingDescription":"100 g","kcal":82,"protein":11.1,"carbs":3.4,"fat":2.3,"notes":"Brands vary.","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ING009","name":"Lean turkey mince","servingDescription":"100 g","kcal":145,"protein":21,"carbs":0,"fat":6,"notes":"Use your package values.","updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"ING010","name":"Courgette","servingDescription":"100 g","kcal":17,"protein":1.2,"carbs":3.1,"fat":0.3,"notes":"Example only.","updatedAt":"2026-07-19T10:00:00.000Z"}],"recipes":[{"id":"RCP001","name":"Chicken courgette rice bowl","category":"Normal cut","servings":2,"totalKcal":780,"protein":92,"carbs":72,"fat":14,"rflFriendly":"No","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Example values only. No bell peppers; adjust to your ingredients.","favourite":false,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"RCP002","name":"Greek yoghurt whey bowl","category":"High protein","servings":1,"totalKcal":410,"protein":55,"carbs":32,"fat":6,"rflFriendly":"Yes","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Good quick protein option; use exact label values.","favourite":true,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"RCP003","name":"Egg-white spinach omelette","category":"RFL-friendly","servings":1,"totalKcal":260,"protein":42,"carbs":8,"fat":6,"rflFriendly":"Yes","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Use herbs, spinach, mushrooms; avoid bell peppers.","favourite":true,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"RCP004","name":"Lean turkey tomato mince","category":"Batch cook","servings":4,"totalKcal":1280,"protein":156,"carbs":64,"fat":36,"rflFriendly":"Maybe","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Serve with rice/potatoes outside RFL or vegetables during RFL.","favourite":false,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"RCP005","name":"Tuna potato salad","category":"Normal cut","servings":2,"totalKcal":650,"protein":62,"carbs":82,"fat":8,"rflFriendly":"No","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Tuna is not shellfish; avoid mayo-heavy versions.","favourite":false,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z"},{"id":"RCP006","name":"Cottage cheese chicken salad","category":"RFL-friendly","servings":1,"totalKcal":360,"protein":60,"carbs":14,"fat":7,"rflFriendly":"Yes","noBellPeppers":"Yes","noShellfish":"Yes","notes":"Use cucumber, lettuce, tomato; no bell peppers.","favourite":true,"instructions":"","ingredients":[],"updatedAt":"2026-07-19T10:00:00.000Z"}],"workoutSessions":[],"workoutLogs":[],"foodLog":[],"bodyMetrics":[],"dailyCheckins":[],"dietPhases":[],"cardioLogs":[],"progressPhotos":[]}</x:v>
-      </x:c>
-      <x:c r="C5" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="103" t="n">
-        <x:v>46222.65625</x:v>
-      </x:c>
-      <x:c r="E5" s="75" t="str">
-        <x:v>template</x:v>
-      </x:c>
-      <x:c r="F5" s="75" t="str">
-        <x:v>v2.2 template</x:v>
-      </x:c>
-      <x:c r="G5" s="76" t="str"/>
+      <x:c r="A5" s="74"/>
+      <x:c r="B5" s="75"/>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="103"/>
+      <x:c r="E5" s="75"/>
+      <x:c r="F5" s="75"/>
+      <x:c r="G5" s="76"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6"/>
@@ -2201,7 +2442,7 @@
     <x:mergeCell ref="A12:H12"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6b3be7c53a34da8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4be63c8f76494783"/>
 </x:worksheet>
 </file>
 
@@ -3266,454 +3507,631 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="56" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="44" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="54" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="63" t="str">
+      <x:c r="A1" s="118" t="str">
         <x:v>Key</x:v>
       </x:c>
-      <x:c r="B1" s="63" t="str">
+      <x:c r="B1" s="118" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C1" s="63" t="str">
+      <x:c r="C1" s="118" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D1" s="63" t="str">
+      <x:c r="D1" s="118" t="str">
         <x:v>Group</x:v>
       </x:c>
-      <x:c r="E1" s="63" t="str">
+      <x:c r="E1" s="118" t="str">
         <x:v>Description</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="64" t="str">
+      <x:c r="A2" s="133" t="str">
         <x:v>profileName</x:v>
       </x:c>
-      <x:c r="B2" s="65" t="str"/>
-      <x:c r="C2" s="65" t="str">
+      <x:c r="B2" s="134" t="str"/>
+      <x:c r="C2" s="134" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="D2" s="65" t="str">
+      <x:c r="D2" s="134" t="str">
         <x:v>Profile</x:v>
       </x:c>
-      <x:c r="E2" s="66" t="str">
+      <x:c r="E2" s="135" t="str">
         <x:v>Name shown in the app</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="67" t="str">
+      <x:c r="A3" s="136" t="str">
         <x:v>age</x:v>
       </x:c>
-      <x:c r="B3" s="68" t="str"/>
-      <x:c r="C3" s="68" t="str">
+      <x:c r="B3" s="137" t="str"/>
+      <x:c r="C3" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D3" s="68" t="str">
+      <x:c r="D3" s="137" t="str">
         <x:v>Profile</x:v>
       </x:c>
-      <x:c r="E3" s="69" t="str">
+      <x:c r="E3" s="138" t="str">
         <x:v>Age</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="67" t="str">
+      <x:c r="A4" s="136" t="str">
         <x:v>heightCm</x:v>
       </x:c>
-      <x:c r="B4" s="68" t="str"/>
-      <x:c r="C4" s="68" t="str">
+      <x:c r="B4" s="137" t="str"/>
+      <x:c r="C4" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D4" s="68" t="str">
+      <x:c r="D4" s="137" t="str">
         <x:v>Profile</x:v>
       </x:c>
-      <x:c r="E4" s="69" t="str">
+      <x:c r="E4" s="138" t="str">
         <x:v>Height in centimetres</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="67" t="str">
+      <x:c r="A5" s="136" t="str">
         <x:v>targetWeightKg</x:v>
       </x:c>
-      <x:c r="B5" s="68" t="str"/>
-      <x:c r="C5" s="68" t="str">
+      <x:c r="B5" s="137" t="str"/>
+      <x:c r="C5" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D5" s="68" t="str">
+      <x:c r="D5" s="137" t="str">
         <x:v>Profile</x:v>
       </x:c>
-      <x:c r="E5" s="69" t="str">
+      <x:c r="E5" s="138" t="str">
         <x:v>Long-term weight target</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="67" t="str">
+      <x:c r="A6" s="136" t="str">
         <x:v>activeProgram</x:v>
       </x:c>
-      <x:c r="B6" s="68" t="str">
+      <x:c r="B6" s="137" t="str">
         <x:v>UL4</x:v>
       </x:c>
-      <x:c r="C6" s="68" t="str">
+      <x:c r="C6" s="137" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="D6" s="68" t="str">
+      <x:c r="D6" s="137" t="str">
         <x:v>Training</x:v>
       </x:c>
-      <x:c r="E6" s="69" t="str">
+      <x:c r="E6" s="138" t="str">
         <x:v>Active program ID</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="67" t="str">
+      <x:c r="A7" s="136" t="str">
         <x:v>dietMode</x:v>
       </x:c>
-      <x:c r="B7" s="68" t="str">
+      <x:c r="B7" s="137" t="str">
         <x:v>Normal / moderate deficit</x:v>
       </x:c>
-      <x:c r="C7" s="68" t="str">
+      <x:c r="C7" s="137" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="D7" s="68" t="str">
+      <x:c r="D7" s="137" t="str">
         <x:v>Diet</x:v>
       </x:c>
-      <x:c r="E7" s="69" t="str">
+      <x:c r="E7" s="138" t="str">
         <x:v>Current diet phase</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="67" t="str">
+      <x:c r="A8" s="136" t="str">
         <x:v>normalCalorieTarget</x:v>
       </x:c>
-      <x:c r="B8" s="68" t="n">
+      <x:c r="B8" s="137" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="C8" s="68" t="str">
+      <x:c r="C8" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D8" s="68" t="str">
+      <x:c r="D8" s="137" t="str">
         <x:v>Diet</x:v>
       </x:c>
-      <x:c r="E8" s="69" t="str">
+      <x:c r="E8" s="138" t="str">
         <x:v>Daily calorie target outside RFL</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="67" t="str">
+      <x:c r="A9" s="136" t="str">
         <x:v>normalProteinTarget</x:v>
       </x:c>
-      <x:c r="B9" s="68" t="n">
+      <x:c r="B9" s="137" t="n">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C9" s="68" t="str">
+      <x:c r="C9" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D9" s="68" t="str">
+      <x:c r="D9" s="137" t="str">
         <x:v>Diet</x:v>
       </x:c>
-      <x:c r="E9" s="69" t="str">
+      <x:c r="E9" s="138" t="str">
         <x:v>Daily protein target outside RFL</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="67" t="str">
+      <x:c r="A10" s="136" t="str">
         <x:v>normalCarbTarget</x:v>
       </x:c>
-      <x:c r="B10" s="68" t="n">
+      <x:c r="B10" s="137" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="C10" s="68" t="str">
+      <x:c r="C10" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D10" s="68" t="str">
+      <x:c r="D10" s="137" t="str">
         <x:v>Diet</x:v>
       </x:c>
-      <x:c r="E10" s="69" t="str">
+      <x:c r="E10" s="138" t="str">
         <x:v>Daily carbohydrate target outside RFL</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="67" t="str">
+      <x:c r="A11" s="136" t="str">
         <x:v>normalFatTarget</x:v>
       </x:c>
-      <x:c r="B11" s="68" t="n">
+      <x:c r="B11" s="137" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C11" s="68" t="str">
+      <x:c r="C11" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D11" s="68" t="str">
+      <x:c r="D11" s="137" t="str">
         <x:v>Diet</x:v>
       </x:c>
-      <x:c r="E11" s="69" t="str">
+      <x:c r="E11" s="138" t="str">
         <x:v>Daily fat target outside RFL</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="67" t="str">
+      <x:c r="A12" s="136" t="str">
         <x:v>rflCalorieTarget</x:v>
       </x:c>
-      <x:c r="B12" s="68" t="str"/>
-      <x:c r="C12" s="68" t="str">
+      <x:c r="B12" s="137" t="str"/>
+      <x:c r="C12" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D12" s="68" t="str">
+      <x:c r="D12" s="137" t="str">
         <x:v>RFL</x:v>
       </x:c>
-      <x:c r="E12" s="69" t="str">
+      <x:c r="E12" s="138" t="str">
         <x:v>Use your edition of RFL; do not guess</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="67" t="str">
+      <x:c r="A13" s="136" t="str">
         <x:v>rflProteinTarget</x:v>
       </x:c>
-      <x:c r="B13" s="68" t="str"/>
-      <x:c r="C13" s="68" t="str">
+      <x:c r="B13" s="137" t="str"/>
+      <x:c r="C13" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D13" s="68" t="str">
+      <x:c r="D13" s="137" t="str">
         <x:v>RFL</x:v>
       </x:c>
-      <x:c r="E13" s="69" t="str">
+      <x:c r="E13" s="138" t="str">
         <x:v>Use your edition of RFL; do not guess</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="67" t="str">
+      <x:c r="A14" s="136" t="str">
         <x:v>rflCarbTarget</x:v>
       </x:c>
-      <x:c r="B14" s="68" t="str"/>
-      <x:c r="C14" s="68" t="str">
+      <x:c r="B14" s="137" t="str"/>
+      <x:c r="C14" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D14" s="68" t="str">
+      <x:c r="D14" s="137" t="str">
         <x:v>RFL</x:v>
       </x:c>
-      <x:c r="E14" s="69" t="str">
+      <x:c r="E14" s="138" t="str">
         <x:v>Use your edition of RFL; do not guess</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="67" t="str">
+      <x:c r="A15" s="136" t="str">
         <x:v>rflFatTarget</x:v>
       </x:c>
-      <x:c r="B15" s="68" t="str"/>
-      <x:c r="C15" s="68" t="str">
+      <x:c r="B15" s="137" t="str"/>
+      <x:c r="C15" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D15" s="68" t="str">
+      <x:c r="D15" s="137" t="str">
         <x:v>RFL</x:v>
       </x:c>
-      <x:c r="E15" s="69" t="str">
+      <x:c r="E15" s="138" t="str">
         <x:v>Use your edition of RFL; do not guess</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="67" t="str">
+      <x:c r="A16" s="136" t="str">
         <x:v>stepsTarget</x:v>
       </x:c>
-      <x:c r="B16" s="68" t="n">
+      <x:c r="B16" s="137" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="C16" s="68" t="str">
+      <x:c r="C16" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D16" s="68" t="str">
+      <x:c r="D16" s="137" t="str">
         <x:v>Recovery</x:v>
       </x:c>
-      <x:c r="E16" s="69" t="str">
+      <x:c r="E16" s="138" t="str">
         <x:v>Daily step target</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="67" t="str">
+      <x:c r="A17" s="136" t="str">
         <x:v>sleepTargetHrs</x:v>
       </x:c>
-      <x:c r="B17" s="68" t="n">
+      <x:c r="B17" s="137" t="n">
         <x:v>7.5</x:v>
       </x:c>
-      <x:c r="C17" s="68" t="str">
+      <x:c r="C17" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D17" s="68" t="str">
+      <x:c r="D17" s="137" t="str">
         <x:v>Recovery</x:v>
       </x:c>
-      <x:c r="E17" s="69" t="str">
+      <x:c r="E17" s="138" t="str">
         <x:v>Daily sleep target</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="67" t="str">
+      <x:c r="A18" s="136" t="str">
         <x:v>waterTargetMl</x:v>
       </x:c>
-      <x:c r="B18" s="68" t="n">
+      <x:c r="B18" s="137" t="n">
         <x:v>2500</x:v>
       </x:c>
-      <x:c r="C18" s="68" t="str">
+      <x:c r="C18" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D18" s="68" t="str">
+      <x:c r="D18" s="137" t="str">
         <x:v>Recovery</x:v>
       </x:c>
-      <x:c r="E18" s="69" t="str">
+      <x:c r="E18" s="138" t="str">
         <x:v>Daily water target</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="67" t="str">
+      <x:c r="A19" s="136" t="str">
         <x:v>noBellPeppers</x:v>
       </x:c>
-      <x:c r="B19" s="70" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C19" s="68" t="str">
+      <x:c r="B19" s="139" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="137" t="str">
         <x:v>boolean</x:v>
       </x:c>
-      <x:c r="D19" s="68" t="str">
+      <x:c r="D19" s="137" t="str">
         <x:v>Diet</x:v>
       </x:c>
-      <x:c r="E19" s="69" t="str">
+      <x:c r="E19" s="138" t="str">
         <x:v>Recipe preference</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="67" t="str">
+      <x:c r="A20" s="136" t="str">
         <x:v>noShellfish</x:v>
       </x:c>
-      <x:c r="B20" s="70" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="68" t="str">
+      <x:c r="B20" s="139" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="137" t="str">
         <x:v>boolean</x:v>
       </x:c>
-      <x:c r="D20" s="68" t="str">
+      <x:c r="D20" s="137" t="str">
         <x:v>Diet</x:v>
       </x:c>
-      <x:c r="E20" s="69" t="str">
+      <x:c r="E20" s="138" t="str">
         <x:v>Recipe preference</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="67" t="str">
+      <x:c r="A21" s="136" t="str">
         <x:v>lastSession</x:v>
       </x:c>
-      <x:c r="B21" s="68" t="str">
+      <x:c r="B21" s="137" t="str">
         <x:v>UL4|lower-a</x:v>
       </x:c>
-      <x:c r="C21" s="68" t="str">
+      <x:c r="C21" s="137" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="D21" s="68" t="str">
+      <x:c r="D21" s="137" t="str">
         <x:v>Training</x:v>
       </x:c>
-      <x:c r="E21" s="69" t="str">
+      <x:c r="E21" s="138" t="str">
         <x:v>Last selected ProgramID|SessionID</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="67" t="str">
+      <x:c r="A22" s="136" t="str">
         <x:v>weekStartsMonday</x:v>
       </x:c>
-      <x:c r="B22" s="70" t="b">
+      <x:c r="B22" s="139" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C22" s="68" t="str">
+      <x:c r="C22" s="137" t="str">
         <x:v>boolean</x:v>
       </x:c>
-      <x:c r="D22" s="68" t="str">
+      <x:c r="D22" s="137" t="str">
         <x:v>App</x:v>
       </x:c>
-      <x:c r="E22" s="69" t="str">
+      <x:c r="E22" s="138" t="str">
         <x:v>Week starts Monday</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="67" t="str">
+      <x:c r="A23" s="136" t="str">
         <x:v>availableEquipment</x:v>
       </x:c>
-      <x:c r="B23" s="68" t="str">
+      <x:c r="B23" s="137" t="str">
         <x:v>["Bodyweight / floor space", "Power rack / squat stands", "Barbell + plates", "Adjustable bench", "Adjustable dumbbells", "Cable station / functional trainer", "Pull-up bar", "Gymnastic rings / suspension trainer", "Calf raise platform / machine", "Ankle strap", "Rope cable attachment", "Ab wheel"]</x:v>
       </x:c>
-      <x:c r="C23" s="68" t="str">
+      <x:c r="C23" s="137" t="str">
         <x:v>json</x:v>
       </x:c>
-      <x:c r="D23" s="68" t="str">
+      <x:c r="D23" s="137" t="str">
         <x:v>Training</x:v>
       </x:c>
-      <x:c r="E23" s="69" t="str">
+      <x:c r="E23" s="138" t="str">
         <x:v>Selected equipment used by exercise compatibility</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="67" t="str">
+      <x:c r="A24" s="136" t="str">
         <x:v>customEquipment</x:v>
       </x:c>
-      <x:c r="B24" s="68" t="str">
+      <x:c r="B24" s="137" t="str">
         <x:v>[]</x:v>
       </x:c>
-      <x:c r="C24" s="68" t="str">
+      <x:c r="C24" s="137" t="str">
         <x:v>json</x:v>
       </x:c>
-      <x:c r="D24" s="68" t="str">
+      <x:c r="D24" s="137" t="str">
         <x:v>Training</x:v>
       </x:c>
-      <x:c r="E24" s="69" t="str">
+      <x:c r="E24" s="138" t="str">
         <x:v>Custom equipment names</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="67" t="str">
+      <x:c r="A25" s="136" t="str">
         <x:v>equipmentProfileName</x:v>
       </x:c>
-      <x:c r="B25" s="68" t="str">
+      <x:c r="B25" s="137" t="str">
         <x:v>Custom home gym</x:v>
       </x:c>
-      <x:c r="C25" s="68" t="str">
+      <x:c r="C25" s="137" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="D25" s="68" t="str">
+      <x:c r="D25" s="137" t="str">
         <x:v>Training</x:v>
       </x:c>
-      <x:c r="E25" s="69" t="str">
+      <x:c r="E25" s="138" t="str">
         <x:v>Current equipment preset or profile name</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="67" t="str">
+      <x:c r="A26" s="136" t="str">
         <x:v>restTimerDefaultSec</x:v>
       </x:c>
-      <x:c r="B26" s="68" t="n">
+      <x:c r="B26" s="137" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C26" s="68" t="str">
+      <x:c r="C26" s="137" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D26" s="68" t="str">
+      <x:c r="D26" s="137" t="str">
         <x:v>Training</x:v>
       </x:c>
-      <x:c r="E26" s="69" t="str">
+      <x:c r="E26" s="138" t="str">
         <x:v>Default rest timer</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="77" t="str">
+      <x:c r="A27" s="140" t="str">
+        <x:v>autoRestTimer</x:v>
+      </x:c>
+      <x:c r="B27" s="162" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" s="141" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="D27" s="141" t="str">
+        <x:v>Training</x:v>
+      </x:c>
+      <x:c r="E27" s="142" t="str">
+        <x:v>Start the rest timer after completing a work set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="143" t="str">
+        <x:v>restTimerSound</x:v>
+      </x:c>
+      <x:c r="B28" s="144" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C28" s="143" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="D28" s="143" t="str">
+        <x:v>Training</x:v>
+      </x:c>
+      <x:c r="E28" s="143" t="str">
+        <x:v>Play sound when rest timer finishes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="143" t="str">
+        <x:v>autoAdvanceSets</x:v>
+      </x:c>
+      <x:c r="B29" s="144" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C29" s="143" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="D29" s="143" t="str">
+        <x:v>Training</x:v>
+      </x:c>
+      <x:c r="E29" s="143" t="str">
+        <x:v>Move focus to the next incomplete set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="143" t="str">
+        <x:v>weightIncrementKg</x:v>
+      </x:c>
+      <x:c r="B30" s="143" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="C30" s="143" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="D30" s="143" t="str">
+        <x:v>Training</x:v>
+      </x:c>
+      <x:c r="E30" s="143" t="str">
+        <x:v>Default progression increment for barbell/standard exercises</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="143" t="str">
+        <x:v>smallWeightIncrementKg</x:v>
+      </x:c>
+      <x:c r="B31" s="143" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C31" s="143" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="D31" s="143" t="str">
+        <x:v>Training</x:v>
+      </x:c>
+      <x:c r="E31" s="143" t="str">
+        <x:v>Default progression increment for isolation/small exercises</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="143" t="str">
+        <x:v>dumbbellWeightIncrementKg</x:v>
+      </x:c>
+      <x:c r="B32" s="143" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C32" s="143" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="D32" s="143" t="str">
+        <x:v>Training</x:v>
+      </x:c>
+      <x:c r="E32" s="143" t="str">
+        <x:v>Default progression increment for dumbbell exercises</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="143" t="str">
+        <x:v>trainView</x:v>
+      </x:c>
+      <x:c r="B33" s="143" t="str">
+        <x:v>workout</x:v>
+      </x:c>
+      <x:c r="C33" s="143" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D33" s="143" t="str">
+        <x:v>App</x:v>
+      </x:c>
+      <x:c r="E33" s="143" t="str">
+        <x:v>Current Train sub-view</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="143" t="str">
+        <x:v>recipeImportAutoMatch</x:v>
+      </x:c>
+      <x:c r="B34" s="144" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C34" s="143" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="D34" s="143" t="str">
+        <x:v>Recipe import</x:v>
+      </x:c>
+      <x:c r="E34" s="143" t="str">
+        <x:v>Automatically attempt local ingredient matching after import</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="143" t="str">
+        <x:v>recipeImportPreferMetric</x:v>
+      </x:c>
+      <x:c r="B35" s="144" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C35" s="143" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="D35" s="143" t="str">
+        <x:v>Recipe import</x:v>
+      </x:c>
+      <x:c r="E35" s="143" t="str">
+        <x:v>Prefer metric quantities when interpreting recipes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="143" t="str">
+        <x:v>foodReferenceSource</x:v>
+      </x:c>
+      <x:c r="B36" s="143" t="str">
+        <x:v>USDA + Open Food Facts</x:v>
+      </x:c>
+      <x:c r="C36" s="143" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D36" s="143" t="str">
+        <x:v>Recipe import</x:v>
+      </x:c>
+      <x:c r="E36" s="143" t="str">
+        <x:v>Reference search sources used by the v2.3 backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="143" t="str">
         <x:v>theme</x:v>
       </x:c>
-      <x:c r="B27" s="78" t="str">
+      <x:c r="B37" s="143" t="str">
         <x:v>system</x:v>
       </x:c>
-      <x:c r="C27" s="78" t="str">
+      <x:c r="C37" s="143" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="D27" s="78" t="str">
+      <x:c r="D37" s="143" t="str">
         <x:v>App</x:v>
       </x:c>
-      <x:c r="E27" s="79" t="str">
+      <x:c r="E37" s="143" t="str">
         <x:v>system, light, or dark</x:v>
       </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="143"/>
+      <x:c r="B38" s="143"/>
+      <x:c r="C38" s="143"/>
+      <x:c r="D38" s="143"/>
+      <x:c r="E38" s="143"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
@@ -15322,339 +15740,3068 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="6.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="4.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="10" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="34" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="36" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="11" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="54" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="22" t="str">
+      <x:c r="A1" s="118" t="str">
         <x:v>IngredientID</x:v>
       </x:c>
-      <x:c r="B1" s="22" t="str">
+      <x:c r="B1" s="118" t="str">
         <x:v>IngredientName</x:v>
       </x:c>
-      <x:c r="C1" s="22" t="str">
+      <x:c r="C1" s="118" t="str">
+        <x:v>Brand</x:v>
+      </x:c>
+      <x:c r="D1" s="118" t="str">
+        <x:v>FoodState</x:v>
+      </x:c>
+      <x:c r="E1" s="118" t="str">
         <x:v>ServingDescription</x:v>
       </x:c>
-      <x:c r="D1" s="22" t="str">
+      <x:c r="F1" s="118" t="str">
+        <x:v>BaseAmount</x:v>
+      </x:c>
+      <x:c r="G1" s="118" t="str">
+        <x:v>BaseUnit</x:v>
+      </x:c>
+      <x:c r="H1" s="118" t="str">
+        <x:v>DensityGPerMl</x:v>
+      </x:c>
+      <x:c r="I1" s="118" t="str">
         <x:v>kcal</x:v>
       </x:c>
-      <x:c r="E1" s="22" t="str">
+      <x:c r="J1" s="118" t="str">
         <x:v>Protein_g</x:v>
       </x:c>
-      <x:c r="F1" s="22" t="str">
+      <x:c r="K1" s="118" t="str">
         <x:v>Carbs_g</x:v>
       </x:c>
-      <x:c r="G1" s="22" t="str">
+      <x:c r="L1" s="118" t="str">
         <x:v>Fat_g</x:v>
       </x:c>
-      <x:c r="H1" s="22" t="str">
+      <x:c r="M1" s="118" t="str">
+        <x:v>Fibre_g</x:v>
+      </x:c>
+      <x:c r="N1" s="118" t="str">
+        <x:v>Sodium_mg</x:v>
+      </x:c>
+      <x:c r="O1" s="118" t="str">
+        <x:v>AliasesJSON</x:v>
+      </x:c>
+      <x:c r="P1" s="118" t="str">
+        <x:v>CommonMeasuresJSON</x:v>
+      </x:c>
+      <x:c r="Q1" s="118" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="R1" s="118" t="str">
+        <x:v>SourceID</x:v>
+      </x:c>
+      <x:c r="S1" s="118" t="str">
+        <x:v>SourceURL</x:v>
+      </x:c>
+      <x:c r="T1" s="118" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="U1" s="118" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="I1" s="22" t="str">
+      <x:c r="V1" s="118" t="str">
         <x:v>UpdatedAt</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="16" t="str">
+      <x:c r="A2" s="143" t="str">
         <x:v>ING001</x:v>
       </x:c>
-      <x:c r="B2" s="16" t="str">
+      <x:c r="B2" s="143" t="str">
         <x:v>Chicken breast</x:v>
       </x:c>
-      <x:c r="C2" s="16" t="str">
+      <x:c r="C2" s="143" t="str"/>
+      <x:c r="D2" s="143" t="str">
+        <x:v>cooked</x:v>
+      </x:c>
+      <x:c r="E2" s="143" t="str">
         <x:v>100 g cooked</x:v>
       </x:c>
-      <x:c r="D2" s="16" t="n">
+      <x:c r="F2" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G2" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H2" s="161" t="str"/>
+      <x:c r="I2" s="161" t="n">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="E2" s="16" t="n">
+      <x:c r="J2" s="161" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F2" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="16" t="n">
+      <x:c r="K2" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L2" s="161" t="n">
         <x:v>3.6</x:v>
       </x:c>
-      <x:c r="H2" s="16" t="str">
+      <x:c r="M2" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N2" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O2" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P2" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q2" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R2" s="143" t="str"/>
+      <x:c r="S2" s="143" t="str"/>
+      <x:c r="T2" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U2" s="143" t="str">
         <x:v>Example only; replace with your package/cooked-weight values.</x:v>
       </x:c>
-      <x:c r="I2" s="16" t="n">
+      <x:c r="V2" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="143" t="str">
         <x:v>ING002</x:v>
       </x:c>
-      <x:c r="B3" s="16" t="str">
+      <x:c r="B3" s="143" t="str">
         <x:v>0% Greek yoghurt</x:v>
       </x:c>
-      <x:c r="C3" s="16" t="str">
+      <x:c r="C3" s="143" t="str"/>
+      <x:c r="D3" s="143" t="str"/>
+      <x:c r="E3" s="143" t="str">
         <x:v>100 g</x:v>
       </x:c>
-      <x:c r="D3" s="16" t="n">
+      <x:c r="F3" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G3" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H3" s="161" t="str"/>
+      <x:c r="I3" s="161" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E3" s="16" t="n">
+      <x:c r="J3" s="161" t="n">
         <x:v>10.3</x:v>
       </x:c>
-      <x:c r="F3" s="16" t="n">
+      <x:c r="K3" s="161" t="n">
         <x:v>3.6</x:v>
       </x:c>
-      <x:c r="G3" s="16" t="n">
+      <x:c r="L3" s="161" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="H3" s="16" t="str">
+      <x:c r="M3" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N3" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O3" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P3" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q3" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R3" s="143" t="str"/>
+      <x:c r="S3" s="143" t="str"/>
+      <x:c r="T3" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U3" s="143" t="str">
         <x:v>Example only; brands vary.</x:v>
       </x:c>
-      <x:c r="I3" s="16" t="n">
+      <x:c r="V3" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="143" t="str">
         <x:v>ING003</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B4" s="143" t="str">
         <x:v>Whey protein</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="str">
+      <x:c r="C4" s="143" t="str"/>
+      <x:c r="D4" s="143" t="str"/>
+      <x:c r="E4" s="143" t="str">
         <x:v>30 g scoop</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="n">
+      <x:c r="F4" s="161" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G4" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H4" s="161" t="str"/>
+      <x:c r="I4" s="161" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="n">
+      <x:c r="J4" s="161" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="n">
+      <x:c r="K4" s="161" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G4" s="16" t="n">
+      <x:c r="L4" s="161" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H4" s="16" t="str">
+      <x:c r="M4" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N4" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O4" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P4" s="143" t="str">
+        <x:v>{"scoop": 30.0}</x:v>
+      </x:c>
+      <x:c r="Q4" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R4" s="143" t="str"/>
+      <x:c r="S4" s="143" t="str"/>
+      <x:c r="T4" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U4" s="143" t="str">
         <x:v>Use the exact label values.</x:v>
       </x:c>
-      <x:c r="I4" s="16" t="n">
+      <x:c r="V4" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" s="143" t="str">
         <x:v>ING004</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B5" s="143" t="str">
         <x:v>Egg whites</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="C5" s="143" t="str"/>
+      <x:c r="D5" s="143" t="str"/>
+      <x:c r="E5" s="143" t="str">
         <x:v>100 g</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="n">
+      <x:c r="F5" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G5" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H5" s="161" t="str"/>
+      <x:c r="I5" s="161" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="n">
+      <x:c r="J5" s="161" t="n">
         <x:v>10.9</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="n">
+      <x:c r="K5" s="161" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="G5" s="16" t="n">
+      <x:c r="L5" s="161" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="H5" s="16" t="str">
+      <x:c r="M5" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O5" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P5" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q5" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R5" s="143" t="str"/>
+      <x:c r="S5" s="143" t="str"/>
+      <x:c r="T5" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U5" s="143" t="str">
         <x:v>Example only.</x:v>
       </x:c>
-      <x:c r="I5" s="16" t="n">
+      <x:c r="V5" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="16" t="str">
+      <x:c r="A6" s="143" t="str">
         <x:v>ING005</x:v>
       </x:c>
-      <x:c r="B6" s="16" t="str">
+      <x:c r="B6" s="143" t="str">
         <x:v>Cooked white rice</x:v>
       </x:c>
-      <x:c r="C6" s="16" t="str">
+      <x:c r="C6" s="143" t="str"/>
+      <x:c r="D6" s="143" t="str"/>
+      <x:c r="E6" s="143" t="str">
         <x:v>100 g</x:v>
       </x:c>
-      <x:c r="D6" s="16" t="n">
+      <x:c r="F6" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G6" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H6" s="161" t="str"/>
+      <x:c r="I6" s="161" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="n">
+      <x:c r="J6" s="161" t="n">
         <x:v>2.4</x:v>
       </x:c>
-      <x:c r="F6" s="16" t="n">
+      <x:c r="K6" s="161" t="n">
         <x:v>28.2</x:v>
       </x:c>
-      <x:c r="G6" s="16" t="n">
+      <x:c r="L6" s="161" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="H6" s="16" t="str">
+      <x:c r="M6" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N6" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P6" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q6" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R6" s="143" t="str"/>
+      <x:c r="S6" s="143" t="str"/>
+      <x:c r="T6" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U6" s="143" t="str">
         <x:v>Cooked weight; example only.</x:v>
       </x:c>
-      <x:c r="I6" s="16" t="n">
+      <x:c r="V6" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="16" t="str">
+      <x:c r="A7" s="143" t="str">
         <x:v>ING006</x:v>
       </x:c>
-      <x:c r="B7" s="16" t="str">
+      <x:c r="B7" s="143" t="str">
         <x:v>Boiled potato</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="str">
+      <x:c r="C7" s="143" t="str"/>
+      <x:c r="D7" s="143" t="str"/>
+      <x:c r="E7" s="143" t="str">
         <x:v>100 g</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="n">
+      <x:c r="F7" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G7" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H7" s="161" t="str"/>
+      <x:c r="I7" s="161" t="n">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="n">
+      <x:c r="J7" s="161" t="n">
         <x:v>1.9</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="n">
+      <x:c r="K7" s="161" t="n">
         <x:v>20.1</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="n">
+      <x:c r="L7" s="161" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="H7" s="16" t="str">
+      <x:c r="M7" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P7" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q7" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R7" s="143" t="str"/>
+      <x:c r="S7" s="143" t="str"/>
+      <x:c r="T7" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U7" s="143" t="str">
         <x:v>Example only.</x:v>
       </x:c>
-      <x:c r="I7" s="16" t="n">
+      <x:c r="V7" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="16" t="str">
+      <x:c r="A8" s="143" t="str">
         <x:v>ING007</x:v>
       </x:c>
-      <x:c r="B8" s="16" t="str">
+      <x:c r="B8" s="143" t="str">
         <x:v>Tuna in water, drained</x:v>
       </x:c>
-      <x:c r="C8" s="16" t="str">
+      <x:c r="C8" s="143" t="str"/>
+      <x:c r="D8" s="143" t="str"/>
+      <x:c r="E8" s="143" t="str">
         <x:v>100 g</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="n">
+      <x:c r="F8" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G8" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H8" s="161" t="str"/>
+      <x:c r="I8" s="161" t="n">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="E8" s="16" t="n">
+      <x:c r="J8" s="161" t="n">
         <x:v>25.5</x:v>
       </x:c>
-      <x:c r="F8" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="16" t="n">
+      <x:c r="K8" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L8" s="161" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="H8" s="16" t="str">
+      <x:c r="M8" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P8" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q8" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R8" s="143" t="str"/>
+      <x:c r="S8" s="143" t="str"/>
+      <x:c r="T8" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U8" s="143" t="str">
         <x:v>Check the can label.</x:v>
       </x:c>
-      <x:c r="I8" s="16" t="n">
+      <x:c r="V8" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="16" t="str">
+      <x:c r="A9" s="143" t="str">
         <x:v>ING008</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
+      <x:c r="B9" s="143" t="str">
         <x:v>Low-fat cottage cheese</x:v>
       </x:c>
-      <x:c r="C9" s="16" t="str">
+      <x:c r="C9" s="143" t="str"/>
+      <x:c r="D9" s="143" t="str"/>
+      <x:c r="E9" s="143" t="str">
         <x:v>100 g</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="n">
+      <x:c r="F9" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G9" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H9" s="161" t="str"/>
+      <x:c r="I9" s="161" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E9" s="16" t="n">
+      <x:c r="J9" s="161" t="n">
         <x:v>11.1</x:v>
       </x:c>
-      <x:c r="F9" s="16" t="n">
+      <x:c r="K9" s="161" t="n">
         <x:v>3.4</x:v>
       </x:c>
-      <x:c r="G9" s="16" t="n">
+      <x:c r="L9" s="161" t="n">
         <x:v>2.3</x:v>
       </x:c>
-      <x:c r="H9" s="16" t="str">
+      <x:c r="M9" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P9" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q9" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R9" s="143" t="str"/>
+      <x:c r="S9" s="143" t="str"/>
+      <x:c r="T9" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U9" s="143" t="str">
         <x:v>Brands vary.</x:v>
       </x:c>
-      <x:c r="I9" s="16" t="n">
+      <x:c r="V9" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="16" t="str">
+      <x:c r="A10" s="143" t="str">
         <x:v>ING009</x:v>
       </x:c>
-      <x:c r="B10" s="16" t="str">
+      <x:c r="B10" s="143" t="str">
         <x:v>Lean turkey mince</x:v>
       </x:c>
-      <x:c r="C10" s="16" t="str">
+      <x:c r="C10" s="143" t="str"/>
+      <x:c r="D10" s="143" t="str"/>
+      <x:c r="E10" s="143" t="str">
         <x:v>100 g</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="n">
+      <x:c r="F10" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G10" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H10" s="161" t="str"/>
+      <x:c r="I10" s="161" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="n">
+      <x:c r="J10" s="161" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F10" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="n">
+      <x:c r="K10" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="161" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H10" s="16" t="str">
+      <x:c r="M10" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P10" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q10" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R10" s="143" t="str"/>
+      <x:c r="S10" s="143" t="str"/>
+      <x:c r="T10" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U10" s="143" t="str">
         <x:v>Use your package values.</x:v>
       </x:c>
-      <x:c r="I10" s="16" t="n">
+      <x:c r="V10" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="16" t="str">
+      <x:c r="A11" s="143" t="str">
         <x:v>ING010</x:v>
       </x:c>
-      <x:c r="B11" s="16" t="str">
+      <x:c r="B11" s="143" t="str">
         <x:v>Courgette</x:v>
       </x:c>
-      <x:c r="C11" s="16" t="str">
+      <x:c r="C11" s="143" t="str"/>
+      <x:c r="D11" s="143" t="str"/>
+      <x:c r="E11" s="143" t="str">
         <x:v>100 g</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="n">
+      <x:c r="F11" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G11" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H11" s="161" t="str"/>
+      <x:c r="I11" s="161" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="n">
+      <x:c r="J11" s="161" t="n">
         <x:v>1.2</x:v>
       </x:c>
-      <x:c r="F11" s="16" t="n">
+      <x:c r="K11" s="161" t="n">
         <x:v>3.1</x:v>
       </x:c>
-      <x:c r="G11" s="16" t="n">
+      <x:c r="L11" s="161" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="H11" s="16" t="str">
+      <x:c r="M11" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P11" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q11" s="143" t="str">
+        <x:v>Example cache – verify</x:v>
+      </x:c>
+      <x:c r="R11" s="143" t="str"/>
+      <x:c r="S11" s="143" t="str"/>
+      <x:c r="T11" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U11" s="143" t="str">
         <x:v>Example only.</x:v>
       </x:c>
-      <x:c r="I11" s="16" t="n">
+      <x:c r="V11" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="143" t="str">
+        <x:v>ING011</x:v>
+      </x:c>
+      <x:c r="B12" s="143" t="str">
+        <x:v>Chicken breast, raw</x:v>
+      </x:c>
+      <x:c r="C12" s="143" t="str"/>
+      <x:c r="D12" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E12" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F12" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G12" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H12" s="161" t="str"/>
+      <x:c r="I12" s="161" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J12" s="161" t="n">
+        <x:v>22.5</x:v>
+      </x:c>
+      <x:c r="K12" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="161" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="M12" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="161" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O12" s="143" t="str">
+        <x:v>["raw chicken breast", "chicken fillet"]</x:v>
+      </x:c>
+      <x:c r="P12" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q12" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R12" s="143" t="str"/>
+      <x:c r="S12" s="143" t="str"/>
+      <x:c r="T12" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U12" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V12" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="143" t="str">
+        <x:v>ING012</x:v>
+      </x:c>
+      <x:c r="B13" s="143" t="str">
+        <x:v>Olive oil</x:v>
+      </x:c>
+      <x:c r="C13" s="143" t="str"/>
+      <x:c r="D13" s="143" t="str"/>
+      <x:c r="E13" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F13" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G13" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H13" s="161" t="str"/>
+      <x:c r="I13" s="161" t="n">
+        <x:v>884</x:v>
+      </x:c>
+      <x:c r="J13" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="M13" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="143" t="str">
+        <x:v>["extra virgin olive oil", "evoo"]</x:v>
+      </x:c>
+      <x:c r="P13" s="143" t="str">
+        <x:v>{"tbsp": 13.5, "tsp": 4.5}</x:v>
+      </x:c>
+      <x:c r="Q13" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R13" s="143" t="str"/>
+      <x:c r="S13" s="143" t="str"/>
+      <x:c r="T13" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U13" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V13" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="143" t="str">
+        <x:v>ING013</x:v>
+      </x:c>
+      <x:c r="B14" s="143" t="str">
+        <x:v>Onion, raw</x:v>
+      </x:c>
+      <x:c r="C14" s="143" t="str"/>
+      <x:c r="D14" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E14" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F14" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G14" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H14" s="161" t="str"/>
+      <x:c r="I14" s="161" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J14" s="161" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K14" s="161" t="n">
+        <x:v>9.3</x:v>
+      </x:c>
+      <x:c r="L14" s="161" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="M14" s="161" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="N14" s="161" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O14" s="143" t="str">
+        <x:v>["onion", "yellow onion", "white onion", "red onion"]</x:v>
+      </x:c>
+      <x:c r="P14" s="143" t="str">
+        <x:v>{"each": 150, "medium": 150, "small": 90, "large": 220}</x:v>
+      </x:c>
+      <x:c r="Q14" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R14" s="143" t="str"/>
+      <x:c r="S14" s="143" t="str"/>
+      <x:c r="T14" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U14" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V14" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="143" t="str">
+        <x:v>ING014</x:v>
+      </x:c>
+      <x:c r="B15" s="143" t="str">
+        <x:v>Garlic, raw</x:v>
+      </x:c>
+      <x:c r="C15" s="143" t="str"/>
+      <x:c r="D15" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E15" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F15" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G15" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H15" s="161" t="str"/>
+      <x:c r="I15" s="161" t="n">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="J15" s="161" t="n">
+        <x:v>6.4</x:v>
+      </x:c>
+      <x:c r="K15" s="161" t="n">
+        <x:v>33.1</x:v>
+      </x:c>
+      <x:c r="L15" s="161" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="M15" s="161" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="N15" s="161" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O15" s="143" t="str">
+        <x:v>["garlic", "garlic clove"]</x:v>
+      </x:c>
+      <x:c r="P15" s="143" t="str">
+        <x:v>{"clove": 3, "tsp": 2.8}</x:v>
+      </x:c>
+      <x:c r="Q15" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R15" s="143" t="str"/>
+      <x:c r="S15" s="143" t="str"/>
+      <x:c r="T15" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U15" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V15" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="143" t="str">
+        <x:v>ING015</x:v>
+      </x:c>
+      <x:c r="B16" s="143" t="str">
+        <x:v>Chopped tomatoes, canned</x:v>
+      </x:c>
+      <x:c r="C16" s="143" t="str"/>
+      <x:c r="D16" s="143" t="str">
+        <x:v>canned</x:v>
+      </x:c>
+      <x:c r="E16" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F16" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G16" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H16" s="161" t="str"/>
+      <x:c r="I16" s="161" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J16" s="161" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="K16" s="161" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L16" s="161" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="M16" s="161" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="N16" s="161" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="O16" s="143" t="str">
+        <x:v>["canned tomatoes", "tinned tomatoes", "chopped tomato"]</x:v>
+      </x:c>
+      <x:c r="P16" s="143" t="str">
+        <x:v>{"can": 400}</x:v>
+      </x:c>
+      <x:c r="Q16" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R16" s="143" t="str"/>
+      <x:c r="S16" s="143" t="str"/>
+      <x:c r="T16" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U16" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V16" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="143" t="str">
+        <x:v>ING016</x:v>
+      </x:c>
+      <x:c r="B17" s="143" t="str">
+        <x:v>Tomato passata</x:v>
+      </x:c>
+      <x:c r="C17" s="143" t="str"/>
+      <x:c r="D17" s="143" t="str"/>
+      <x:c r="E17" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F17" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G17" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H17" s="161" t="str"/>
+      <x:c r="I17" s="161" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J17" s="161" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="K17" s="161" t="n">
+        <x:v>4.8</x:v>
+      </x:c>
+      <x:c r="L17" s="161" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="M17" s="161" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="N17" s="161" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="O17" s="143" t="str">
+        <x:v>["passata", "tomato puree sauce"]</x:v>
+      </x:c>
+      <x:c r="P17" s="143" t="str">
+        <x:v>{"cup": 245, "tbsp": 15}</x:v>
+      </x:c>
+      <x:c r="Q17" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R17" s="143" t="str"/>
+      <x:c r="S17" s="143" t="str"/>
+      <x:c r="T17" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U17" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V17" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="143" t="str">
+        <x:v>ING017</x:v>
+      </x:c>
+      <x:c r="B18" s="143" t="str">
+        <x:v>Spinach, raw</x:v>
+      </x:c>
+      <x:c r="C18" s="143" t="str"/>
+      <x:c r="D18" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E18" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F18" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G18" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H18" s="161" t="str"/>
+      <x:c r="I18" s="161" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J18" s="161" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="K18" s="161" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="L18" s="161" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="M18" s="161" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="N18" s="161" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="O18" s="143" t="str">
+        <x:v>["spinach", "baby spinach"]</x:v>
+      </x:c>
+      <x:c r="P18" s="143" t="str">
+        <x:v>{"cup": 30}</x:v>
+      </x:c>
+      <x:c r="Q18" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R18" s="143" t="str"/>
+      <x:c r="S18" s="143" t="str"/>
+      <x:c r="T18" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U18" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V18" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="143" t="str">
+        <x:v>ING018</x:v>
+      </x:c>
+      <x:c r="B19" s="143" t="str">
+        <x:v>Broccoli, raw</x:v>
+      </x:c>
+      <x:c r="C19" s="143" t="str"/>
+      <x:c r="D19" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E19" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F19" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G19" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H19" s="161" t="str"/>
+      <x:c r="I19" s="161" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J19" s="161" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="K19" s="161" t="n">
+        <x:v>6.6</x:v>
+      </x:c>
+      <x:c r="L19" s="161" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="M19" s="161" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="N19" s="161" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O19" s="143" t="str">
+        <x:v>["broccoli", "broccoli florets"]</x:v>
+      </x:c>
+      <x:c r="P19" s="143" t="str">
+        <x:v>{"cup": 91}</x:v>
+      </x:c>
+      <x:c r="Q19" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R19" s="143" t="str"/>
+      <x:c r="S19" s="143" t="str"/>
+      <x:c r="T19" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U19" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V19" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="143" t="str">
+        <x:v>ING019</x:v>
+      </x:c>
+      <x:c r="B20" s="143" t="str">
+        <x:v>Carrot, raw</x:v>
+      </x:c>
+      <x:c r="C20" s="143" t="str"/>
+      <x:c r="D20" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E20" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F20" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G20" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H20" s="161" t="str"/>
+      <x:c r="I20" s="161" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J20" s="161" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K20" s="161" t="n">
+        <x:v>9.6</x:v>
+      </x:c>
+      <x:c r="L20" s="161" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="M20" s="161" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="N20" s="161" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="O20" s="143" t="str">
+        <x:v>["carrot", "carrots"]</x:v>
+      </x:c>
+      <x:c r="P20" s="143" t="str">
+        <x:v>{"each": 61, "medium": 61, "cup": 128}</x:v>
+      </x:c>
+      <x:c r="Q20" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R20" s="143" t="str"/>
+      <x:c r="S20" s="143" t="str"/>
+      <x:c r="T20" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U20" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V20" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="143" t="str">
+        <x:v>ING020</x:v>
+      </x:c>
+      <x:c r="B21" s="143" t="str">
+        <x:v>Mushrooms, raw</x:v>
+      </x:c>
+      <x:c r="C21" s="143" t="str"/>
+      <x:c r="D21" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E21" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F21" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G21" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H21" s="161" t="str"/>
+      <x:c r="I21" s="161" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J21" s="161" t="n">
+        <x:v>3.1</x:v>
+      </x:c>
+      <x:c r="K21" s="161" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="L21" s="161" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M21" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N21" s="161" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O21" s="143" t="str">
+        <x:v>["mushroom", "mushrooms", "button mushrooms"]</x:v>
+      </x:c>
+      <x:c r="P21" s="143" t="str">
+        <x:v>{"cup": 70}</x:v>
+      </x:c>
+      <x:c r="Q21" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R21" s="143" t="str"/>
+      <x:c r="S21" s="143" t="str"/>
+      <x:c r="T21" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U21" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V21" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="143" t="str">
+        <x:v>ING021</x:v>
+      </x:c>
+      <x:c r="B22" s="143" t="str">
+        <x:v>Rolled oats, dry</x:v>
+      </x:c>
+      <x:c r="C22" s="143" t="str"/>
+      <x:c r="D22" s="143" t="str">
+        <x:v>dry</x:v>
+      </x:c>
+      <x:c r="E22" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F22" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G22" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H22" s="161" t="str"/>
+      <x:c r="I22" s="161" t="n">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="J22" s="161" t="n">
+        <x:v>13.2</x:v>
+      </x:c>
+      <x:c r="K22" s="161" t="n">
+        <x:v>67.7</x:v>
+      </x:c>
+      <x:c r="L22" s="161" t="n">
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="M22" s="161" t="n">
+        <x:v>10.1</x:v>
+      </x:c>
+      <x:c r="N22" s="161" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O22" s="143" t="str">
+        <x:v>["oats", "rolled oats", "porridge oats"]</x:v>
+      </x:c>
+      <x:c r="P22" s="143" t="str">
+        <x:v>{"cup": 80, "tbsp": 5}</x:v>
+      </x:c>
+      <x:c r="Q22" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R22" s="143" t="str"/>
+      <x:c r="S22" s="143" t="str"/>
+      <x:c r="T22" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U22" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V22" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="143" t="str">
+        <x:v>ING022</x:v>
+      </x:c>
+      <x:c r="B23" s="143" t="str">
+        <x:v>Basmati rice, dry</x:v>
+      </x:c>
+      <x:c r="C23" s="143" t="str"/>
+      <x:c r="D23" s="143" t="str">
+        <x:v>dry</x:v>
+      </x:c>
+      <x:c r="E23" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F23" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G23" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H23" s="161" t="str"/>
+      <x:c r="I23" s="161" t="n">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="J23" s="161" t="n">
+        <x:v>8.9</x:v>
+      </x:c>
+      <x:c r="K23" s="161" t="n">
+        <x:v>78.6</x:v>
+      </x:c>
+      <x:c r="L23" s="161" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="M23" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N23" s="161" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O23" s="143" t="str">
+        <x:v>["basmati rice", "white rice dry", "uncooked rice"]</x:v>
+      </x:c>
+      <x:c r="P23" s="143" t="str">
+        <x:v>{"cup": 185}</x:v>
+      </x:c>
+      <x:c r="Q23" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R23" s="143" t="str"/>
+      <x:c r="S23" s="143" t="str"/>
+      <x:c r="T23" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U23" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V23" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="143" t="str">
+        <x:v>ING023</x:v>
+      </x:c>
+      <x:c r="B24" s="143" t="str">
+        <x:v>Pasta, dry</x:v>
+      </x:c>
+      <x:c r="C24" s="143" t="str"/>
+      <x:c r="D24" s="143" t="str">
+        <x:v>dry</x:v>
+      </x:c>
+      <x:c r="E24" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F24" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G24" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H24" s="161" t="str"/>
+      <x:c r="I24" s="161" t="n">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="J24" s="161" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K24" s="161" t="n">
+        <x:v>74.7</x:v>
+      </x:c>
+      <x:c r="L24" s="161" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="M24" s="161" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="N24" s="161" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O24" s="143" t="str">
+        <x:v>["dry pasta", "uncooked pasta", "spaghetti dry"]</x:v>
+      </x:c>
+      <x:c r="P24" s="143" t="str">
+        <x:v>{"cup": 100}</x:v>
+      </x:c>
+      <x:c r="Q24" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R24" s="143" t="str"/>
+      <x:c r="S24" s="143" t="str"/>
+      <x:c r="T24" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U24" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V24" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="143" t="str">
+        <x:v>ING024</x:v>
+      </x:c>
+      <x:c r="B25" s="143" t="str">
+        <x:v>Pasta, cooked</x:v>
+      </x:c>
+      <x:c r="C25" s="143" t="str"/>
+      <x:c r="D25" s="143" t="str">
+        <x:v>cooked</x:v>
+      </x:c>
+      <x:c r="E25" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F25" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G25" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H25" s="161" t="str"/>
+      <x:c r="I25" s="161" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J25" s="161" t="n">
+        <x:v>5.8</x:v>
+      </x:c>
+      <x:c r="K25" s="161" t="n">
+        <x:v>30.9</x:v>
+      </x:c>
+      <x:c r="L25" s="161" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="M25" s="161" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="N25" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O25" s="143" t="str">
+        <x:v>["cooked pasta", "boiled pasta"]</x:v>
+      </x:c>
+      <x:c r="P25" s="143" t="str">
+        <x:v>{"cup": 140}</x:v>
+      </x:c>
+      <x:c r="Q25" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R25" s="143" t="str"/>
+      <x:c r="S25" s="143" t="str"/>
+      <x:c r="T25" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U25" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V25" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="143" t="str">
+        <x:v>ING025</x:v>
+      </x:c>
+      <x:c r="B26" s="143" t="str">
+        <x:v>Lean beef mince, 5% fat</x:v>
+      </x:c>
+      <x:c r="C26" s="143" t="str"/>
+      <x:c r="D26" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E26" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F26" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G26" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H26" s="161" t="str"/>
+      <x:c r="I26" s="161" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="J26" s="161" t="n">
+        <x:v>21.4</x:v>
+      </x:c>
+      <x:c r="K26" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="161" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M26" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="161" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="O26" s="143" t="str">
+        <x:v>["lean beef mince", "ground beef 5%", "minced beef"]</x:v>
+      </x:c>
+      <x:c r="P26" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q26" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R26" s="143" t="str"/>
+      <x:c r="S26" s="143" t="str"/>
+      <x:c r="T26" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U26" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V26" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="143" t="str">
+        <x:v>ING026</x:v>
+      </x:c>
+      <x:c r="B27" s="143" t="str">
+        <x:v>Salmon fillet, raw</x:v>
+      </x:c>
+      <x:c r="C27" s="143" t="str"/>
+      <x:c r="D27" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E27" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F27" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G27" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H27" s="161" t="str"/>
+      <x:c r="I27" s="161" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="J27" s="161" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K27" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="161" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M27" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="161" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O27" s="143" t="str">
+        <x:v>["salmon", "salmon fillet"]</x:v>
+      </x:c>
+      <x:c r="P27" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="Q27" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R27" s="143" t="str"/>
+      <x:c r="S27" s="143" t="str"/>
+      <x:c r="T27" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U27" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V27" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="143" t="str">
+        <x:v>ING027</x:v>
+      </x:c>
+      <x:c r="B28" s="143" t="str">
+        <x:v>Whole egg, raw</x:v>
+      </x:c>
+      <x:c r="C28" s="143" t="str"/>
+      <x:c r="D28" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E28" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F28" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G28" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H28" s="161" t="str"/>
+      <x:c r="I28" s="161" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="J28" s="161" t="n">
+        <x:v>12.6</x:v>
+      </x:c>
+      <x:c r="K28" s="161" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="L28" s="161" t="n">
+        <x:v>9.5</x:v>
+      </x:c>
+      <x:c r="M28" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" s="161" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="O28" s="143" t="str">
+        <x:v>["egg", "eggs", "whole egg"]</x:v>
+      </x:c>
+      <x:c r="P28" s="143" t="str">
+        <x:v>{"each": 50, "large": 50, "medium": 44}</x:v>
+      </x:c>
+      <x:c r="Q28" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R28" s="143" t="str"/>
+      <x:c r="S28" s="143" t="str"/>
+      <x:c r="T28" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U28" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V28" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="143" t="str">
+        <x:v>ING028</x:v>
+      </x:c>
+      <x:c r="B29" s="143" t="str">
+        <x:v>Skimmed milk</x:v>
+      </x:c>
+      <x:c r="C29" s="143" t="str"/>
+      <x:c r="D29" s="143" t="str"/>
+      <x:c r="E29" s="143" t="str">
+        <x:v>100 ml</x:v>
+      </x:c>
+      <x:c r="F29" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G29" s="161" t="str">
+        <x:v>ml</x:v>
+      </x:c>
+      <x:c r="H29" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I29" s="161" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J29" s="161" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="K29" s="161" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L29" s="161" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="M29" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="161" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O29" s="143" t="str">
+        <x:v>["skim milk", "skimmed milk", "fat free milk"]</x:v>
+      </x:c>
+      <x:c r="P29" s="143" t="str">
+        <x:v>{"cup": 244, "tbsp": 15}</x:v>
+      </x:c>
+      <x:c r="Q29" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R29" s="143" t="str"/>
+      <x:c r="S29" s="143" t="str"/>
+      <x:c r="T29" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U29" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V29" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="143" t="str">
+        <x:v>ING029</x:v>
+      </x:c>
+      <x:c r="B30" s="143" t="str">
+        <x:v>Cheddar cheese</x:v>
+      </x:c>
+      <x:c r="C30" s="143" t="str"/>
+      <x:c r="D30" s="143" t="str"/>
+      <x:c r="E30" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F30" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G30" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H30" s="161" t="str"/>
+      <x:c r="I30" s="161" t="n">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="J30" s="161" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K30" s="161" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="L30" s="161" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="M30" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N30" s="161" t="n">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="O30" s="143" t="str">
+        <x:v>["cheddar", "cheese"]</x:v>
+      </x:c>
+      <x:c r="P30" s="143" t="str">
+        <x:v>{"cup": 113, "slice": 28}</x:v>
+      </x:c>
+      <x:c r="Q30" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R30" s="143" t="str"/>
+      <x:c r="S30" s="143" t="str"/>
+      <x:c r="T30" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U30" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V30" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="143" t="str">
+        <x:v>ING030</x:v>
+      </x:c>
+      <x:c r="B31" s="143" t="str">
+        <x:v>Lentils, cooked</x:v>
+      </x:c>
+      <x:c r="C31" s="143" t="str"/>
+      <x:c r="D31" s="143" t="str">
+        <x:v>cooked</x:v>
+      </x:c>
+      <x:c r="E31" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F31" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G31" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H31" s="161" t="str"/>
+      <x:c r="I31" s="161" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="J31" s="161" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K31" s="161" t="n">
+        <x:v>20.1</x:v>
+      </x:c>
+      <x:c r="L31" s="161" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="M31" s="161" t="n">
+        <x:v>7.9</x:v>
+      </x:c>
+      <x:c r="N31" s="161" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O31" s="143" t="str">
+        <x:v>["lentils", "cooked lentils"]</x:v>
+      </x:c>
+      <x:c r="P31" s="143" t="str">
+        <x:v>{"cup": 198}</x:v>
+      </x:c>
+      <x:c r="Q31" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R31" s="143" t="str"/>
+      <x:c r="S31" s="143" t="str"/>
+      <x:c r="T31" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U31" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V31" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="143" t="str">
+        <x:v>ING031</x:v>
+      </x:c>
+      <x:c r="B32" s="143" t="str">
+        <x:v>Chickpeas, drained</x:v>
+      </x:c>
+      <x:c r="C32" s="143" t="str"/>
+      <x:c r="D32" s="143" t="str">
+        <x:v>drained</x:v>
+      </x:c>
+      <x:c r="E32" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F32" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G32" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H32" s="161" t="str"/>
+      <x:c r="I32" s="161" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="J32" s="161" t="n">
+        <x:v>7.2</x:v>
+      </x:c>
+      <x:c r="K32" s="161" t="n">
+        <x:v>19.1</x:v>
+      </x:c>
+      <x:c r="L32" s="161" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="M32" s="161" t="n">
+        <x:v>5.1</x:v>
+      </x:c>
+      <x:c r="N32" s="161" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="O32" s="143" t="str">
+        <x:v>["chickpeas", "garbanzo beans"]</x:v>
+      </x:c>
+      <x:c r="P32" s="143" t="str">
+        <x:v>{"cup": 164, "can": 240}</x:v>
+      </x:c>
+      <x:c r="Q32" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R32" s="143" t="str"/>
+      <x:c r="S32" s="143" t="str"/>
+      <x:c r="T32" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U32" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V32" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="143" t="str">
+        <x:v>ING032</x:v>
+      </x:c>
+      <x:c r="B33" s="143" t="str">
+        <x:v>Kidney beans, drained</x:v>
+      </x:c>
+      <x:c r="C33" s="143" t="str"/>
+      <x:c r="D33" s="143" t="str">
+        <x:v>drained</x:v>
+      </x:c>
+      <x:c r="E33" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F33" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G33" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H33" s="161" t="str"/>
+      <x:c r="I33" s="161" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="J33" s="161" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="K33" s="161" t="n">
+        <x:v>14.5</x:v>
+      </x:c>
+      <x:c r="L33" s="161" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="M33" s="161" t="n">
+        <x:v>6.4</x:v>
+      </x:c>
+      <x:c r="N33" s="161" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="O33" s="143" t="str">
+        <x:v>["kidney beans", "red kidney beans"]</x:v>
+      </x:c>
+      <x:c r="P33" s="143" t="str">
+        <x:v>{"cup": 177, "can": 240}</x:v>
+      </x:c>
+      <x:c r="Q33" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R33" s="143" t="str"/>
+      <x:c r="S33" s="143" t="str"/>
+      <x:c r="T33" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U33" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V33" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="143" t="str">
+        <x:v>ING033</x:v>
+      </x:c>
+      <x:c r="B34" s="143" t="str">
+        <x:v>Banana, raw</x:v>
+      </x:c>
+      <x:c r="C34" s="143" t="str"/>
+      <x:c r="D34" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E34" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F34" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G34" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H34" s="161" t="str"/>
+      <x:c r="I34" s="161" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="J34" s="161" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="K34" s="161" t="n">
+        <x:v>22.8</x:v>
+      </x:c>
+      <x:c r="L34" s="161" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M34" s="161" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="N34" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O34" s="143" t="str">
+        <x:v>["banana"]</x:v>
+      </x:c>
+      <x:c r="P34" s="143" t="str">
+        <x:v>{"each": 118, "medium": 118, "small": 101, "large": 136}</x:v>
+      </x:c>
+      <x:c r="Q34" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R34" s="143" t="str"/>
+      <x:c r="S34" s="143" t="str"/>
+      <x:c r="T34" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U34" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V34" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="143" t="str">
+        <x:v>ING034</x:v>
+      </x:c>
+      <x:c r="B35" s="143" t="str">
+        <x:v>Apple, raw</x:v>
+      </x:c>
+      <x:c r="C35" s="143" t="str"/>
+      <x:c r="D35" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E35" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F35" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G35" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H35" s="161" t="str"/>
+      <x:c r="I35" s="161" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J35" s="161" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K35" s="161" t="n">
+        <x:v>13.8</x:v>
+      </x:c>
+      <x:c r="L35" s="161" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="M35" s="161" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="N35" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O35" s="143" t="str">
+        <x:v>["apple"]</x:v>
+      </x:c>
+      <x:c r="P35" s="143" t="str">
+        <x:v>{"each": 182, "medium": 182, "small": 149, "large": 223}</x:v>
+      </x:c>
+      <x:c r="Q35" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R35" s="143" t="str"/>
+      <x:c r="S35" s="143" t="str"/>
+      <x:c r="T35" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U35" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V35" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="143" t="str">
+        <x:v>ING035</x:v>
+      </x:c>
+      <x:c r="B36" s="143" t="str">
+        <x:v>Blueberries, raw</x:v>
+      </x:c>
+      <x:c r="C36" s="143" t="str"/>
+      <x:c r="D36" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E36" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F36" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G36" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H36" s="161" t="str"/>
+      <x:c r="I36" s="161" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J36" s="161" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="K36" s="161" t="n">
+        <x:v>14.5</x:v>
+      </x:c>
+      <x:c r="L36" s="161" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M36" s="161" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="N36" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O36" s="143" t="str">
+        <x:v>["blueberries", "blueberry"]</x:v>
+      </x:c>
+      <x:c r="P36" s="143" t="str">
+        <x:v>{"cup": 148}</x:v>
+      </x:c>
+      <x:c r="Q36" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R36" s="143" t="str"/>
+      <x:c r="S36" s="143" t="str"/>
+      <x:c r="T36" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U36" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V36" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="143" t="str">
+        <x:v>ING036</x:v>
+      </x:c>
+      <x:c r="B37" s="143" t="str">
+        <x:v>Honey</x:v>
+      </x:c>
+      <x:c r="C37" s="143" t="str"/>
+      <x:c r="D37" s="143" t="str"/>
+      <x:c r="E37" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F37" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G37" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H37" s="161" t="str"/>
+      <x:c r="I37" s="161" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="J37" s="161" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K37" s="161" t="n">
+        <x:v>82.4</x:v>
+      </x:c>
+      <x:c r="L37" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="161" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="N37" s="161" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O37" s="143" t="str">
+        <x:v>["honey"]</x:v>
+      </x:c>
+      <x:c r="P37" s="143" t="str">
+        <x:v>{"tbsp": 21, "tsp": 7}</x:v>
+      </x:c>
+      <x:c r="Q37" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R37" s="143" t="str"/>
+      <x:c r="S37" s="143" t="str"/>
+      <x:c r="T37" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U37" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V37" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="143" t="str">
+        <x:v>ING037</x:v>
+      </x:c>
+      <x:c r="B38" s="143" t="str">
+        <x:v>Plain wheat flour</x:v>
+      </x:c>
+      <x:c r="C38" s="143" t="str"/>
+      <x:c r="D38" s="143" t="str">
+        <x:v>dry</x:v>
+      </x:c>
+      <x:c r="E38" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F38" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G38" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H38" s="161" t="str"/>
+      <x:c r="I38" s="161" t="n">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="J38" s="161" t="n">
+        <x:v>10.3</x:v>
+      </x:c>
+      <x:c r="K38" s="161" t="n">
+        <x:v>76.3</x:v>
+      </x:c>
+      <x:c r="L38" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M38" s="161" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="N38" s="161" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O38" s="143" t="str">
+        <x:v>["flour", "plain flour", "all purpose flour"]</x:v>
+      </x:c>
+      <x:c r="P38" s="143" t="str">
+        <x:v>{"cup": 125, "tbsp": 8}</x:v>
+      </x:c>
+      <x:c r="Q38" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R38" s="143" t="str"/>
+      <x:c r="S38" s="143" t="str"/>
+      <x:c r="T38" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U38" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V38" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="143" t="str">
+        <x:v>ING038</x:v>
+      </x:c>
+      <x:c r="B39" s="143" t="str">
+        <x:v>Butter</x:v>
+      </x:c>
+      <x:c r="C39" s="143" t="str"/>
+      <x:c r="D39" s="143" t="str"/>
+      <x:c r="E39" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F39" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G39" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H39" s="161" t="str"/>
+      <x:c r="I39" s="161" t="n">
+        <x:v>717</x:v>
+      </x:c>
+      <x:c r="J39" s="161" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K39" s="161" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L39" s="161" t="n">
+        <x:v>81.1</x:v>
+      </x:c>
+      <x:c r="M39" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" s="161" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="O39" s="143" t="str">
+        <x:v>["butter", "unsalted butter", "salted butter"]</x:v>
+      </x:c>
+      <x:c r="P39" s="143" t="str">
+        <x:v>{"tbsp": 14, "tsp": 4.7}</x:v>
+      </x:c>
+      <x:c r="Q39" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R39" s="143" t="str"/>
+      <x:c r="S39" s="143" t="str"/>
+      <x:c r="T39" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U39" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V39" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="143" t="str">
+        <x:v>ING039</x:v>
+      </x:c>
+      <x:c r="B40" s="143" t="str">
+        <x:v>Granulated sugar</x:v>
+      </x:c>
+      <x:c r="C40" s="143" t="str"/>
+      <x:c r="D40" s="143" t="str">
+        <x:v>dry</x:v>
+      </x:c>
+      <x:c r="E40" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F40" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G40" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H40" s="161" t="str"/>
+      <x:c r="I40" s="161" t="n">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="J40" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L40" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O40" s="143" t="str">
+        <x:v>["sugar", "white sugar", "caster sugar"]</x:v>
+      </x:c>
+      <x:c r="P40" s="143" t="str">
+        <x:v>{"cup": 200, "tbsp": 12.5, "tsp": 4.2}</x:v>
+      </x:c>
+      <x:c r="Q40" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R40" s="143" t="str"/>
+      <x:c r="S40" s="143" t="str"/>
+      <x:c r="T40" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U40" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V40" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="143" t="str">
+        <x:v>ING040</x:v>
+      </x:c>
+      <x:c r="B41" s="143" t="str">
+        <x:v>Soy sauce</x:v>
+      </x:c>
+      <x:c r="C41" s="143" t="str"/>
+      <x:c r="D41" s="143" t="str"/>
+      <x:c r="E41" s="143" t="str">
+        <x:v>100 ml</x:v>
+      </x:c>
+      <x:c r="F41" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G41" s="161" t="str">
+        <x:v>ml</x:v>
+      </x:c>
+      <x:c r="H41" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I41" s="161" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J41" s="161" t="n">
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="K41" s="161" t="n">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="L41" s="161" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="M41" s="161" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="N41" s="161" t="n">
+        <x:v>5493</x:v>
+      </x:c>
+      <x:c r="O41" s="143" t="str">
+        <x:v>["soy sauce", "light soy sauce"]</x:v>
+      </x:c>
+      <x:c r="P41" s="143" t="str">
+        <x:v>{"tbsp": 15, "tsp": 5}</x:v>
+      </x:c>
+      <x:c r="Q41" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R41" s="143" t="str"/>
+      <x:c r="S41" s="143" t="str"/>
+      <x:c r="T41" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U41" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V41" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="143" t="str">
+        <x:v>ING041</x:v>
+      </x:c>
+      <x:c r="B42" s="143" t="str">
+        <x:v>Lemon juice</x:v>
+      </x:c>
+      <x:c r="C42" s="143" t="str"/>
+      <x:c r="D42" s="143" t="str"/>
+      <x:c r="E42" s="143" t="str">
+        <x:v>100 ml</x:v>
+      </x:c>
+      <x:c r="F42" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G42" s="161" t="str">
+        <x:v>ml</x:v>
+      </x:c>
+      <x:c r="H42" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I42" s="161" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J42" s="161" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="K42" s="161" t="n">
+        <x:v>6.9</x:v>
+      </x:c>
+      <x:c r="L42" s="161" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="M42" s="161" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="N42" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O42" s="143" t="str">
+        <x:v>["lemon juice", "juice of lemon"]</x:v>
+      </x:c>
+      <x:c r="P42" s="143" t="str">
+        <x:v>{"tbsp": 15, "tsp": 5, "lemon": 48}</x:v>
+      </x:c>
+      <x:c r="Q42" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R42" s="143" t="str"/>
+      <x:c r="S42" s="143" t="str"/>
+      <x:c r="T42" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U42" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V42" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="143" t="str">
+        <x:v>ING042</x:v>
+      </x:c>
+      <x:c r="B43" s="143" t="str">
+        <x:v>Coconut milk, canned</x:v>
+      </x:c>
+      <x:c r="C43" s="143" t="str"/>
+      <x:c r="D43" s="143" t="str">
+        <x:v>canned</x:v>
+      </x:c>
+      <x:c r="E43" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F43" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G43" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H43" s="161" t="str"/>
+      <x:c r="I43" s="161" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="J43" s="161" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K43" s="161" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="L43" s="161" t="n">
+        <x:v>21.3</x:v>
+      </x:c>
+      <x:c r="M43" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N43" s="161" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="O43" s="143" t="str">
+        <x:v>["coconut milk", "full fat coconut milk"]</x:v>
+      </x:c>
+      <x:c r="P43" s="143" t="str">
+        <x:v>{"cup": 240, "can": 400}</x:v>
+      </x:c>
+      <x:c r="Q43" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R43" s="143" t="str"/>
+      <x:c r="S43" s="143" t="str"/>
+      <x:c r="T43" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U43" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V43" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="143" t="str">
+        <x:v>ING043</x:v>
+      </x:c>
+      <x:c r="B44" s="143" t="str">
+        <x:v>White bread</x:v>
+      </x:c>
+      <x:c r="C44" s="143" t="str"/>
+      <x:c r="D44" s="143" t="str"/>
+      <x:c r="E44" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F44" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G44" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H44" s="161" t="str"/>
+      <x:c r="I44" s="161" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="J44" s="161" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K44" s="161" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L44" s="161" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="M44" s="161" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="N44" s="161" t="n">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="O44" s="143" t="str">
+        <x:v>["bread", "white bread"]</x:v>
+      </x:c>
+      <x:c r="P44" s="143" t="str">
+        <x:v>{"slice": 36}</x:v>
+      </x:c>
+      <x:c r="Q44" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R44" s="143" t="str"/>
+      <x:c r="S44" s="143" t="str"/>
+      <x:c r="T44" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U44" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V44" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="143" t="str">
+        <x:v>ING044</x:v>
+      </x:c>
+      <x:c r="B45" s="143" t="str">
+        <x:v>Sweet potato, raw</x:v>
+      </x:c>
+      <x:c r="C45" s="143" t="str"/>
+      <x:c r="D45" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E45" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F45" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G45" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H45" s="161" t="str"/>
+      <x:c r="I45" s="161" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J45" s="161" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="K45" s="161" t="n">
+        <x:v>20.1</x:v>
+      </x:c>
+      <x:c r="L45" s="161" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="M45" s="161" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N45" s="161" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O45" s="143" t="str">
+        <x:v>["sweet potato", "sweet potatoes"]</x:v>
+      </x:c>
+      <x:c r="P45" s="143" t="str">
+        <x:v>{"each": 130, "medium": 130}</x:v>
+      </x:c>
+      <x:c r="Q45" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R45" s="143" t="str"/>
+      <x:c r="S45" s="143" t="str"/>
+      <x:c r="T45" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U45" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V45" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="143" t="str">
+        <x:v>ING045</x:v>
+      </x:c>
+      <x:c r="B46" s="143" t="str">
+        <x:v>Avocado, raw</x:v>
+      </x:c>
+      <x:c r="C46" s="143" t="str"/>
+      <x:c r="D46" s="143" t="str">
+        <x:v>raw</x:v>
+      </x:c>
+      <x:c r="E46" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F46" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G46" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H46" s="161" t="str"/>
+      <x:c r="I46" s="161" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J46" s="161" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K46" s="161" t="n">
+        <x:v>8.5</x:v>
+      </x:c>
+      <x:c r="L46" s="161" t="n">
+        <x:v>14.7</x:v>
+      </x:c>
+      <x:c r="M46" s="161" t="n">
+        <x:v>6.7</x:v>
+      </x:c>
+      <x:c r="N46" s="161" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="O46" s="143" t="str">
+        <x:v>["avocado"]</x:v>
+      </x:c>
+      <x:c r="P46" s="143" t="str">
+        <x:v>{"each": 136, "half": 68}</x:v>
+      </x:c>
+      <x:c r="Q46" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R46" s="143" t="str"/>
+      <x:c r="S46" s="143" t="str"/>
+      <x:c r="T46" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U46" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V46" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="143" t="str">
+        <x:v>ING046</x:v>
+      </x:c>
+      <x:c r="B47" s="143" t="str">
+        <x:v>Low-fat mayonnaise</x:v>
+      </x:c>
+      <x:c r="C47" s="143" t="str"/>
+      <x:c r="D47" s="143" t="str"/>
+      <x:c r="E47" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F47" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G47" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H47" s="161" t="str"/>
+      <x:c r="I47" s="161" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="J47" s="161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K47" s="161" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L47" s="161" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M47" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N47" s="161" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="O47" s="143" t="str">
+        <x:v>["light mayonnaise", "low fat mayo", "mayonnaise"]</x:v>
+      </x:c>
+      <x:c r="P47" s="143" t="str">
+        <x:v>{"tbsp": 15, "tsp": 5}</x:v>
+      </x:c>
+      <x:c r="Q47" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R47" s="143" t="str"/>
+      <x:c r="S47" s="143" t="str"/>
+      <x:c r="T47" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U47" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V47" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="143" t="str">
+        <x:v>ING047</x:v>
+      </x:c>
+      <x:c r="B48" s="143" t="str">
+        <x:v>Peanut butter</x:v>
+      </x:c>
+      <x:c r="C48" s="143" t="str"/>
+      <x:c r="D48" s="143" t="str"/>
+      <x:c r="E48" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F48" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G48" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H48" s="161" t="str"/>
+      <x:c r="I48" s="161" t="n">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="J48" s="161" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K48" s="161" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L48" s="161" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M48" s="161" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N48" s="161" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="O48" s="143" t="str">
+        <x:v>["peanut butter"]</x:v>
+      </x:c>
+      <x:c r="P48" s="143" t="str">
+        <x:v>{"tbsp": 16, "tsp": 5.3}</x:v>
+      </x:c>
+      <x:c r="Q48" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R48" s="143" t="str"/>
+      <x:c r="S48" s="143" t="str"/>
+      <x:c r="T48" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U48" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V48" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="143" t="str">
+        <x:v>ING048</x:v>
+      </x:c>
+      <x:c r="B49" s="143" t="str">
+        <x:v>Plain low-fat yoghurt</x:v>
+      </x:c>
+      <x:c r="C49" s="143" t="str"/>
+      <x:c r="D49" s="143" t="str"/>
+      <x:c r="E49" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F49" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G49" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H49" s="161" t="str"/>
+      <x:c r="I49" s="161" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J49" s="161" t="n">
+        <x:v>5.3</x:v>
+      </x:c>
+      <x:c r="K49" s="161" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L49" s="161" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="M49" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N49" s="161" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="O49" s="143" t="str">
+        <x:v>["plain yoghurt", "low fat yogurt", "natural yoghurt"]</x:v>
+      </x:c>
+      <x:c r="P49" s="143" t="str">
+        <x:v>{"cup": 245, "tbsp": 15}</x:v>
+      </x:c>
+      <x:c r="Q49" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R49" s="143" t="str"/>
+      <x:c r="S49" s="143" t="str"/>
+      <x:c r="T49" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U49" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V49" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="143" t="str">
+        <x:v>ING049</x:v>
+      </x:c>
+      <x:c r="B50" s="143" t="str">
+        <x:v>Quinoa, cooked</x:v>
+      </x:c>
+      <x:c r="C50" s="143" t="str"/>
+      <x:c r="D50" s="143" t="str">
+        <x:v>cooked</x:v>
+      </x:c>
+      <x:c r="E50" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F50" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G50" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H50" s="161" t="str"/>
+      <x:c r="I50" s="161" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J50" s="161" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="K50" s="161" t="n">
+        <x:v>21.3</x:v>
+      </x:c>
+      <x:c r="L50" s="161" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="M50" s="161" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="N50" s="161" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="O50" s="143" t="str">
+        <x:v>["quinoa", "cooked quinoa"]</x:v>
+      </x:c>
+      <x:c r="P50" s="143" t="str">
+        <x:v>{"cup": 185}</x:v>
+      </x:c>
+      <x:c r="Q50" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R50" s="143" t="str"/>
+      <x:c r="S50" s="143" t="str"/>
+      <x:c r="T50" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U50" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V50" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="143" t="str">
+        <x:v>ING050</x:v>
+      </x:c>
+      <x:c r="B51" s="143" t="str">
+        <x:v>Frozen mixed vegetables</x:v>
+      </x:c>
+      <x:c r="C51" s="143" t="str"/>
+      <x:c r="D51" s="143" t="str">
+        <x:v>frozen</x:v>
+      </x:c>
+      <x:c r="E51" s="143" t="str">
+        <x:v>100 g</x:v>
+      </x:c>
+      <x:c r="F51" s="161" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G51" s="161" t="str">
+        <x:v>g</x:v>
+      </x:c>
+      <x:c r="H51" s="161" t="str"/>
+      <x:c r="I51" s="161" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J51" s="161" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K51" s="161" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L51" s="161" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="M51" s="161" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N51" s="161" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="O51" s="143" t="str">
+        <x:v>["mixed vegetables", "frozen vegetables"]</x:v>
+      </x:c>
+      <x:c r="P51" s="143" t="str">
+        <x:v>{"cup": 150}</x:v>
+      </x:c>
+      <x:c r="Q51" s="143" t="str">
+        <x:v>Generic reference – verify</x:v>
+      </x:c>
+      <x:c r="R51" s="143" t="str"/>
+      <x:c r="S51" s="143" t="str"/>
+      <x:c r="T51" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U51" s="143" t="str">
+        <x:v>Starting reference value. Confirm against a package label or reference record before relying on it.</x:v>
+      </x:c>
+      <x:c r="V51" s="160" t="n">
+        <x:v>46222.87152777778</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="T2:T51">
+    <x:cfRule type="expression" dxfId="3" priority="1">
+      <x:formula>T2=TRUE</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -15663,449 +18810,759 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="7.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12.5" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.25" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="13.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="12.75" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="10.25" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="7.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="13.5" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="10.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="17" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="38" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="24" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="20" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="12" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="12" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="12" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="18" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="18" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="15" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="30" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="38" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="38" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="14" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="11" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="16" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="14" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="58" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="58" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="22" t="str">
+      <x:c r="A1" s="118" t="str">
         <x:v>RecipeID</x:v>
       </x:c>
-      <x:c r="B1" s="22" t="str">
+      <x:c r="B1" s="118" t="str">
         <x:v>RecipeName</x:v>
       </x:c>
-      <x:c r="C1" s="22" t="str">
+      <x:c r="C1" s="118" t="str">
         <x:v>Category</x:v>
       </x:c>
-      <x:c r="D1" s="22" t="str">
+      <x:c r="D1" s="118" t="str">
         <x:v>Servings</x:v>
       </x:c>
-      <x:c r="E1" s="22" t="str">
+      <x:c r="E1" s="118" t="str">
+        <x:v>FinishedWeight_g</x:v>
+      </x:c>
+      <x:c r="F1" s="118" t="str">
         <x:v>Total_kcal</x:v>
       </x:c>
-      <x:c r="F1" s="22" t="str">
+      <x:c r="G1" s="118" t="str">
         <x:v>Total_Protein_g</x:v>
       </x:c>
-      <x:c r="G1" s="22" t="str">
+      <x:c r="H1" s="118" t="str">
         <x:v>Total_Carbs_g</x:v>
       </x:c>
-      <x:c r="H1" s="22" t="str">
+      <x:c r="I1" s="118" t="str">
         <x:v>Total_Fat_g</x:v>
       </x:c>
-      <x:c r="I1" s="22" t="str">
+      <x:c r="J1" s="118" t="str">
+        <x:v>Total_Fibre_g</x:v>
+      </x:c>
+      <x:c r="K1" s="118" t="str">
+        <x:v>Total_Sodium_mg</x:v>
+      </x:c>
+      <x:c r="L1" s="118" t="str">
         <x:v>kcal_per_serving</x:v>
       </x:c>
-      <x:c r="J1" s="22" t="str">
+      <x:c r="M1" s="118" t="str">
         <x:v>Protein_per_serving</x:v>
       </x:c>
-      <x:c r="K1" s="22" t="str">
+      <x:c r="N1" s="118" t="str">
         <x:v>Carbs_per_serving</x:v>
       </x:c>
-      <x:c r="L1" s="22" t="str">
+      <x:c r="O1" s="118" t="str">
         <x:v>Fat_per_serving</x:v>
       </x:c>
-      <x:c r="M1" s="22" t="str">
+      <x:c r="P1" s="118" t="str">
+        <x:v>kcal_per_100g</x:v>
+      </x:c>
+      <x:c r="Q1" s="118" t="str">
+        <x:v>SourceType</x:v>
+      </x:c>
+      <x:c r="R1" s="118" t="str">
+        <x:v>SourceName</x:v>
+      </x:c>
+      <x:c r="S1" s="118" t="str">
+        <x:v>SourceURL</x:v>
+      </x:c>
+      <x:c r="T1" s="118" t="str">
+        <x:v>SourceAuthor</x:v>
+      </x:c>
+      <x:c r="U1" s="118" t="str">
+        <x:v>SourceBook</x:v>
+      </x:c>
+      <x:c r="V1" s="118" t="str">
+        <x:v>ImportedAt</x:v>
+      </x:c>
+      <x:c r="W1" s="118" t="str">
+        <x:v>PrepTime</x:v>
+      </x:c>
+      <x:c r="X1" s="118" t="str">
+        <x:v>CookTime</x:v>
+      </x:c>
+      <x:c r="Y1" s="118" t="str">
+        <x:v>TotalTime</x:v>
+      </x:c>
+      <x:c r="Z1" s="118" t="str">
+        <x:v>YieldText</x:v>
+      </x:c>
+      <x:c r="AA1" s="118" t="str">
+        <x:v>NutritionConfidence</x:v>
+      </x:c>
+      <x:c r="AB1" s="118" t="str">
+        <x:v>ImportStatus</x:v>
+      </x:c>
+      <x:c r="AC1" s="118" t="str">
+        <x:v>TagsJSON</x:v>
+      </x:c>
+      <x:c r="AD1" s="118" t="str">
+        <x:v>ImageURL</x:v>
+      </x:c>
+      <x:c r="AE1" s="118" t="str">
+        <x:v>SourceNutritionJSON</x:v>
+      </x:c>
+      <x:c r="AF1" s="118" t="str">
         <x:v>RFL_Friendly</x:v>
       </x:c>
-      <x:c r="N1" s="22" t="str">
+      <x:c r="AG1" s="118" t="str">
         <x:v>Favourite</x:v>
       </x:c>
-      <x:c r="O1" s="22" t="str">
+      <x:c r="AH1" s="118" t="str">
         <x:v>No_Bell_Peppers</x:v>
       </x:c>
-      <x:c r="P1" s="22" t="str">
+      <x:c r="AI1" s="118" t="str">
         <x:v>No_Shellfish</x:v>
       </x:c>
-      <x:c r="Q1" s="22" t="str">
+      <x:c r="AJ1" s="118" t="str">
         <x:v>Instructions</x:v>
       </x:c>
-      <x:c r="R1" s="22" t="str">
+      <x:c r="AK1" s="118" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="S1" s="22" t="str">
+      <x:c r="AL1" s="118" t="str">
         <x:v>UpdatedAt</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="16" t="str">
+      <x:c r="A2" s="143" t="str">
         <x:v>RCP001</x:v>
       </x:c>
-      <x:c r="B2" s="16" t="str">
+      <x:c r="B2" s="143" t="str">
         <x:v>Chicken courgette rice bowl</x:v>
       </x:c>
-      <x:c r="C2" s="16" t="str">
+      <x:c r="C2" s="143" t="str">
         <x:v>Normal cut</x:v>
       </x:c>
-      <x:c r="D2" s="46" t="n">
+      <x:c r="D2" s="161" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="46" t="n">
+      <x:c r="E2" s="161" t="str"/>
+      <x:c r="F2" s="161" t="n">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="F2" s="46" t="n">
+      <x:c r="G2" s="161" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G2" s="46" t="n">
+      <x:c r="H2" s="161" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H2" s="46" t="n">
+      <x:c r="I2" s="161" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="I2" s="46" t="n">
-        <x:f>IFERROR(E2/D2,"")</x:f>
+      <x:c r="J2" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L2" s="161" t="n">
+        <x:f>IFERROR(F2/D2,"")</x:f>
         <x:v>390</x:v>
       </x:c>
-      <x:c r="J2" s="46" t="n">
-        <x:f>IFERROR(F2/D2,"")</x:f>
+      <x:c r="M2" s="161" t="n">
+        <x:f>IFERROR(G2/D2,"")</x:f>
         <x:v>46</x:v>
       </x:c>
-      <x:c r="K2" s="46" t="n">
-        <x:f>IFERROR(G2/D2,"")</x:f>
+      <x:c r="N2" s="161" t="n">
+        <x:f>IFERROR(H2/D2,"")</x:f>
         <x:v>36</x:v>
       </x:c>
-      <x:c r="L2" s="46" t="n">
-        <x:f>IFERROR(H2/D2,"")</x:f>
+      <x:c r="O2" s="161" t="n">
+        <x:f>IFERROR(I2/D2,"")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="M2" s="16" t="str">
+      <x:c r="P2" s="161" t="str">
+        <x:f>IFERROR(F2/E2*100,"")</x:f>
+      </x:c>
+      <x:c r="Q2" s="143" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+      <x:c r="R2" s="143" t="str">
+        <x:v>Lift &amp; Cut starter recipe</x:v>
+      </x:c>
+      <x:c r="S2" s="143" t="str"/>
+      <x:c r="T2" s="143" t="str"/>
+      <x:c r="U2" s="143" t="str"/>
+      <x:c r="V2" s="160"/>
+      <x:c r="W2" s="143" t="str"/>
+      <x:c r="X2" s="143" t="str"/>
+      <x:c r="Y2" s="143" t="str"/>
+      <x:c r="Z2" s="143" t="str">
+        <x:v>2 servings</x:v>
+      </x:c>
+      <x:c r="AA2" s="143" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="AB2" s="143" t="str">
+        <x:v>Ready</x:v>
+      </x:c>
+      <x:c r="AC2" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="AD2" s="143" t="str"/>
+      <x:c r="AE2" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="AF2" s="143" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="N2" s="42" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O2" s="16" t="str">
+      <x:c r="AG2" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH2" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P2" s="16" t="str">
+      <x:c r="AI2" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q2" s="16" t="str"/>
-      <x:c r="R2" s="16" t="str">
+      <x:c r="AJ2" s="143" t="str"/>
+      <x:c r="AK2" s="143" t="str">
         <x:v>Example values only. No bell peppers; adjust to your ingredients.</x:v>
       </x:c>
-      <x:c r="S2" s="16" t="n">
+      <x:c r="AL2" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="143" t="str">
         <x:v>RCP002</x:v>
       </x:c>
-      <x:c r="B3" s="16" t="str">
+      <x:c r="B3" s="143" t="str">
         <x:v>Greek yoghurt whey bowl</x:v>
       </x:c>
-      <x:c r="C3" s="16" t="str">
+      <x:c r="C3" s="143" t="str">
         <x:v>High protein</x:v>
       </x:c>
-      <x:c r="D3" s="46" t="n">
+      <x:c r="D3" s="161" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="46" t="n">
+      <x:c r="E3" s="161" t="str"/>
+      <x:c r="F3" s="161" t="n">
         <x:v>410</x:v>
       </x:c>
-      <x:c r="F3" s="46" t="n">
+      <x:c r="G3" s="161" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G3" s="46" t="n">
+      <x:c r="H3" s="161" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H3" s="46" t="n">
+      <x:c r="I3" s="161" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I3" s="46" t="n">
-        <x:f>IFERROR(E3/D3,"")</x:f>
+      <x:c r="J3" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K3" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L3" s="161" t="n">
+        <x:f>IFERROR(F3/D3,"")</x:f>
         <x:v>410</x:v>
       </x:c>
-      <x:c r="J3" s="46" t="n">
-        <x:f>IFERROR(F3/D3,"")</x:f>
+      <x:c r="M3" s="161" t="n">
+        <x:f>IFERROR(G3/D3,"")</x:f>
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K3" s="46" t="n">
-        <x:f>IFERROR(G3/D3,"")</x:f>
+      <x:c r="N3" s="161" t="n">
+        <x:f>IFERROR(H3/D3,"")</x:f>
         <x:v>32</x:v>
       </x:c>
-      <x:c r="L3" s="46" t="n">
-        <x:f>IFERROR(H3/D3,"")</x:f>
+      <x:c r="O3" s="161" t="n">
+        <x:f>IFERROR(I3/D3,"")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="M3" s="16" t="str">
+      <x:c r="P3" s="161" t="str">
+        <x:f>IFERROR(F3/E3*100,"")</x:f>
+      </x:c>
+      <x:c r="Q3" s="143" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+      <x:c r="R3" s="143" t="str">
+        <x:v>Lift &amp; Cut starter recipe</x:v>
+      </x:c>
+      <x:c r="S3" s="143" t="str"/>
+      <x:c r="T3" s="143" t="str"/>
+      <x:c r="U3" s="143" t="str"/>
+      <x:c r="V3" s="160"/>
+      <x:c r="W3" s="143" t="str"/>
+      <x:c r="X3" s="143" t="str"/>
+      <x:c r="Y3" s="143" t="str"/>
+      <x:c r="Z3" s="143" t="str">
+        <x:v>1 servings</x:v>
+      </x:c>
+      <x:c r="AA3" s="143" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="AB3" s="143" t="str">
+        <x:v>Ready</x:v>
+      </x:c>
+      <x:c r="AC3" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="AD3" s="143" t="str"/>
+      <x:c r="AE3" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="AF3" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="N3" s="42" t="b">
+      <x:c r="AG3" s="144" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O3" s="16" t="str">
+      <x:c r="AH3" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P3" s="16" t="str">
+      <x:c r="AI3" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q3" s="16" t="str"/>
-      <x:c r="R3" s="16" t="str">
+      <x:c r="AJ3" s="143" t="str"/>
+      <x:c r="AK3" s="143" t="str">
         <x:v>Good quick protein option; use exact label values.</x:v>
       </x:c>
-      <x:c r="S3" s="16" t="n">
+      <x:c r="AL3" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="143" t="str">
         <x:v>RCP003</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B4" s="143" t="str">
         <x:v>Egg-white spinach omelette</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="str">
+      <x:c r="C4" s="143" t="str">
         <x:v>RFL-friendly</x:v>
       </x:c>
-      <x:c r="D4" s="46" t="n">
+      <x:c r="D4" s="161" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E4" s="46" t="n">
+      <x:c r="E4" s="161" t="str"/>
+      <x:c r="F4" s="161" t="n">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="F4" s="46" t="n">
+      <x:c r="G4" s="161" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G4" s="46" t="n">
+      <x:c r="H4" s="161" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H4" s="46" t="n">
+      <x:c r="I4" s="161" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I4" s="46" t="n">
-        <x:f>IFERROR(E4/D4,"")</x:f>
+      <x:c r="J4" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L4" s="161" t="n">
+        <x:f>IFERROR(F4/D4,"")</x:f>
         <x:v>260</x:v>
       </x:c>
-      <x:c r="J4" s="46" t="n">
-        <x:f>IFERROR(F4/D4,"")</x:f>
+      <x:c r="M4" s="161" t="n">
+        <x:f>IFERROR(G4/D4,"")</x:f>
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K4" s="46" t="n">
-        <x:f>IFERROR(G4/D4,"")</x:f>
+      <x:c r="N4" s="161" t="n">
+        <x:f>IFERROR(H4/D4,"")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="L4" s="46" t="n">
-        <x:f>IFERROR(H4/D4,"")</x:f>
+      <x:c r="O4" s="161" t="n">
+        <x:f>IFERROR(I4/D4,"")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="M4" s="16" t="str">
+      <x:c r="P4" s="161" t="str">
+        <x:f>IFERROR(F4/E4*100,"")</x:f>
+      </x:c>
+      <x:c r="Q4" s="143" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+      <x:c r="R4" s="143" t="str">
+        <x:v>Lift &amp; Cut starter recipe</x:v>
+      </x:c>
+      <x:c r="S4" s="143" t="str"/>
+      <x:c r="T4" s="143" t="str"/>
+      <x:c r="U4" s="143" t="str"/>
+      <x:c r="V4" s="160"/>
+      <x:c r="W4" s="143" t="str"/>
+      <x:c r="X4" s="143" t="str"/>
+      <x:c r="Y4" s="143" t="str"/>
+      <x:c r="Z4" s="143" t="str">
+        <x:v>1 servings</x:v>
+      </x:c>
+      <x:c r="AA4" s="143" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="AB4" s="143" t="str">
+        <x:v>Ready</x:v>
+      </x:c>
+      <x:c r="AC4" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="AD4" s="143" t="str"/>
+      <x:c r="AE4" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="AF4" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="N4" s="42" t="b">
+      <x:c r="AG4" s="144" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O4" s="16" t="str">
+      <x:c r="AH4" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P4" s="16" t="str">
+      <x:c r="AI4" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q4" s="16" t="str"/>
-      <x:c r="R4" s="16" t="str">
+      <x:c r="AJ4" s="143" t="str"/>
+      <x:c r="AK4" s="143" t="str">
         <x:v>Use herbs, spinach, mushrooms; avoid bell peppers.</x:v>
       </x:c>
-      <x:c r="S4" s="16" t="n">
+      <x:c r="AL4" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" s="143" t="str">
         <x:v>RCP004</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B5" s="143" t="str">
         <x:v>Lean turkey tomato mince</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="C5" s="143" t="str">
         <x:v>Batch cook</x:v>
       </x:c>
-      <x:c r="D5" s="46" t="n">
+      <x:c r="D5" s="161" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E5" s="46" t="n">
+      <x:c r="E5" s="161" t="str"/>
+      <x:c r="F5" s="161" t="n">
         <x:v>1280</x:v>
       </x:c>
-      <x:c r="F5" s="46" t="n">
+      <x:c r="G5" s="161" t="n">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G5" s="46" t="n">
+      <x:c r="H5" s="161" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H5" s="46" t="n">
+      <x:c r="I5" s="161" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="I5" s="46" t="n">
-        <x:f>IFERROR(E5/D5,"")</x:f>
+      <x:c r="J5" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L5" s="161" t="n">
+        <x:f>IFERROR(F5/D5,"")</x:f>
         <x:v>320</x:v>
       </x:c>
-      <x:c r="J5" s="46" t="n">
-        <x:f>IFERROR(F5/D5,"")</x:f>
+      <x:c r="M5" s="161" t="n">
+        <x:f>IFERROR(G5/D5,"")</x:f>
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K5" s="46" t="n">
-        <x:f>IFERROR(G5/D5,"")</x:f>
+      <x:c r="N5" s="161" t="n">
+        <x:f>IFERROR(H5/D5,"")</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="L5" s="46" t="n">
-        <x:f>IFERROR(H5/D5,"")</x:f>
+      <x:c r="O5" s="161" t="n">
+        <x:f>IFERROR(I5/D5,"")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="M5" s="16" t="str">
+      <x:c r="P5" s="161" t="str">
+        <x:f>IFERROR(F5/E5*100,"")</x:f>
+      </x:c>
+      <x:c r="Q5" s="143" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+      <x:c r="R5" s="143" t="str">
+        <x:v>Lift &amp; Cut starter recipe</x:v>
+      </x:c>
+      <x:c r="S5" s="143" t="str"/>
+      <x:c r="T5" s="143" t="str"/>
+      <x:c r="U5" s="143" t="str"/>
+      <x:c r="V5" s="160"/>
+      <x:c r="W5" s="143" t="str"/>
+      <x:c r="X5" s="143" t="str"/>
+      <x:c r="Y5" s="143" t="str"/>
+      <x:c r="Z5" s="143" t="str">
+        <x:v>4 servings</x:v>
+      </x:c>
+      <x:c r="AA5" s="143" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="AB5" s="143" t="str">
+        <x:v>Ready</x:v>
+      </x:c>
+      <x:c r="AC5" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="AD5" s="143" t="str"/>
+      <x:c r="AE5" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="AF5" s="143" t="str">
         <x:v>Maybe</x:v>
       </x:c>
-      <x:c r="N5" s="42" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O5" s="16" t="str">
+      <x:c r="AG5" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH5" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P5" s="16" t="str">
+      <x:c r="AI5" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q5" s="16" t="str"/>
-      <x:c r="R5" s="16" t="str">
+      <x:c r="AJ5" s="143" t="str"/>
+      <x:c r="AK5" s="143" t="str">
         <x:v>Serve with rice/potatoes outside RFL or vegetables during RFL.</x:v>
       </x:c>
-      <x:c r="S5" s="16" t="n">
+      <x:c r="AL5" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="16" t="str">
+      <x:c r="A6" s="143" t="str">
         <x:v>RCP005</x:v>
       </x:c>
-      <x:c r="B6" s="16" t="str">
+      <x:c r="B6" s="143" t="str">
         <x:v>Tuna potato salad</x:v>
       </x:c>
-      <x:c r="C6" s="16" t="str">
+      <x:c r="C6" s="143" t="str">
         <x:v>Normal cut</x:v>
       </x:c>
-      <x:c r="D6" s="46" t="n">
+      <x:c r="D6" s="161" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E6" s="46" t="n">
+      <x:c r="E6" s="161" t="str"/>
+      <x:c r="F6" s="161" t="n">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="F6" s="46" t="n">
+      <x:c r="G6" s="161" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G6" s="46" t="n">
+      <x:c r="H6" s="161" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H6" s="46" t="n">
+      <x:c r="I6" s="161" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I6" s="46" t="n">
-        <x:f>IFERROR(E6/D6,"")</x:f>
+      <x:c r="J6" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" s="161" t="n">
+        <x:f>IFERROR(F6/D6,"")</x:f>
         <x:v>325</x:v>
       </x:c>
-      <x:c r="J6" s="46" t="n">
-        <x:f>IFERROR(F6/D6,"")</x:f>
+      <x:c r="M6" s="161" t="n">
+        <x:f>IFERROR(G6/D6,"")</x:f>
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K6" s="46" t="n">
-        <x:f>IFERROR(G6/D6,"")</x:f>
+      <x:c r="N6" s="161" t="n">
+        <x:f>IFERROR(H6/D6,"")</x:f>
         <x:v>41</x:v>
       </x:c>
-      <x:c r="L6" s="46" t="n">
-        <x:f>IFERROR(H6/D6,"")</x:f>
+      <x:c r="O6" s="161" t="n">
+        <x:f>IFERROR(I6/D6,"")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="M6" s="16" t="str">
+      <x:c r="P6" s="161" t="str">
+        <x:f>IFERROR(F6/E6*100,"")</x:f>
+      </x:c>
+      <x:c r="Q6" s="143" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+      <x:c r="R6" s="143" t="str">
+        <x:v>Lift &amp; Cut starter recipe</x:v>
+      </x:c>
+      <x:c r="S6" s="143" t="str"/>
+      <x:c r="T6" s="143" t="str"/>
+      <x:c r="U6" s="143" t="str"/>
+      <x:c r="V6" s="160"/>
+      <x:c r="W6" s="143" t="str"/>
+      <x:c r="X6" s="143" t="str"/>
+      <x:c r="Y6" s="143" t="str"/>
+      <x:c r="Z6" s="143" t="str">
+        <x:v>2 servings</x:v>
+      </x:c>
+      <x:c r="AA6" s="143" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="AB6" s="143" t="str">
+        <x:v>Ready</x:v>
+      </x:c>
+      <x:c r="AC6" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="AD6" s="143" t="str"/>
+      <x:c r="AE6" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="AF6" s="143" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="N6" s="42" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O6" s="16" t="str">
+      <x:c r="AG6" s="144" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH6" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P6" s="16" t="str">
+      <x:c r="AI6" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q6" s="16" t="str"/>
-      <x:c r="R6" s="16" t="str">
+      <x:c r="AJ6" s="143" t="str"/>
+      <x:c r="AK6" s="143" t="str">
         <x:v>Tuna is not shellfish; avoid mayo-heavy versions.</x:v>
       </x:c>
-      <x:c r="S6" s="16" t="n">
+      <x:c r="AL6" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="16" t="str">
+      <x:c r="A7" s="143" t="str">
         <x:v>RCP006</x:v>
       </x:c>
-      <x:c r="B7" s="16" t="str">
+      <x:c r="B7" s="143" t="str">
         <x:v>Cottage cheese chicken salad</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="str">
+      <x:c r="C7" s="143" t="str">
         <x:v>RFL-friendly</x:v>
       </x:c>
-      <x:c r="D7" s="46" t="n">
+      <x:c r="D7" s="161" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E7" s="46" t="n">
+      <x:c r="E7" s="161" t="str"/>
+      <x:c r="F7" s="161" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="F7" s="46" t="n">
+      <x:c r="G7" s="161" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G7" s="46" t="n">
+      <x:c r="H7" s="161" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H7" s="46" t="n">
+      <x:c r="I7" s="161" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="46" t="n">
-        <x:f>IFERROR(E7/D7,"")</x:f>
+      <x:c r="J7" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="161" t="n">
+        <x:f>IFERROR(F7/D7,"")</x:f>
         <x:v>360</x:v>
       </x:c>
-      <x:c r="J7" s="46" t="n">
-        <x:f>IFERROR(F7/D7,"")</x:f>
+      <x:c r="M7" s="161" t="n">
+        <x:f>IFERROR(G7/D7,"")</x:f>
         <x:v>60</x:v>
       </x:c>
-      <x:c r="K7" s="46" t="n">
-        <x:f>IFERROR(G7/D7,"")</x:f>
+      <x:c r="N7" s="161" t="n">
+        <x:f>IFERROR(H7/D7,"")</x:f>
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L7" s="46" t="n">
-        <x:f>IFERROR(H7/D7,"")</x:f>
+      <x:c r="O7" s="161" t="n">
+        <x:f>IFERROR(I7/D7,"")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="M7" s="16" t="str">
+      <x:c r="P7" s="161" t="str">
+        <x:f>IFERROR(F7/E7*100,"")</x:f>
+      </x:c>
+      <x:c r="Q7" s="143" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+      <x:c r="R7" s="143" t="str">
+        <x:v>Lift &amp; Cut starter recipe</x:v>
+      </x:c>
+      <x:c r="S7" s="143" t="str"/>
+      <x:c r="T7" s="143" t="str"/>
+      <x:c r="U7" s="143" t="str"/>
+      <x:c r="V7" s="160"/>
+      <x:c r="W7" s="143" t="str"/>
+      <x:c r="X7" s="143" t="str"/>
+      <x:c r="Y7" s="143" t="str"/>
+      <x:c r="Z7" s="143" t="str">
+        <x:v>1 servings</x:v>
+      </x:c>
+      <x:c r="AA7" s="143" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="AB7" s="143" t="str">
+        <x:v>Ready</x:v>
+      </x:c>
+      <x:c r="AC7" s="143" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="AD7" s="143" t="str"/>
+      <x:c r="AE7" s="143" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="AF7" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="N7" s="42" t="b">
+      <x:c r="AG7" s="144" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O7" s="16" t="str">
+      <x:c r="AH7" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P7" s="16" t="str">
+      <x:c r="AI7" s="143" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q7" s="16" t="str"/>
-      <x:c r="R7" s="16" t="str">
+      <x:c r="AJ7" s="143" t="str"/>
+      <x:c r="AK7" s="143" t="str">
         <x:v>Use cucumber, lettuce, tomato; no bell peppers.</x:v>
       </x:c>
-      <x:c r="S7" s="16" t="n">
+      <x:c r="AL7" s="160" t="n">
         <x:v>46222.416666666664</x:v>
       </x:c>
     </x:row>
@@ -16113,6 +19570,14 @@
   <x:conditionalFormatting sqref="M2:M1000">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>M2="Yes"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="AA2:AA7">
+    <x:cfRule type="expression" dxfId="1" priority="2">
+      <x:formula>AA2="High"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="2" priority="3">
+      <x:formula>AA2="Low"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
@@ -16128,57 +19593,79 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="3.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="3.5" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="6.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="4.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="5" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="11" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="22" t="str">
+      <x:c r="A1" s="118" t="str">
         <x:v>IngredientRowID</x:v>
       </x:c>
-      <x:c r="B1" s="22" t="str">
+      <x:c r="B1" s="118" t="str">
         <x:v>RecipeID</x:v>
       </x:c>
-      <x:c r="C1" s="22" t="str">
+      <x:c r="C1" s="118" t="str">
         <x:v>IngredientID</x:v>
       </x:c>
-      <x:c r="D1" s="22" t="str">
+      <x:c r="D1" s="118" t="str">
         <x:v>IngredientName</x:v>
       </x:c>
-      <x:c r="E1" s="22" t="str">
+      <x:c r="E1" s="118" t="str">
+        <x:v>SourceLine</x:v>
+      </x:c>
+      <x:c r="F1" s="118" t="str">
         <x:v>Amount</x:v>
       </x:c>
-      <x:c r="F1" s="22" t="str">
+      <x:c r="G1" s="118" t="str">
         <x:v>Unit</x:v>
       </x:c>
-      <x:c r="G1" s="22" t="str">
+      <x:c r="H1" s="118" t="str">
+        <x:v>Grams</x:v>
+      </x:c>
+      <x:c r="I1" s="118" t="str">
+        <x:v>MatchStatus</x:v>
+      </x:c>
+      <x:c r="J1" s="118" t="str">
+        <x:v>MatchConfidence</x:v>
+      </x:c>
+      <x:c r="K1" s="118" t="str">
         <x:v>kcal</x:v>
       </x:c>
-      <x:c r="H1" s="22" t="str">
+      <x:c r="L1" s="118" t="str">
         <x:v>Protein_g</x:v>
       </x:c>
-      <x:c r="I1" s="22" t="str">
+      <x:c r="M1" s="118" t="str">
         <x:v>Carbs_g</x:v>
       </x:c>
-      <x:c r="J1" s="22" t="str">
+      <x:c r="N1" s="118" t="str">
         <x:v>Fat_g</x:v>
       </x:c>
-      <x:c r="K1" s="22" t="str">
+      <x:c r="O1" s="118" t="str">
+        <x:v>Fibre_g</x:v>
+      </x:c>
+      <x:c r="P1" s="118" t="str">
+        <x:v>Sodium_mg</x:v>
+      </x:c>
+      <x:c r="Q1" s="118" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="L1" s="22" t="str">
+      <x:c r="R1" s="118" t="str">
         <x:v>UpdatedAt</x:v>
       </x:c>
     </x:row>
